--- a/GearSage-client/pkgGear/data_raw/megabass_reel_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/megabass_reel_import.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:O19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -447,27 +447,6 @@
       <c r="O1" t="str">
         <v>market_status</v>
       </c>
-      <c r="P1" t="str">
-        <v>series</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>series_cn</v>
-      </c>
-      <c r="R1" t="str">
-        <v>water_type</v>
-      </c>
-      <c r="S1" t="str">
-        <v>description</v>
-      </c>
-      <c r="T1" t="str">
-        <v>source_url</v>
-      </c>
-      <c r="U1" t="str">
-        <v>main_image_url</v>
-      </c>
-      <c r="V1" t="str">
-        <v>local_image_path</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -488,28 +467,31 @@
       <c r="F2" t="str">
         <v/>
       </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
       <c r="H2" t="str">
         <v>spinning</v>
       </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
-        <v/>
-      </c>
-      <c r="R2" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S2" t="str">
-        <v/>
-      </c>
-      <c r="T2" t="str">
-        <v>https://www.megabass.co.jp/site/products/gaus-20x/</v>
-      </c>
-      <c r="U2" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2013/07/main_001_GAUS_20X-2.jpg</v>
-      </c>
-      <c r="V2" t="str">
+      <c r="I2" t="str">
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_GAUS_20X-2.jpg</v>
+      </c>
+      <c r="J2" t="str">
+        <v>2026-04-09T16:03:04.387Z</v>
+      </c>
+      <c r="K2" t="str">
+        <v>2026-04-09T16:03:04.387Z</v>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
         <v/>
       </c>
     </row>
@@ -532,28 +514,31 @@
       <c r="F3" t="str">
         <v/>
       </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
       <c r="H3" t="str">
         <v>spinning</v>
       </c>
-      <c r="P3" t="str">
-        <v/>
-      </c>
-      <c r="Q3" t="str">
-        <v/>
-      </c>
-      <c r="R3" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S3" t="str">
-        <v/>
-      </c>
-      <c r="T3" t="str">
-        <v>https://www.megabass.co.jp/site/products/gaus-30x/</v>
-      </c>
-      <c r="U3" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2013/07/main_001_GAUS_30X-1.jpg</v>
-      </c>
-      <c r="V3" t="str">
+      <c r="I3" t="str">
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_GAUS_30X-1.jpg</v>
+      </c>
+      <c r="J3" t="str">
+        <v>2026-04-09T16:03:04.751Z</v>
+      </c>
+      <c r="K3" t="str">
+        <v>2026-04-09T16:03:04.751Z</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
         <v/>
       </c>
     </row>
@@ -576,28 +561,31 @@
       <c r="F4" t="str">
         <v/>
       </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
       <c r="H4" t="str">
         <v>baitcasting</v>
       </c>
-      <c r="P4" t="str">
-        <v/>
-      </c>
-      <c r="Q4" t="str">
-        <v/>
-      </c>
-      <c r="R4" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S4" t="str">
-        <v/>
-      </c>
-      <c r="T4" t="str">
-        <v>https://www.megabass.co.jp/site/products/lin258hm/</v>
-      </c>
-      <c r="U4" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2013/07/main_001_LIN258HM.jpg</v>
-      </c>
-      <c r="V4" t="str">
+      <c r="I4" t="str">
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_LIN258HM.jpg</v>
+      </c>
+      <c r="J4" t="str">
+        <v>2026-04-09T16:03:05.113Z</v>
+      </c>
+      <c r="K4" t="str">
+        <v>2026-04-09T16:03:05.113Z</v>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
         <v/>
       </c>
     </row>
@@ -620,28 +608,31 @@
       <c r="F5" t="str">
         <v/>
       </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
       <c r="H5" t="str">
         <v>baitcasting</v>
       </c>
-      <c r="P5" t="str">
-        <v/>
-      </c>
-      <c r="Q5" t="str">
-        <v/>
-      </c>
-      <c r="R5" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S5" t="str">
-        <v/>
-      </c>
-      <c r="T5" t="str">
-        <v>https://www.megabass.co.jp/site/products/rc-idaten256/</v>
-      </c>
-      <c r="U5" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2014/06/main_001_megabass_idaten-x_256.jpg</v>
-      </c>
-      <c r="V5" t="str">
+      <c r="I5" t="str">
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_megabass_idaten-x_256.jpg</v>
+      </c>
+      <c r="J5" t="str">
+        <v>2026-04-09T16:03:05.419Z</v>
+      </c>
+      <c r="K5" t="str">
+        <v>2026-04-09T16:03:05.419Z</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
         <v/>
       </c>
     </row>
@@ -664,28 +655,31 @@
       <c r="F6" t="str">
         <v/>
       </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
       <c r="H6" t="str">
         <v>baitcasting</v>
       </c>
-      <c r="P6" t="str">
-        <v/>
-      </c>
-      <c r="Q6" t="str">
-        <v/>
-      </c>
-      <c r="R6" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S6" t="str">
-        <v/>
-      </c>
-      <c r="T6" t="str">
-        <v>https://www.megabass.co.jp/site/products/monoblock_sp_grigio_stone/</v>
-      </c>
-      <c r="U6" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2016/12/main_001_MONOBLOCK_SPECIALE_GRIGIO_STONE.jpg</v>
-      </c>
-      <c r="V6" t="str">
+      <c r="I6" t="str">
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_MONOBLOCK_SPECIALE_GRIGIO_STONE.jpg</v>
+      </c>
+      <c r="J6" t="str">
+        <v>2026-04-09T16:03:05.733Z</v>
+      </c>
+      <c r="K6" t="str">
+        <v>2026-04-09T16:03:05.733Z</v>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
         <v/>
       </c>
     </row>
@@ -708,28 +702,31 @@
       <c r="F7" t="str">
         <v/>
       </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
       <c r="H7" t="str">
         <v>baitcasting</v>
       </c>
-      <c r="P7" t="str">
-        <v/>
-      </c>
-      <c r="Q7" t="str">
-        <v/>
-      </c>
-      <c r="R7" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S7" t="str">
-        <v/>
-      </c>
-      <c r="T7" t="str">
-        <v>https://www.megabass.co.jp/site/products/monoblock_ito-gambler/</v>
-      </c>
-      <c r="U7" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2017/02/main_001_MONOBLOCK_SPECIALE_ITO-GAMBLER.jpg</v>
-      </c>
-      <c r="V7" t="str">
+      <c r="I7" t="str">
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_MONOBLOCK_SPECIALE_ITO-GAMBLER.jpg</v>
+      </c>
+      <c r="J7" t="str">
+        <v>2026-04-09T16:03:06.104Z</v>
+      </c>
+      <c r="K7" t="str">
+        <v>2026-04-09T16:03:06.104Z</v>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
         <v/>
       </c>
     </row>
@@ -752,28 +749,31 @@
       <c r="F8" t="str">
         <v/>
       </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
       <c r="H8" t="str">
         <v>baitcasting</v>
       </c>
-      <c r="P8" t="str">
-        <v/>
-      </c>
-      <c r="Q8" t="str">
-        <v/>
-      </c>
-      <c r="R8" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S8" t="str">
-        <v/>
-      </c>
-      <c r="T8" t="str">
-        <v>https://www.megabass.co.jp/site/products/monoblock-speciale/</v>
-      </c>
-      <c r="U8" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2015/04/main_001_MONOBLOCK_SPECIALE.jpg</v>
-      </c>
-      <c r="V8" t="str">
+      <c r="I8" t="str">
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_MONOBLOCK_SPECIALE.jpg</v>
+      </c>
+      <c r="J8" t="str">
+        <v>2026-04-09T16:03:06.704Z</v>
+      </c>
+      <c r="K8" t="str">
+        <v>2026-04-09T16:03:06.704Z</v>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
         <v/>
       </c>
     </row>
@@ -796,28 +796,31 @@
       <c r="F9" t="str">
         <v/>
       </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
       <c r="H9" t="str">
         <v>baitcasting</v>
       </c>
-      <c r="P9" t="str">
-        <v/>
-      </c>
-      <c r="Q9" t="str">
-        <v/>
-      </c>
-      <c r="R9" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S9" t="str">
-        <v/>
-      </c>
-      <c r="T9" t="str">
-        <v>https://www.megabass.co.jp/site/products/rhodium73/</v>
-      </c>
-      <c r="U9" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2021/01/main_001_megabass_rhodium_73.jpg</v>
-      </c>
-      <c r="V9" t="str">
+      <c r="I9" t="str">
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_megabass_rhodium_73.jpg</v>
+      </c>
+      <c r="J9" t="str">
+        <v>2026-04-09T16:03:07.101Z</v>
+      </c>
+      <c r="K9" t="str">
+        <v>2026-04-09T16:03:07.101Z</v>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
         <v/>
       </c>
     </row>
@@ -840,28 +843,31 @@
       <c r="F10" t="str">
         <v/>
       </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
       <c r="H10" t="str">
         <v>baitcasting</v>
       </c>
-      <c r="P10" t="str">
-        <v/>
-      </c>
-      <c r="Q10" t="str">
-        <v/>
-      </c>
-      <c r="R10" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S10" t="str">
-        <v/>
-      </c>
-      <c r="T10" t="str">
-        <v>https://www.megabass.co.jp/site/products/rhodium81/</v>
-      </c>
-      <c r="U10" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2018/04/main_001_RHODIUM_81.jpg</v>
-      </c>
-      <c r="V10" t="str">
+      <c r="I10" t="str">
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_RHODIUM_81.jpg</v>
+      </c>
+      <c r="J10" t="str">
+        <v>2026-04-09T16:03:07.457Z</v>
+      </c>
+      <c r="K10" t="str">
+        <v>2026-04-09T16:03:07.457Z</v>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
         <v/>
       </c>
     </row>
@@ -884,28 +890,31 @@
       <c r="F11" t="str">
         <v/>
       </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
       <c r="H11" t="str">
         <v>baitcasting</v>
       </c>
-      <c r="P11" t="str">
-        <v/>
-      </c>
-      <c r="Q11" t="str">
-        <v/>
-      </c>
-      <c r="R11" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S11" t="str">
-        <v/>
-      </c>
-      <c r="T11" t="str">
-        <v>https://www.megabass.co.jp/site/products/rhodium63/</v>
-      </c>
-      <c r="U11" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2018/04/main_001_RHODIUM_63.jpg</v>
-      </c>
-      <c r="V11" t="str">
+      <c r="I11" t="str">
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_RHODIUM_63.jpg</v>
+      </c>
+      <c r="J11" t="str">
+        <v>2026-04-09T16:03:07.869Z</v>
+      </c>
+      <c r="K11" t="str">
+        <v>2026-04-09T16:03:07.869Z</v>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
         <v/>
       </c>
     </row>
@@ -928,28 +937,31 @@
       <c r="F12" t="str">
         <v/>
       </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
       <c r="H12" t="str">
         <v>baitcasting</v>
       </c>
-      <c r="P12" t="str">
-        <v/>
-      </c>
-      <c r="Q12" t="str">
-        <v/>
-      </c>
-      <c r="R12" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S12" t="str">
-        <v/>
-      </c>
-      <c r="T12" t="str">
-        <v>https://www.megabass.co.jp/site/products/pagani-r100/</v>
-      </c>
-      <c r="U12" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2013/07/main_001_Pagani_R100-1.jpg</v>
-      </c>
-      <c r="V12" t="str">
+      <c r="I12" t="str">
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_Pagani_R100-1.jpg</v>
+      </c>
+      <c r="J12" t="str">
+        <v>2026-04-09T16:03:08.227Z</v>
+      </c>
+      <c r="K12" t="str">
+        <v>2026-04-09T16:03:08.227Z</v>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
         <v/>
       </c>
     </row>
@@ -972,28 +984,31 @@
       <c r="F13" t="str">
         <v/>
       </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
       <c r="H13" t="str">
         <v>baitcasting</v>
       </c>
-      <c r="P13" t="str">
-        <v/>
-      </c>
-      <c r="Q13" t="str">
-        <v/>
-      </c>
-      <c r="R13" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S13" t="str">
-        <v/>
-      </c>
-      <c r="T13" t="str">
-        <v>https://www.megabass.co.jp/site/products/pagani-p200/</v>
-      </c>
-      <c r="U13" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2013/07/main_001_Pagani_P200_black-chrome.jpg</v>
-      </c>
-      <c r="V13" t="str">
+      <c r="I13" t="str">
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_Pagani_P200_black-chrome.jpg</v>
+      </c>
+      <c r="J13" t="str">
+        <v>2026-04-09T16:03:08.638Z</v>
+      </c>
+      <c r="K13" t="str">
+        <v>2026-04-09T16:03:08.638Z</v>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
         <v/>
       </c>
     </row>
@@ -1016,28 +1031,31 @@
       <c r="F14" t="str">
         <v/>
       </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
       <c r="H14" t="str">
         <v>baitcasting</v>
       </c>
-      <c r="P14" t="str">
-        <v/>
-      </c>
-      <c r="Q14" t="str">
-        <v/>
-      </c>
-      <c r="R14" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S14" t="str">
-        <v/>
-      </c>
-      <c r="T14" t="str">
-        <v>https://www.megabass.co.jp/site/products/pagani-p300/</v>
-      </c>
-      <c r="U14" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2013/07/main_001_Pagani_P300_01_CHAMPAGNE_GOLD.jpg</v>
-      </c>
-      <c r="V14" t="str">
+      <c r="I14" t="str">
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_Pagani_P300_01_CHAMPAGNE_GOLD.jpg</v>
+      </c>
+      <c r="J14" t="str">
+        <v>2026-04-09T16:03:09.002Z</v>
+      </c>
+      <c r="K14" t="str">
+        <v>2026-04-09T16:03:09.002Z</v>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
         <v/>
       </c>
     </row>
@@ -1060,28 +1078,31 @@
       <c r="F15" t="str">
         <v/>
       </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
       <c r="H15" t="str">
         <v>baitcasting</v>
       </c>
-      <c r="P15" t="str">
-        <v/>
-      </c>
-      <c r="Q15" t="str">
-        <v/>
-      </c>
-      <c r="R15" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S15" t="str">
-        <v/>
-      </c>
-      <c r="T15" t="str">
-        <v>https://www.megabass.co.jp/site/products/lauda58/</v>
-      </c>
-      <c r="U15" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2017/02/main_001_LAUDA_58.jpg</v>
-      </c>
-      <c r="V15" t="str">
+      <c r="I15" t="str">
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_LAUDA_58.jpg</v>
+      </c>
+      <c r="J15" t="str">
+        <v>2026-04-09T16:03:09.406Z</v>
+      </c>
+      <c r="K15" t="str">
+        <v>2026-04-09T16:03:09.406Z</v>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
         <v/>
       </c>
     </row>
@@ -1104,28 +1125,31 @@
       <c r="F16" t="str">
         <v/>
       </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
       <c r="H16" t="str">
         <v>baitcasting</v>
       </c>
-      <c r="P16" t="str">
-        <v/>
-      </c>
-      <c r="Q16" t="str">
-        <v/>
-      </c>
-      <c r="R16" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S16" t="str">
-        <v/>
-      </c>
-      <c r="T16" t="str">
-        <v>https://www.megabass.co.jp/site/products/lauda72/</v>
-      </c>
-      <c r="U16" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2016/12/main_001_LAUDA_72.jpg</v>
-      </c>
-      <c r="V16" t="str">
+      <c r="I16" t="str">
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_LAUDA_72.jpg</v>
+      </c>
+      <c r="J16" t="str">
+        <v>2026-04-09T16:03:09.802Z</v>
+      </c>
+      <c r="K16" t="str">
+        <v>2026-04-09T16:03:09.802Z</v>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
         <v/>
       </c>
     </row>
@@ -1148,28 +1172,31 @@
       <c r="F17" t="str">
         <v/>
       </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
       <c r="H17" t="str">
         <v>baitcasting</v>
       </c>
-      <c r="P17" t="str">
-        <v/>
-      </c>
-      <c r="Q17" t="str">
-        <v/>
-      </c>
-      <c r="R17" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S17" t="str">
-        <v/>
-      </c>
-      <c r="T17" t="str">
-        <v>https://www.megabass.co.jp/site/products/lauda72ltd/</v>
-      </c>
-      <c r="U17" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2017/02/main_001_LAUDA_72_LIMITED-EDITION.jpg</v>
-      </c>
-      <c r="V17" t="str">
+      <c r="I17" t="str">
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_LAUDA_72_LIMITED-EDITION.jpg</v>
+      </c>
+      <c r="J17" t="str">
+        <v>2026-04-09T16:03:10.384Z</v>
+      </c>
+      <c r="K17" t="str">
+        <v>2026-04-09T16:03:10.384Z</v>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
         <v/>
       </c>
     </row>
@@ -1192,28 +1219,31 @@
       <c r="F18" t="str">
         <v/>
       </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
       <c r="H18" t="str">
         <v>baitcasting</v>
       </c>
-      <c r="P18" t="str">
-        <v/>
-      </c>
-      <c r="Q18" t="str">
-        <v/>
-      </c>
-      <c r="R18" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S18" t="str">
-        <v/>
-      </c>
-      <c r="T18" t="str">
-        <v>https://www.megabass.co.jp/site/products/ip79/</v>
-      </c>
-      <c r="U18" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2013/08/main_001_IP79.jpg</v>
-      </c>
-      <c r="V18" t="str">
+      <c r="I18" t="str">
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_IP79.jpg</v>
+      </c>
+      <c r="J18" t="str">
+        <v>2026-04-09T16:03:10.796Z</v>
+      </c>
+      <c r="K18" t="str">
+        <v>2026-04-09T16:03:10.796Z</v>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
         <v/>
       </c>
     </row>
@@ -1236,34 +1266,37 @@
       <c r="F19" t="str">
         <v/>
       </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
       <c r="H19" t="str">
         <v>baitcasting</v>
       </c>
-      <c r="P19" t="str">
-        <v/>
-      </c>
-      <c r="Q19" t="str">
-        <v/>
-      </c>
-      <c r="R19" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S19" t="str">
-        <v/>
-      </c>
-      <c r="T19" t="str">
-        <v>https://www.megabass.co.jp/site/products/ip68/</v>
-      </c>
-      <c r="U19" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2014/06/main_001_IP68.jpg</v>
-      </c>
-      <c r="V19" t="str">
+      <c r="I19" t="str">
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_IP68.jpg</v>
+      </c>
+      <c r="J19" t="str">
+        <v>2026-04-09T16:03:11.194Z</v>
+      </c>
+      <c r="K19" t="str">
+        <v>2026-04-09T16:03:11.194Z</v>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:V19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O19"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1366,7 +1399,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v/>
+        <v>MRED50000</v>
       </c>
       <c r="B2" t="str">
         <v>MRE5000</v>
@@ -1431,7 +1464,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v/>
+        <v>MRED50001</v>
       </c>
       <c r="B3" t="str">
         <v>MRE5001</v>
@@ -1629,7 +1662,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v/>
+        <v>MRED50002</v>
       </c>
       <c r="B2" t="str">
         <v>MRE5002</v>
@@ -1691,7 +1724,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v/>
+        <v>MRED50003</v>
       </c>
       <c r="B3" t="str">
         <v>MRE5003</v>
@@ -1753,7 +1786,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v/>
+        <v>MRED50004</v>
       </c>
       <c r="B4" t="str">
         <v>MRE5004</v>
@@ -1815,7 +1848,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v/>
+        <v>MRED50005</v>
       </c>
       <c r="B5" t="str">
         <v>MRE5005</v>
@@ -1877,7 +1910,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v/>
+        <v>MRED50006</v>
       </c>
       <c r="B6" t="str">
         <v>MRE5006</v>
@@ -1939,7 +1972,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v/>
+        <v>MRED50007</v>
       </c>
       <c r="B7" t="str">
         <v>MRE5007</v>
@@ -2001,7 +2034,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v/>
+        <v>MRED50008</v>
       </c>
       <c r="B8" t="str">
         <v>MRE5008</v>
@@ -2063,7 +2096,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v/>
+        <v>MRED50009</v>
       </c>
       <c r="B9" t="str">
         <v>MRE5009</v>
@@ -2125,7 +2158,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v/>
+        <v>MRED50010</v>
       </c>
       <c r="B10" t="str">
         <v>MRE5010</v>
@@ -2187,7 +2220,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v/>
+        <v>MRED50011</v>
       </c>
       <c r="B11" t="str">
         <v>MRE5011</v>
@@ -2249,7 +2282,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v/>
+        <v>MRED50012</v>
       </c>
       <c r="B12" t="str">
         <v>MRE5012</v>
@@ -2311,7 +2344,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v/>
+        <v>MRED50013</v>
       </c>
       <c r="B13" t="str">
         <v>MRE5013</v>
@@ -2373,7 +2406,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v/>
+        <v>MRED50014</v>
       </c>
       <c r="B14" t="str">
         <v>MRE5014</v>
@@ -2435,7 +2468,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v/>
+        <v>MRED50015</v>
       </c>
       <c r="B15" t="str">
         <v>MRE5015</v>
@@ -2497,7 +2530,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v/>
+        <v>MRED50016</v>
       </c>
       <c r="B16" t="str">
         <v>MRE5016</v>
@@ -2559,7 +2592,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v/>
+        <v>MRED50017</v>
       </c>
       <c r="B17" t="str">
         <v>MRE5017</v>

--- a/GearSage-client/pkgGear/data_raw/megabass_reel_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/megabass_reel_import.xlsx
@@ -474,7 +474,7 @@
         <v>spinning</v>
       </c>
       <c r="I2" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_GAUS_20X-2.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/GAUS 20X_main.jpg</v>
       </c>
       <c r="J2" t="str">
         <v>2026-04-09T16:03:04.387Z</v>
@@ -521,7 +521,7 @@
         <v>spinning</v>
       </c>
       <c r="I3" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_GAUS_30X-1.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/GAUS 30X_main.jpg</v>
       </c>
       <c r="J3" t="str">
         <v>2026-04-09T16:03:04.751Z</v>
@@ -568,7 +568,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I4" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_LIN258HM.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/LIN258HM_main.jpg</v>
       </c>
       <c r="J4" t="str">
         <v>2026-04-09T16:03:05.113Z</v>
@@ -615,7 +615,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I5" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_megabass_idaten-x_256.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/RC-IDATEN 256_main.jpg</v>
       </c>
       <c r="J5" t="str">
         <v>2026-04-09T16:03:05.419Z</v>
@@ -662,7 +662,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I6" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_MONOBLOCK_SPECIALE_GRIGIO_STONE.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/MONOBLOCK SPECIALE GRIGIO STONE_main.jpg</v>
       </c>
       <c r="J6" t="str">
         <v>2026-04-09T16:03:05.733Z</v>
@@ -709,7 +709,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I7" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_MONOBLOCK_SPECIALE_ITO-GAMBLER.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/MONOBLOCK SPECIALE ITO-GAMBLER_main.jpg</v>
       </c>
       <c r="J7" t="str">
         <v>2026-04-09T16:03:06.104Z</v>
@@ -756,7 +756,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I8" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_MONOBLOCK_SPECIALE.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/MONOBLOCK SPECIALE_main.jpg</v>
       </c>
       <c r="J8" t="str">
         <v>2026-04-09T16:03:06.704Z</v>
@@ -803,7 +803,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I9" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_megabass_rhodium_73.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/RHODIUM 73_main.jpg</v>
       </c>
       <c r="J9" t="str">
         <v>2026-04-09T16:03:07.101Z</v>
@@ -850,7 +850,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I10" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_RHODIUM_81.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/RHODIUM 81_main.jpg</v>
       </c>
       <c r="J10" t="str">
         <v>2026-04-09T16:03:07.457Z</v>
@@ -897,7 +897,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I11" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_RHODIUM_63.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/RHODIUM 63_main.jpg</v>
       </c>
       <c r="J11" t="str">
         <v>2026-04-09T16:03:07.869Z</v>
@@ -944,7 +944,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I12" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_Pagani_R100-1.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/Pagani R100_main.jpg</v>
       </c>
       <c r="J12" t="str">
         <v>2026-04-09T16:03:08.227Z</v>
@@ -991,7 +991,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I13" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_Pagani_P200_black-chrome.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/Pagani P200_main.jpg</v>
       </c>
       <c r="J13" t="str">
         <v>2026-04-09T16:03:08.638Z</v>
@@ -1038,7 +1038,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I14" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_Pagani_P300_01_CHAMPAGNE_GOLD.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/Pagani P300_main.jpg</v>
       </c>
       <c r="J14" t="str">
         <v>2026-04-09T16:03:09.002Z</v>
@@ -1085,7 +1085,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I15" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_LAUDA_58.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/LAUDA58_main.jpg</v>
       </c>
       <c r="J15" t="str">
         <v>2026-04-09T16:03:09.406Z</v>
@@ -1132,7 +1132,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I16" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_LAUDA_72.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/LAUDA72_main.jpg</v>
       </c>
       <c r="J16" t="str">
         <v>2026-04-09T16:03:09.802Z</v>
@@ -1179,7 +1179,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I17" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_LAUDA_72_LIMITED-EDITION.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/LAUDA72 LIMITED EDITION_main.jpg</v>
       </c>
       <c r="J17" t="str">
         <v>2026-04-09T16:03:10.384Z</v>
@@ -1226,7 +1226,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I18" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_IP79.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/IP79_main.jpg</v>
       </c>
       <c r="J18" t="str">
         <v>2026-04-09T16:03:10.796Z</v>
@@ -1273,7 +1273,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I19" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_IP68.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/IP68_main.jpg</v>
       </c>
       <c r="J19" t="str">
         <v>2026-04-09T16:03:11.194Z</v>

--- a/GearSage-client/pkgGear/data_raw/megabass_reel_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/megabass_reel_import.xlsx
@@ -474,7 +474,7 @@
         <v>spinning</v>
       </c>
       <c r="I2" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/GAUS 20X_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/GAUS%2020X_main.jpg</v>
       </c>
       <c r="J2" t="str">
         <v>2026-04-09T16:03:04.387Z</v>
@@ -521,7 +521,7 @@
         <v>spinning</v>
       </c>
       <c r="I3" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/GAUS 30X_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/GAUS%2030X_main.jpg</v>
       </c>
       <c r="J3" t="str">
         <v>2026-04-09T16:03:04.751Z</v>
@@ -568,7 +568,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I4" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/LIN258HM_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/LIN258HM_main.jpg</v>
       </c>
       <c r="J4" t="str">
         <v>2026-04-09T16:03:05.113Z</v>
@@ -615,7 +615,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I5" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/RC-IDATEN 256_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/RC-IDATEN%20256_main.jpg</v>
       </c>
       <c r="J5" t="str">
         <v>2026-04-09T16:03:05.419Z</v>
@@ -662,7 +662,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I6" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/MONOBLOCK SPECIALE GRIGIO STONE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/MONOBLOCK%20SPECIALE%20GRIGIO%20STONE_main.jpg</v>
       </c>
       <c r="J6" t="str">
         <v>2026-04-09T16:03:05.733Z</v>
@@ -709,7 +709,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I7" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/MONOBLOCK SPECIALE ITO-GAMBLER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/MONOBLOCK%20SPECIALE%20ITO-GAMBLER_main.jpg</v>
       </c>
       <c r="J7" t="str">
         <v>2026-04-09T16:03:06.104Z</v>
@@ -756,7 +756,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I8" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/MONOBLOCK SPECIALE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/MONOBLOCK%20SPECIALE%20GRIGIO%20STONE_main.jpg</v>
       </c>
       <c r="J8" t="str">
         <v>2026-04-09T16:03:06.704Z</v>
@@ -803,7 +803,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I9" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/RHODIUM 73_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/RHODIUM%2073_main.jpg</v>
       </c>
       <c r="J9" t="str">
         <v>2026-04-09T16:03:07.101Z</v>
@@ -850,7 +850,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I10" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/RHODIUM 81_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/RHODIUM%2081_main.jpg</v>
       </c>
       <c r="J10" t="str">
         <v>2026-04-09T16:03:07.457Z</v>
@@ -897,7 +897,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I11" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/RHODIUM 63_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/RHODIUM%2063_main.jpg</v>
       </c>
       <c r="J11" t="str">
         <v>2026-04-09T16:03:07.869Z</v>
@@ -944,7 +944,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I12" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/Pagani R100_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/Pagani%20R100_main.jpg</v>
       </c>
       <c r="J12" t="str">
         <v>2026-04-09T16:03:08.227Z</v>
@@ -991,7 +991,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I13" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/Pagani P200_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/Pagani%20P200_main.jpg</v>
       </c>
       <c r="J13" t="str">
         <v>2026-04-09T16:03:08.638Z</v>
@@ -1038,7 +1038,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I14" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/Pagani P300_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/Pagani%20P300_main.jpg</v>
       </c>
       <c r="J14" t="str">
         <v>2026-04-09T16:03:09.002Z</v>
@@ -1085,7 +1085,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I15" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/LAUDA58_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/LAUDA58_main.jpg</v>
       </c>
       <c r="J15" t="str">
         <v>2026-04-09T16:03:09.406Z</v>
@@ -1132,7 +1132,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I16" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/LAUDA72_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/LAUDA72_main.jpg</v>
       </c>
       <c r="J16" t="str">
         <v>2026-04-09T16:03:09.802Z</v>
@@ -1179,7 +1179,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I17" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/LAUDA72 LIMITED EDITION_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/LAUDA72%20LIMITED%20EDITION_main.jpg</v>
       </c>
       <c r="J17" t="str">
         <v>2026-04-09T16:03:10.384Z</v>
@@ -1226,7 +1226,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I18" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/IP79_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/IP79_main.jpg</v>
       </c>
       <c r="J18" t="str">
         <v>2026-04-09T16:03:10.796Z</v>
@@ -1273,7 +1273,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I19" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/IP68_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/IP68_main.jpg</v>
       </c>
       <c r="J19" t="str">
         <v>2026-04-09T16:03:11.194Z</v>

--- a/GearSage-client/pkgGear/data_raw/megabass_reel_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/megabass_reel_import.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:S19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -447,6 +447,18 @@
       <c r="O1" t="str">
         <v>market_status</v>
       </c>
+      <c r="P1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>market_reference_price</v>
+      </c>
+      <c r="R1" t="str">
+        <v>player_positioning</v>
+      </c>
+      <c r="S1" t="str">
+        <v>player_selling_points</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -459,7 +471,7 @@
         <v>GAUS 20X</v>
       </c>
       <c r="D2" t="str">
-        <v>GAUS 20X</v>
+        <v/>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -477,22 +489,34 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/GAUS%2020X_main.jpg</v>
       </c>
       <c r="J2" t="str">
-        <v>2026-04-09T16:03:04.387Z</v>
+        <v>2026-04-21T12:02:54.928Z</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-04-09T16:03:04.387Z</v>
+        <v>2026-04-21T12:02:54.928Z</v>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>小型高端纺车</v>
       </c>
       <c r="M2" t="str">
-        <v/>
+        <v>その名のとおり、あらゆるものを引き付けてしまう魔性を発揮する、スーパーコンパクトリールが、ついにベールを脱ぎました。 ガウスは、見た目のコンパクトな風貌からは想像できない強靭さと、これまでの基準を覆すハイパワーをスモールボディで発揮する、新世代のスピニングマシンとして開発されています。LIN258HMで高い評価を得た「磁性流体シールドシステム」を、そのコンパクトボディに搭載。大切なギアユニット内部をクリーンな状態に保つだけでなく、ボディとローターは実質無接点のため、シルキーな回転性能が長期間持続。羽の軽さとも評される「X-GRAPHITE COMPSITEROTER」は、スピニングリールにおける回転レスポンスを格段に引き上げると同時に、感度感知にも貢献。また、ハイパワーゲームにおいてローターの変形を抑えるため、ビッグフィッシュのファイトによる負荷をローター全体に分散するために開発した。「高密度カーボンコンポジットボディ」は、恐るべき軽さを実現しただけでなく、ついにその剛性は、マグネシウムを上回るレベルへと昇華。モンスターフィッシュとのドッグファイトでも、ボディのタワミがないから、ギア間が正確に噛み合うシルキーな回転性能と、それらが相まって生み出すトルクフルな巻き上げ性能が確実に維持されます。すべてが、いままでのスピニングリールの基準を覆すオーバースペックリール、GAUSが、いよいよスピニング新時代への扉を開きます。 / The "High Metal Honeycomb Spool" embodies the ultimate in robust and lightweight construction, made possible with Megabass' original carved metal manufacturing process. With the development of the "Magnetic Fluid Shield System," it creates the ideal head balance for spinning reels. The unlikely power generated from the super lightweight micro body gives it the extreme specs needed to combat record breaking fish with the ultimate finesse approach. The perpendicular 45mm crank handle excels at maintaining a steady and constant high speed retrieve with just a slight snapping motion of the wrist. This small superstar displays great ease of use with fast paced finesse rigs and light plugging in streams. / もはやこれ以上はない堅牢さと軽量化を高次元で両立させた、メガバス独自のメタル削り出し構造による「ハイメタル・ハニカムスプール」は、「磁性流体シールドシステム」の開発によって、スピニングリールにおける理想的なヘッドバランスを実現。その超軽量マイクロボディが発揮してしまう、およそ似合わないハイパワーは、究極のフィネスアプローチでレコードフィッシュと真っ向からわたり合うためのエクストリームなスペック。45mmの垂直クランクハンドルは、手首のわずかなスナップモーションで、ブレなく一定スピードを保持した高速リーリングに最適。フィネスリグの素早いピックアップや、ストリームにおけるライトプラッギングで至極の快適性能を発揮する、小さな超新星です。</v>
       </c>
       <c r="N2" t="str">
-        <v/>
+        <v>¥38,000</v>
       </c>
       <c r="O2" t="str">
-        <v/>
+        <v>在售</v>
+      </c>
+      <c r="P2" t="str">
+        <v>その名のとおり、あらゆるものを引き付けてしまう魔性を発揮する、スーパーコンパクトリールが、ついにベールを脱ぎました。 ガウスは、見た目のコンパクトな風貌からは想像できない強靭さと、これまでの基準を覆すハイパワーをスモールボディで発揮する、新世代のスピニングマシンとして開発されています。LIN258HMで高い評価を得た「磁性流体シールドシステム」を、そのコンパクトボディに搭載。大切なギアユニット内部をクリーンな状態に保つだけでなく、ボディとローターは実質無接点のため、シルキーな回転性能が長期間持続。羽の軽さとも評される「X-GRAPHITE COMPSITEROTER」は、スピニングリールにおける回転レスポンスを格段に引き上げると同時に、感度感知にも貢献。また、ハイパワーゲームにおいてローターの変形を抑えるため、ビッグフィッシュのファイトによる負荷をローター全体に分散するために開発した。「高密度カーボンコンポジットボディ」は、恐るべき軽さを実現しただけでなく、ついにその剛性は、マグネシウムを上回るレベルへと昇華。モンスターフィッシュとのドッグファイトでも、ボディのタワミがないから、ギア間が正確に噛み合うシルキーな回転性能と、それらが相まって生み出すトルクフルな巻き上げ性能が確実に維持されます。すべてが、いままでのスピニングリールの基準を覆すオーバースペックリール、GAUSが、いよいよスピニング新時代への扉を開きます。 The "High Metal Honeycomb Spool" embodies the ultimate in robust and lightweight construction, made possible with Megabass' original carved metal manufacturing process. With the development of the "Magnetic Fluid Shield System," it creates the ideal head balance for spinning reels. The unlikely power generated from the super lightweight micro body gives it the extreme specs needed to combat record breaking fish with the ultimate finesse approach. The perpendicular 45mm crank handle excels at maintaining a steady and constant high speed retrieve with just a slight snapping motion of the wrist. This small superstar displays great ease of use with fast paced finesse rigs and light plugging in streams. もはやこれ以上はない堅牢さと軽量化を高次元で両立させた、メガバス独自のメタル削り出し構造による「ハイメタル・ハニカムスプール」は、「磁性流体シールドシステム」の開発によって、スピニングリールにおける理想的なヘッドバランスを実現。その超軽量マイクロボディが発揮してしまう、およそ似合わないハイパワーは、究極のフィネスアプローチでレコードフィッシュと真っ向からわたり合うためのエクストリームなスペック。45mmの垂直クランクハンドルは、手首のわずかなスナップモーションで、ブレなく一定スピードを保持した高速リーリングに最適。フィネスリグの素早いピックアップや、ストリームにおけるライトプラッギングで至極の快適性能を発揮する、小さな超新星です。</v>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v>溪流与轻量精细</v>
+      </c>
+      <c r="S2" t="str">
+        <v>超小机身 / 高响应 / 微饵与溪流操控友好</v>
       </c>
     </row>
     <row r="3">
@@ -506,7 +530,7 @@
         <v>GAUS 30X</v>
       </c>
       <c r="D3" t="str">
-        <v>GAUS 30X</v>
+        <v/>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -524,22 +548,34 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/GAUS%2030X_main.jpg</v>
       </c>
       <c r="J3" t="str">
-        <v>2026-04-09T16:03:04.751Z</v>
+        <v>2026-04-21T12:02:55.416Z</v>
       </c>
       <c r="K3" t="str">
-        <v>2026-04-09T16:03:04.751Z</v>
+        <v>2026-04-21T12:02:55.416Z</v>
       </c>
       <c r="L3" t="str">
-        <v/>
+        <v>高扭矩纺车</v>
       </c>
       <c r="M3" t="str">
-        <v/>
+        <v>その名のとおり、あらゆるものを引き付けてしまう魔性を発揮する、スーパーコンパクトリールが、ついにベールを脱ぎました。 ガウスは、見た目のコンパクトな風貌からは想像できない強靭さと、これまでの基準を覆すハイパワーをスモールボディで発揮する、新世代のスピニングマシンとして開発されています。LIN258HMで高い評価を得た「磁性流体シールドシステム」を、そのコンパクトボディに搭載。大切なギアユニット内部をクリーンな状態に保つだけでなく、ボディとローターは実質無接点のため、シルキーな回転性能が長期間持続。羽の軽さとも評される「X-GRAPHITE COMPSITEROTER」は、スピニングリールにおける回転レスポンスを格段に引き上げると同時に、感度感知にも貢献。また、ハイパワーゲームにおいてローターの変形を抑えるため、ビッグフィッシュのファイトによる負荷をローター全体に分散するために開発した。「高密度カーボンコンポジットボディ」は、恐るべき軽さを実現しただけでなく、ついにその剛性は、マグネシウムを上回るレベルへと昇華。モンスターフィッシュとのドッグファイトでも、ボディのタワミがないから、ギア間が正確に噛み合うシルキーな回転性能と、それらが相まって生み出すトルクフルな巻き上げ性能が確実に維持されます。すべてが、いままでのスピニングリールの基準を覆すオーバースペックリール、GAUSが、いよいよスピニング新時代への扉を開きます。 / The GAUS30X is a model tuned for active salt water games. The GAUS's solid high rigidity body and instantaneous torque generation will handle big fish with ease. Megabass' unique "Super Lightweight Carbon Hybrid Spool" reduces spool deflection by spreading out the massive weight loads that can occur during heavy line use. The GAUS is equipped with many cutting edge technologies and features to give it the edge in high power games, such as the magnetic fluid system, the powerful 55m machine cut handle, the design that allows for smooth initial rotation and control, the M Drag System, the high power gear system, etc. Once you use it, you won't be able to put it down. That's the power of the GAUS. / ガウス30Xは、シーバスゲームをはじめ、アクティブなソルトゲームにアジャストするモデルです。ガウスが身につけた圧倒的な高剛性ボディと、瞬時に太いトルクを立ち上げるシルキードライブフィールがビッグフィッシュゲームを快適にこなします。メガバス独自の「超軽量カーボン・ハイブリットスプール」は、太いラインにかかる多大な負荷がもたらすスプールのたわみや高荷重を分散して低減化。磁性流体システム、55mmの強靭なマシンカットハンドル、緻密に計算されたスムースな滑り出しとその制御について、徹底追及されたＭドラグシステム、ハイパワーギアシステムなどなど・・数え上げたらキリがありませんが、スピニングリールにおける新次元のハイパワーゲームは、ガウスが武装した最新テクノロジーによって、ついに具現化。一度お使いいただくと、手放せなくなる快適性能こそが、ガウスの魔力を物語ります。</v>
       </c>
       <c r="N3" t="str">
-        <v/>
+        <v>¥44,000</v>
       </c>
       <c r="O3" t="str">
-        <v/>
+        <v>在售</v>
+      </c>
+      <c r="P3" t="str">
+        <v>その名のとおり、あらゆるものを引き付けてしまう魔性を発揮する、スーパーコンパクトリールが、ついにベールを脱ぎました。 ガウスは、見た目のコンパクトな風貌からは想像できない強靭さと、これまでの基準を覆すハイパワーをスモールボディで発揮する、新世代のスピニングマシンとして開発されています。LIN258HMで高い評価を得た「磁性流体シールドシステム」を、そのコンパクトボディに搭載。大切なギアユニット内部をクリーンな状態に保つだけでなく、ボディとローターは実質無接点のため、シルキーな回転性能が長期間持続。羽の軽さとも評される「X-GRAPHITE COMPSITEROTER」は、スピニングリールにおける回転レスポンスを格段に引き上げると同時に、感度感知にも貢献。また、ハイパワーゲームにおいてローターの変形を抑えるため、ビッグフィッシュのファイトによる負荷をローター全体に分散するために開発した。「高密度カーボンコンポジットボディ」は、恐るべき軽さを実現しただけでなく、ついにその剛性は、マグネシウムを上回るレベルへと昇華。モンスターフィッシュとのドッグファイトでも、ボディのタワミがないから、ギア間が正確に噛み合うシルキーな回転性能と、それらが相まって生み出すトルクフルな巻き上げ性能が確実に維持されます。すべてが、いままでのスピニングリールの基準を覆すオーバースペックリール、GAUSが、いよいよスピニング新時代への扉を開きます。 The GAUS30X is a model tuned for active salt water games. The GAUS's solid high rigidity body and instantaneous torque generation will handle big fish with ease. Megabass' unique "Super Lightweight Carbon Hybrid Spool" reduces spool deflection by spreading out the massive weight loads that can occur during heavy line use. The GAUS is equipped with many cutting edge technologies and features to give it the edge in high power games, such as the magnetic fluid system, the powerful 55m machine cut handle, the design that allows for smooth initial rotation and control, the M Drag System, the high power gear system, etc. Once you use it, you won't be able to put it down. That's the power of the GAUS. ガウス30Xは、シーバスゲームをはじめ、アクティブなソルトゲームにアジャストするモデルです。ガウスが身につけた圧倒的な高剛性ボディと、瞬時に太いトルクを立ち上げるシルキードライブフィールがビッグフィッシュゲームを快適にこなします。メガバス独自の「超軽量カーボン・ハイブリットスプール」は、太いラインにかかる多大な負荷がもたらすスプールのたわみや高荷重を分散して低減化。磁性流体システム、55mmの強靭なマシンカットハンドル、緻密に計算されたスムースな滑り出しとその制御について、徹底追及されたＭドラグシステム、ハイパワーギアシステムなどなど・・数え上げたらキリがありませんが、スピニングリールにおける新次元のハイパワーゲームは、ガウスが武装した最新テクノロジーによって、ついに具現化。一度お使いいただくと、手放せなくなる快適性能こそが、ガウスの魔力を物語ります。</v>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v>海水轻中型纺车</v>
+      </c>
+      <c r="S3" t="str">
+        <v>小机身高扭矩 / 轻盐到近海兼顾 / 快速回收友好</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +589,7 @@
         <v>LIN258HM</v>
       </c>
       <c r="D4" t="str">
-        <v>LIN258HM</v>
+        <v/>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -571,22 +607,34 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/LIN258HM_main.jpg</v>
       </c>
       <c r="J4" t="str">
-        <v>2026-04-09T16:03:05.113Z</v>
+        <v>2026-04-21T12:02:55.901Z</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-04-09T16:03:05.113Z</v>
+        <v>2026-04-21T12:02:55.901Z</v>
       </c>
       <c r="L4" t="str">
-        <v/>
+        <v>高刚性BF/泛用</v>
       </c>
       <c r="M4" t="str">
-        <v/>
+        <v>カヴァーフィネスゲームをはじめ、ラフウォーターでのバスボートゲームなど、激しい釣りに耐えうるタフな野外戦用スピニングがLIN258HMである。アルミメタル製のドライブギアは、超高精度マシンカットで「一個一個」「一歯一歯」の工程で歯面の最終仕上げを施すという念の入れ様。噛み合うピニオンギアのデジタル数値に、ドライブギアをミクロンの精度で適合させるという極みの技。リンのシームレスなシルキードライブは、これに加えてギアを支えるハウジングもたわみの発生しない高精度・高剛性のアルミメタル製なのだ。勘合部さえもすべて「一個一個」ミクロンの精度で削り出す。クラフツマンの魂を込めたこの丹念な工程こそが、リンのまるでガタのない強靭な駆動部分を造り出している。リンのハンドルを回せば「噛み合い接触」の感触よりも「スベリ接触」の感触が強めに出ていることが感じていただけると思う。このシルキーな噛み合いこそが、回せば瞬時に立ち上がるロスのないハイパワーと、高次元の感度伝達性を生み出すのだ。なお、メカハウジングとして、可動部には最新の磁性流体シールドで保護。極限の遠心力低減化を追求したローター部分はグラファイトコンポジット製。スプールも限界まで肉抜きされたハニカム構造で耐久性を両立。ハンドルは、最新のメカニカルパワーアシストを施し、もはやワンランク上の機種として使用可能なオーバーパワースペックを持つリールなのだ。世界記録バスのパワーランに耐え得るために、Ｍドラグシステムはスムーズで耐久性・耐力のある高荷重カーボンの多重構造を採用。卓越した追撃性能を具現化したLIN258HMは、バスフィッシングはもちろんのこと、シーバスゲームやノースエリアの巨大鱒族を相手にも存分に威力を発揮。その名のとおり、凛として戦うモンスタースペックのスピニングリールなのだ。 / The LIN258HM is a battle reel made to withstand tough and intense fishing. The aluminum gear drive is finished off by carefully machining each gear tooth with extreme precision. The extreme engineering skills employed allow the drive gear to be fitted to the pinion gear with only microns to spare. The seamless silky drive of the LIN is made of high-precision high-rigidity aluminum, which prevents deflection of the supporting gear housing. The precision manufacturing process combined with the soul of the craftsmen who assemble the product are what make the LIN what it is. This silky gear engagement of the LIN is what creates its sensitivity and creates the high power that engages immediately when turning the handle. Furthermore, in the mechanical housing, the moving parts are protected with the latest magnetic fluid shield. The rotor is made from lightweight graphite composites to reduce centrifugal force and increase stability. The spool also has also undergone weight reduction, implementing a durable honeycomb construction. The mechanical power assist of the handle gives it power equal to higher spec'd models. In order to withstand the power of world record size bass, the M drag system is incorporated with its multiple structured, smooth, durable, heavyweight carbon. The LIN258HM is a powerful spinning reel that shows excellent performance when dealing with bass, sea bass, and large trout species.</v>
       </c>
       <c r="N4" t="str">
-        <v/>
+        <v>¥55,000</v>
       </c>
       <c r="O4" t="str">
-        <v/>
+        <v>在售</v>
+      </c>
+      <c r="P4" t="str">
+        <v>カヴァーフィネスゲームをはじめ、ラフウォーターでのバスボートゲームなど、激しい釣りに耐えうるタフな野外戦用スピニングがLIN258HMである。アルミメタル製のドライブギアは、超高精度マシンカットで「一個一個」「一歯一歯」の工程で歯面の最終仕上げを施すという念の入れ様。噛み合うピニオンギアのデジタル数値に、ドライブギアをミクロンの精度で適合させるという極みの技。リンのシームレスなシルキードライブは、これに加えてギアを支えるハウジングもたわみの発生しない高精度・高剛性のアルミメタル製なのだ。勘合部さえもすべて「一個一個」ミクロンの精度で削り出す。クラフツマンの魂を込めたこの丹念な工程こそが、リンのまるでガタのない強靭な駆動部分を造り出している。リンのハンドルを回せば「噛み合い接触」の感触よりも「スベリ接触」の感触が強めに出ていることが感じていただけると思う。このシルキーな噛み合いこそが、回せば瞬時に立ち上がるロスのないハイパワーと、高次元の感度伝達性を生み出すのだ。なお、メカハウジングとして、可動部には最新の磁性流体シールドで保護。極限の遠心力低減化を追求したローター部分はグラファイトコンポジット製。スプールも限界まで肉抜きされたハニカム構造で耐久性を両立。ハンドルは、最新のメカニカルパワーアシストを施し、もはやワンランク上の機種として使用可能なオーバーパワースペックを持つリールなのだ。世界記録バスのパワーランに耐え得るために、Ｍドラグシステムはスムーズで耐久性・耐力のある高荷重カーボンの多重構造を採用。卓越した追撃性能を具現化したLIN258HMは、バスフィッシングはもちろんのこと、シーバスゲームやノースエリアの巨大鱒族を相手にも存分に威力を発揮。その名のとおり、凛として戦うモンスタースペックのスピニングリールなのだ。 The LIN258HM is a battle reel made to withstand tough and intense fishing. The aluminum gear drive is finished off by carefully machining each gear tooth with extreme precision. The extreme engineering skills employed allow the drive gear to be fitted to the pinion gear with only microns to spare. The seamless silky drive of the LIN is made of high-precision high-rigidity aluminum, which prevents deflection of the supporting gear housing. The precision manufacturing process combined with the soul of the craftsmen who assemble the product are what make the LIN what it is. This silky gear engagement of the LIN is what creates its sensitivity and creates the high power that engages immediately when turning the handle. Furthermore, in the mechanical housing, the moving parts are protected with the latest magnetic fluid shield. The rotor is made from lightweight graphite composites to reduce centrifugal force and increase stability. The spool also has also undergone weight reduction, implementing a durable honeycomb construction. The mechanical power assist of the handle gives it power equal to higher spec'd models. In order to withstand the power of world record size bass, the M drag system is incorporated with its multiple structured, smooth, durable, heavyweight carbon. The LIN258HM is a powerful spinning reel that shows excellent performance when dealing with bass, sea bass, and large trout species.</v>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v>重视刚性的高端泛用</v>
+      </c>
+      <c r="S4" t="str">
+        <v>金属机身 / 丝滑卷收 / 重视耐久与力量</v>
       </c>
     </row>
     <row r="5">
@@ -600,7 +648,7 @@
         <v>RC-IDATEN 256</v>
       </c>
       <c r="D5" t="str">
-        <v>RC-IDATEN 256</v>
+        <v/>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -618,22 +666,34 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/RC-IDATEN%20256_main.jpg</v>
       </c>
       <c r="J5" t="str">
-        <v>2026-04-09T16:03:05.419Z</v>
+        <v>2026-04-21T12:02:56.380Z</v>
       </c>
       <c r="K5" t="str">
-        <v>2026-04-09T16:03:05.419Z</v>
+        <v>2026-04-21T12:02:56.380Z</v>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>高速精细</v>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>「レーシングコンディション256」の軽量コンセプトとパッケージングレイアウトを踏襲し、ハンドル一回転におけるローター回転を高速化。ハンドル一巻きのライン巻き上げ量を大幅にアップした高速リールが、「IDATENプロジェクト」の最新形態として、遂に具現化。ハイスピードスピニングリールで痩せがちだった巻き上げトルクは、IDATEN256が過去のものとしています。「スピード」と「パワー」、この相反する要素の最大公約数にジャストミートさせた新たなIDATENが、効率よく釣り勝つためのハイテンポなフィネスゲームを展開します。 / RC-IDATEN 256 inherits the Racing Condition 256 model’s lightweight concept, while at the same time delivering faster rotor rotation per handle turn.RC-IDATEN 256 has been tuned for blazing speed without stripping away underlying power, bringing a new standard of high-speed gearing and power. Increased retrieve speed without the loss of lightness or power: this is the latest core incarnation of the IDATEN reel project.Experience the perfect combination of speed and power with the new IDATEN 256. / * The photograph is a prototype / もはやこれ以上はない堅牢さと軽量化を高次元で両立させた、メガバス独自のメタル削り出し構造による「ハイメタル・ハニカムスプール」は、「磁性流体シールドシステム」の開発によって、スピニングリールにおける理想的なヘッドバランスを実現。その超軽量マイクロボディが発揮してしまう、およそ似合わないハイパワーは、究極のフィネスアプローチでレコードフィッシュと真っ向からわたり合うためのエクストリームなスペック。</v>
       </c>
       <c r="N5" t="str">
-        <v/>
+        <v>¥59,800</v>
       </c>
       <c r="O5" t="str">
-        <v/>
+        <v>在售</v>
+      </c>
+      <c r="P5" t="str">
+        <v>「レーシングコンディション256」の軽量コンセプトとパッケージングレイアウトを踏襲し、ハンドル一回転におけるローター回転を高速化。ハンドル一巻きのライン巻き上げ量を大幅にアップした高速リールが、「IDATENプロジェクト」の最新形態として、遂に具現化。ハイスピードスピニングリールで痩せがちだった巻き上げトルクは、IDATEN256が過去のものとしています。「スピード」と「パワー」、この相反する要素の最大公約数にジャストミートさせた新たなIDATENが、効率よく釣り勝つためのハイテンポなフィネスゲームを展開します。 RC-IDATEN 256 inherits the Racing Condition 256 model’s lightweight concept, while at the same time delivering faster rotor rotation per handle turn.RC-IDATEN 256 has been tuned for blazing speed without stripping away underlying power, bringing a new standard of high-speed gearing and power. Increased retrieve speed without the loss of lightness or power: this is the latest core incarnation of the IDATEN reel project.Experience the perfect combination of speed and power with the new IDATEN 256. * The photograph is a prototype もはやこれ以上はない堅牢さと軽量化を高次元で両立させた、メガバス独自のメタル削り出し構造による「ハイメタル・ハニカムスプール」は、「磁性流体シールドシステム」の開発によって、スピニングリールにおける理想的なヘッドバランスを実現。その超軽量マイクロボディが発揮してしまう、およそ似合わないハイパワーは、究極のフィネスアプローチでレコードフィッシュと真っ向からわたり合うためのエクストリームなスペック。</v>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v>快节奏精细回收</v>
+      </c>
+      <c r="S5" t="str">
+        <v>高速回收 / 精细与效率兼顾 / 轻量路亚友好</v>
       </c>
     </row>
     <row r="6">
@@ -647,7 +707,7 @@
         <v>MONOBLOCK SPECIALE GRIGIO STONE</v>
       </c>
       <c r="D6" t="str">
-        <v>MONOBLOCK SPECIALE GRIGIO STONE</v>
+        <v/>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -665,22 +725,34 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/MONOBLOCK%20SPECIALE%20GRIGIO%20STONE_main.jpg</v>
       </c>
       <c r="J6" t="str">
-        <v>2026-04-09T16:03:05.733Z</v>
+        <v>2026-04-21T12:02:57.077Z</v>
       </c>
       <c r="K6" t="str">
-        <v>2026-04-09T16:03:05.733Z</v>
+        <v>2026-04-21T12:02:57.077Z</v>
       </c>
       <c r="L6" t="str">
-        <v/>
+        <v>高端收藏机</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>進化するモノブロック / An Evolving Monoblock.</v>
       </c>
       <c r="N6" t="str">
-        <v/>
+        <v>¥92,500</v>
       </c>
       <c r="O6" t="str">
-        <v/>
+        <v>在售</v>
+      </c>
+      <c r="P6" t="str">
+        <v>進化するモノブロック An Evolving Monoblock.</v>
+      </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
+        <v>重视造型与把玩的玩家</v>
+      </c>
+      <c r="S6" t="str">
+        <v>Monoblock 进化版 / 收藏属性强 / 传统高端鼓轮美学</v>
       </c>
     </row>
     <row r="7">
@@ -694,7 +766,7 @@
         <v>MONOBLOCK SPECIALE ITO-GAMBLER</v>
       </c>
       <c r="D7" t="str">
-        <v>MONOBLOCK SPECIALE ITO-GAMBLER</v>
+        <v/>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -712,22 +784,34 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/MONOBLOCK%20SPECIALE%20ITO-GAMBLER_main.jpg</v>
       </c>
       <c r="J7" t="str">
-        <v>2026-04-09T16:03:06.104Z</v>
+        <v>2026-04-21T12:02:57.755Z</v>
       </c>
       <c r="K7" t="str">
-        <v>2026-04-09T16:03:06.104Z</v>
+        <v>2026-04-21T12:02:57.755Z</v>
       </c>
       <c r="L7" t="str">
-        <v/>
+        <v>高端收藏机</v>
       </c>
       <c r="M7" t="str">
-        <v/>
+        <v>進化するモノブロック / An Evolving Monoblock.</v>
       </c>
       <c r="N7" t="str">
-        <v/>
+        <v>¥92,500</v>
       </c>
       <c r="O7" t="str">
-        <v/>
+        <v>在售</v>
+      </c>
+      <c r="P7" t="str">
+        <v>進化するモノブロック An Evolving Monoblock.</v>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
+        <v>重视造型与把玩的玩家</v>
+      </c>
+      <c r="S7" t="str">
+        <v>Monoblock 进化版 / 收藏属性强 / 传统高端鼓轮美学</v>
       </c>
     </row>
     <row r="8">
@@ -741,7 +825,7 @@
         <v>MONOBLOCK SPECIALE</v>
       </c>
       <c r="D8" t="str">
-        <v>MONOBLOCK SPECIALE</v>
+        <v/>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -756,25 +840,37 @@
         <v>baitcasting</v>
       </c>
       <c r="I8" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/MONOBLOCK%20SPECIALE%20GRIGIO%20STONE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/MONOBLOCK%20SPECIALE_main.jpg</v>
       </c>
       <c r="J8" t="str">
-        <v>2026-04-09T16:03:06.704Z</v>
+        <v>2026-04-21T12:02:58.400Z</v>
       </c>
       <c r="K8" t="str">
-        <v>2026-04-09T16:03:06.704Z</v>
+        <v>2026-04-21T12:02:58.400Z</v>
       </c>
       <c r="L8" t="str">
-        <v/>
+        <v>高性能旗舰鼓轮</v>
       </c>
       <c r="M8" t="str">
-        <v/>
+        <v>スペチアーレとは、イタリア語で「特別」の意味。その名の通り、スペックアップされた数々の先進的スペシャルファンクションを満載された究極のハイパフォーマンスマシンです。 / ファストムービングルアーの引き抵抗と、カヴァーゲームのハイパワーファイトがもたらす高荷重ストレスを極限まで低減化させ、ストレスフリーを徹底追求した絶妙なギアユニットでセッティング。 / 堅牢素材の分子レベルでの結束構造を破壊させないため、あえて無垢の高強度アルミブロックから一品一品削り出す、超軽量・高剛性モノコックフレームとサイドプレートパーツ、ダイヤルユニットフレーム、ギアボックスとギアハウジングは圧巻。 / もはや悦楽の境地に至る「ゼロフリクション・シルキーハンドル・ドライビング」と極限まで同調最適化させた、究極のレベルワインド・セッティング。</v>
       </c>
       <c r="N8" t="str">
-        <v/>
+        <v>¥92,500</v>
       </c>
       <c r="O8" t="str">
-        <v/>
+        <v>在售</v>
+      </c>
+      <c r="P8" t="str">
+        <v>スペチアーレとは、イタリア語で「特別」の意味。その名の通り、スペックアップされた数々の先進的スペシャルファンクションを満載された究極のハイパフォーマンスマシンです。 ファストムービングルアーの引き抵抗と、カヴァーゲームのハイパワーファイトがもたらす高荷重ストレスを極限まで低減化させ、ストレスフリーを徹底追求した絶妙なギアユニットでセッティング。 堅牢素材の分子レベルでの結束構造を破壊させないため、あえて無垢の高強度アルミブロックから一品一品削り出す、超軽量・高剛性モノコックフレームとサイドプレートパーツ、ダイヤルユニットフレーム、ギアボックスとギアハウジングは圧巻。 もはや悦楽の境地に至る「ゼロフリクション・シルキーハンドル・ドライビング」と極限まで同調最適化させた、究極のレベルワインド・セッティング。 すべてのムービングパーツを滑らかに作動させる、随所に搭載し尽くした独自の超高精度ボールベアリングパーツをはじめ、新設計のカーボンマグダイヤルシステム、ロープロファイリングITOベンディングピラー、極限までの肉抜きを施したモノコックハンドルシャフト、高剛性ノブシャフト、超軽量・超高精度マシンカットによる超高回転フローティングスプールなど、「スペチアーレ」は、世界各地でジャパンメイドの最高傑作と評される「モノブロック」の進化系にふさわしいスペシャルファンクションでデザインされています。 その名のとおり、選ばれしアングラーのみが生涯お使いいただける芸術作品です。 As its name suggest, the MONOBLOCK SPECIALE features many meticulously upgraded specs to elevate this reel to an exceptional standard of advanced mechanics. Machined from a single block of high-density aluminum, the light yet exceptionally rigid frame is mated to aluminum sideplates, unit frame and gear box for outstanding structural integrity and raw power. Featuring a zero friction silk-handle drive, anglers will experience the ultimate smooth-feel retrieve and special levelwind settings. Premium ball bearings are set in all moving parts to reduce friction and reduce weight, with a custom handle, knob shaft and machine-cut floating spool concept. The SPECIALE is designed to reduce retrieve fatigue and control heavy-cover battles with monsters, delivering stress-free power and performance. Team Megabass is proud to introduce the SPECIALE, the most advanced model in Monoblock series to date. * The photograph is a prototype.</v>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="R8" t="str">
+        <v>高端快饵与重装</v>
+      </c>
+      <c r="S8" t="str">
+        <v>高性能机体 / 高刚性与顺滑并重 / 旗舰鼓轮路线</v>
       </c>
     </row>
     <row r="9">
@@ -788,7 +884,7 @@
         <v>RHODIUM 73</v>
       </c>
       <c r="D9" t="str">
-        <v>RHODIUM 73</v>
+        <v/>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -806,22 +902,34 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/RHODIUM%2073_main.jpg</v>
       </c>
       <c r="J9" t="str">
-        <v>2026-04-09T16:03:07.101Z</v>
+        <v>2026-04-21T12:02:59.044Z</v>
       </c>
       <c r="K9" t="str">
-        <v>2026-04-09T16:03:07.101Z</v>
+        <v>2026-04-21T12:02:59.044Z</v>
       </c>
       <c r="L9" t="str">
-        <v/>
+        <v>高速泛用主力</v>
       </c>
       <c r="M9" t="str">
-        <v/>
+        <v>持ち得るすべてのテクニックを駆使して「フルコンタクト」する釣り。突如として訪れる一瞬のビッグチャンスを確実に手繰り寄せる。近年のマルチプレイングスタイルのバスフィッシングにおいて、ワンチャンスをものにする強靭なメンタリティと、「果敢な攻め」は、欠かせない。新剛体マシン、ロジウムは、アイティオーエンジニアリングによる屈強な超軽量メタルフレームを基本骨格とし、圧巻の巻き上げトルクを瞬時に叩きだすシルキードライブフィールの超精密ギアレイアウトパッケージと、リールビルドにおける最先端テクノロジーをあますことなく導入。その上で、タフなフィールドを多様なメソッドで制するための、「特別なファインチューン」の数々を随所に施している。アキュラシーを大幅にアップさせつつバックラッシュを極限まで低減化させた、「AIRブレーキシステム」。超軽量インダクトローターと超軽量・超々ジュラルミンSVスプール「メガバスブランキングエディション」とのシンクロナイズによって、ピッチングでは驚異的な低弾道キャストを実現。カバーのより奥の奥へと伸びていくスキッピングは圧巻だ。その上、ロングディスタンスキャストでは、わずか４gの軽量ルアーをストレスフリーで投げ込むことができるマルチプレイングパフォーマンスは、ストレスフリーの「フルコンタクト・バスフィッシング」を高次元で実現させている。デストロイヤーシリーズ、ヴァルキリーシリーズ、あらゆるロッドへの優れたマッチ・ザ・バランスも、ロジウムの多様なパフォーマンスのひとつである。 / ※The photograph is a prototype. / TシェイプレベルワインドがクラッチON・OFFに応じて半回転する「ターンアラウンドスタイル」のTWSを採用。キャスティング時にはレベルワインドが前方に回転し、ラインはTシェイプレベルワインドの幅広部を通ってスムーズに放出される。リトリーブ時にはレベルワインドが後ろ方向に倒れる形で半回転し、レベルワインド下部の溝にラインが誘導され、タイトかつ平行に巻き取られる。飛距離アップ＆トラブルフリーの特長はそのままに、タフさにもこだわる。 / 従来通りのルアーが使える事は当然として、軽量ルアーをもストレスなく投げることができ、しかもスプール強度も犠牲にしない。それが次世代のバーサタイル。メガバスのベイトリールはマグネット式のブレーキシステムを採用している。十分な耐久性はもちろん、瞬時にブレーキ設定が可能な外部調整ダイヤル、天候に左右されない安定したブレーキ力。ピンスポット値に調整できない限り最高出力を発揮しない、また時に意図に反する出力を生む他のシステムとは大きく異なり、マグネット式ブレーキならではの実戦メリットを最大限に引き出したSVは、最小限のマグダイヤルの調整だけで4g前後の軽量リグから重量級ルアーまでを文字通りストレスフリーで扱える。スプールを交換したり、サイドプレートを開けたりして、セッティングに時間を掛ける事もない。ルアーの守備範囲が一番広いSVは、陸っぱりからボートまでスタイルやフィールドを選ばない。マグネット式ブレーキの有効性を極限まで高めたSVコンセプトは、まさにバーサタイルリールの新スタンダードなのである。</v>
       </c>
       <c r="N9" t="str">
-        <v/>
+        <v>¥32,000</v>
       </c>
       <c r="O9" t="str">
-        <v/>
+        <v>在售</v>
+      </c>
+      <c r="P9" t="str">
+        <v>持ち得るすべてのテクニックを駆使して「フルコンタクト」する釣り。突如として訪れる一瞬のビッグチャンスを確実に手繰り寄せる。近年のマルチプレイングスタイルのバスフィッシングにおいて、ワンチャンスをものにする強靭なメンタリティと、「果敢な攻め」は、欠かせない。新剛体マシン、ロジウムは、アイティオーエンジニアリングによる屈強な超軽量メタルフレームを基本骨格とし、圧巻の巻き上げトルクを瞬時に叩きだすシルキードライブフィールの超精密ギアレイアウトパッケージと、リールビルドにおける最先端テクノロジーをあますことなく導入。その上で、タフなフィールドを多様なメソッドで制するための、「特別なファインチューン」の数々を随所に施している。アキュラシーを大幅にアップさせつつバックラッシュを極限まで低減化させた、「AIRブレーキシステム」。超軽量インダクトローターと超軽量・超々ジュラルミンSVスプール「メガバスブランキングエディション」とのシンクロナイズによって、ピッチングでは驚異的な低弾道キャストを実現。カバーのより奥の奥へと伸びていくスキッピングは圧巻だ。その上、ロングディスタンスキャストでは、わずか４gの軽量ルアーをストレスフリーで投げ込むことができるマルチプレイングパフォーマンスは、ストレスフリーの「フルコンタクト・バスフィッシング」を高次元で実現させている。デストロイヤーシリーズ、ヴァルキリーシリーズ、あらゆるロッドへの優れたマッチ・ザ・バランスも、ロジウムの多様なパフォーマンスのひとつである。 ※The photograph is a prototype. TシェイプレベルワインドがクラッチON・OFFに応じて半回転する「ターンアラウンドスタイル」のTWSを採用。キャスティング時にはレベルワインドが前方に回転し、ラインはTシェイプレベルワインドの幅広部を通ってスムーズに放出される。リトリーブ時にはレベルワインドが後ろ方向に倒れる形で半回転し、レベルワインド下部の溝にラインが誘導され、タイトかつ平行に巻き取られる。飛距離アップ＆トラブルフリーの特長はそのままに、タフさにもこだわる。 従来通りのルアーが使える事は当然として、軽量ルアーをもストレスなく投げることができ、しかもスプール強度も犠牲にしない。それが次世代のバーサタイル。メガバスのベイトリールはマグネット式のブレーキシステムを採用している。十分な耐久性はもちろん、瞬時にブレーキ設定が可能な外部調整ダイヤル、天候に左右されない安定したブレーキ力。ピンスポット値に調整できない限り最高出力を発揮しない、また時に意図に反する出力を生む他のシステムとは大きく異なり、マグネット式ブレーキならではの実戦メリットを最大限に引き出したSVは、最小限のマグダイヤルの調整だけで4g前後の軽量リグから重量級ルアーまでを文字通りストレスフリーで扱える。スプールを交換したり、サイドプレートを開けたりして、セッティングに時間を掛ける事もない。ルアーの守備範囲が一番広いSVは、陸っぱりからボートまでスタイルやフィールドを選ばない。マグネット式ブレーキの有効性を極限まで高めたSVコンセプトは、まさにバーサタイルリールの新スタンダードなのである。 超軽量かつ高精度なアイティオーエンジニアリング・ブランキングスプール。TWSとの相乗効果で高速回転のままトラブルなく低弾道キャストやスキッピングを可能に。わずか4gの軽量リグやルアーのストレスフリーのロングディスタンスキャストから、ビッグベイトアプローチまでマルチに対応する。</v>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+      <c r="R9" t="str">
+        <v>鲈鱼泛用与快饵</v>
+      </c>
+      <c r="S9" t="str">
+        <v>高速比 / 低弹道操控 / Cover 游戏友好</v>
       </c>
     </row>
     <row r="10">
@@ -835,7 +943,7 @@
         <v>RHODIUM 81</v>
       </c>
       <c r="D10" t="str">
-        <v>RHODIUM 81</v>
+        <v/>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -853,22 +961,34 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/RHODIUM%2081_main.jpg</v>
       </c>
       <c r="J10" t="str">
-        <v>2026-04-09T16:03:07.457Z</v>
+        <v>2026-04-21T12:02:59.672Z</v>
       </c>
       <c r="K10" t="str">
-        <v>2026-04-09T16:03:07.457Z</v>
+        <v>2026-04-21T12:02:59.672Z</v>
       </c>
       <c r="L10" t="str">
-        <v/>
+        <v>超高速泛用主力</v>
       </c>
       <c r="M10" t="str">
-        <v/>
+        <v>持ち得るすべてのテクニックを駆使して「フルコンタクト」する釣り。突如として訪れる一瞬のビッグチャンスを確実に手繰り寄せる。近年のマルチプレイングスタイルのバスフィッシングにおいて、ワンチャンスをものにする強靭なメンタリティと、「果敢な攻め」は、欠かせない。新剛体マシン、ロジウムは、アイティオーエンジニアリングによる屈強な超軽量メタルフレームを基本骨格とし、圧巻の巻き上げトルクを瞬時に叩きだすシルキードライブフィールの超精密ギアレイアウトパッケージと、リールビルドにおける最先端テクノロジーをあますことなく導入。その上で、タフなフィールドを多様なメソッドで制するための、「特別なファインチューン」の数々を随所に施している。アキュラシーを大幅にアップさせつつバックラッシュを極限まで低減化させた、「AIRブレーキシステム」。超軽量インダクトローターと超軽量・超々ジュラルミンSVスプール「メガバスブランキングエディション」とのシンクロナイズによって、ピッチングでは驚異的な低弾道キャストを実現。カバーのより奥の奥へと伸びていくスキッピングは圧巻だ。その上、ロングディスタンスキャストでは、わずか４gの軽量ルアーをストレスフリーで投げ込むことができるマルチプレイングパフォーマンスは、ストレスフリーの「フルコンタクト・バスフィッシング」を高次元で実現させている。デストロイヤーシリーズ、ヴァルキリーシリーズ、あらゆるロッドへの優れたマッチ・ザ・バランスも、ロジウムの多様なパフォーマンスのひとつである。 / ※The photograph is a prototype. / TシェイプレベルワインドがクラッチON・OFFに応じて半回転する「ターンアラウンドスタイル」のTWSを採用。キャスティング時にはレベルワインドが前方に回転し、ラインはTシェイプレベルワインドの幅広部を通ってスムーズに放出される。リトリーブ時にはレベルワインドが後ろ方向に倒れる形で半回転し、レベルワインド下部の溝にラインが誘導され、タイトかつ平行に巻き取られる。飛距離アップ＆トラブルフリーの特長はそのままに、タフさにもこだわる。 / 従来通りのルアーが使える事は当然として、軽量ルアーをもストレスなく投げることができ、しかもスプール強度も犠牲にしない。それが次世代のバーサタイル。メガバスのベイトリールはマグネット式のブレーキシステムを採用している。十分な耐久性はもちろん、瞬時にブレーキ設定が可能な外部調整ダイヤル、天候に左右されない安定したブレーキ力。ピンスポット値に調整できない限り最高出力を発揮しない、また時に意図に反する出力を生む他のシステムとは大きく異なり、マグネット式ブレーキならではの実戦メリットを最大限に引き出したSVは、最小限のマグダイヤルの調整だけで4g前後の軽量リグから重量級ルアーまでを文字通りストレスフリーで扱える。スプールを交換したり、サイドプレートを開けたりして、セッティングに時間を掛ける事もない。ルアーの守備範囲が一番広いSVは、陸っぱりからボートまでスタイルやフィールドを選ばない。マグネット式ブレーキの有効性を極限まで高めたSVコンセプトは、まさにバーサタイルリールの新スタンダードなのである。</v>
       </c>
       <c r="N10" t="str">
-        <v/>
+        <v>¥32,000</v>
       </c>
       <c r="O10" t="str">
-        <v/>
+        <v>在售</v>
+      </c>
+      <c r="P10" t="str">
+        <v>持ち得るすべてのテクニックを駆使して「フルコンタクト」する釣り。突如として訪れる一瞬のビッグチャンスを確実に手繰り寄せる。近年のマルチプレイングスタイルのバスフィッシングにおいて、ワンチャンスをものにする強靭なメンタリティと、「果敢な攻め」は、欠かせない。新剛体マシン、ロジウムは、アイティオーエンジニアリングによる屈強な超軽量メタルフレームを基本骨格とし、圧巻の巻き上げトルクを瞬時に叩きだすシルキードライブフィールの超精密ギアレイアウトパッケージと、リールビルドにおける最先端テクノロジーをあますことなく導入。その上で、タフなフィールドを多様なメソッドで制するための、「特別なファインチューン」の数々を随所に施している。アキュラシーを大幅にアップさせつつバックラッシュを極限まで低減化させた、「AIRブレーキシステム」。超軽量インダクトローターと超軽量・超々ジュラルミンSVスプール「メガバスブランキングエディション」とのシンクロナイズによって、ピッチングでは驚異的な低弾道キャストを実現。カバーのより奥の奥へと伸びていくスキッピングは圧巻だ。その上、ロングディスタンスキャストでは、わずか４gの軽量ルアーをストレスフリーで投げ込むことができるマルチプレイングパフォーマンスは、ストレスフリーの「フルコンタクト・バスフィッシング」を高次元で実現させている。デストロイヤーシリーズ、ヴァルキリーシリーズ、あらゆるロッドへの優れたマッチ・ザ・バランスも、ロジウムの多様なパフォーマンスのひとつである。 ※The photograph is a prototype. TシェイプレベルワインドがクラッチON・OFFに応じて半回転する「ターンアラウンドスタイル」のTWSを採用。キャスティング時にはレベルワインドが前方に回転し、ラインはTシェイプレベルワインドの幅広部を通ってスムーズに放出される。リトリーブ時にはレベルワインドが後ろ方向に倒れる形で半回転し、レベルワインド下部の溝にラインが誘導され、タイトかつ平行に巻き取られる。飛距離アップ＆トラブルフリーの特長はそのままに、タフさにもこだわる。 従来通りのルアーが使える事は当然として、軽量ルアーをもストレスなく投げることができ、しかもスプール強度も犠牲にしない。それが次世代のバーサタイル。メガバスのベイトリールはマグネット式のブレーキシステムを採用している。十分な耐久性はもちろん、瞬時にブレーキ設定が可能な外部調整ダイヤル、天候に左右されない安定したブレーキ力。ピンスポット値に調整できない限り最高出力を発揮しない、また時に意図に反する出力を生む他のシステムとは大きく異なり、マグネット式ブレーキならではの実戦メリットを最大限に引き出したSVは、最小限のマグダイヤルの調整だけで4g前後の軽量リグから重量級ルアーまでを文字通りストレスフリーで扱える。スプールを交換したり、サイドプレートを開けたりして、セッティングに時間を掛ける事もない。ルアーの守備範囲が一番広いSVは、陸っぱりからボートまでスタイルやフィールドを選ばない。マグネット式ブレーキの有効性を極限まで高めたSVコンセプトは、まさにバーサタイルリールの新スタンダードなのである。 超軽量かつ高精度なアイティオーエンジニアリング・ブランキングスプール。TWSとの相乗効果で高速回転のままトラブルなく低弾道キャストやスキッピングを可能に。わずか4gの軽量リグやルアーのストレスフリーのロングディスタンスキャストから、ビッグベイトアプローチまでマルチに対応する。</v>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="R10" t="str">
+        <v>快节奏鲈鱼路亚</v>
+      </c>
+      <c r="S10" t="str">
+        <v>更高回收速度 / 快节奏搜索 / 快饵友好</v>
       </c>
     </row>
     <row r="11">
@@ -882,7 +1002,7 @@
         <v>RHODIUM 63</v>
       </c>
       <c r="D11" t="str">
-        <v>RHODIUM 63</v>
+        <v/>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -900,22 +1020,34 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/RHODIUM%2063_main.jpg</v>
       </c>
       <c r="J11" t="str">
-        <v>2026-04-09T16:03:07.869Z</v>
+        <v>2026-04-21T12:03:00.367Z</v>
       </c>
       <c r="K11" t="str">
-        <v>2026-04-09T16:03:07.869Z</v>
+        <v>2026-04-21T12:03:00.367Z</v>
       </c>
       <c r="L11" t="str">
-        <v/>
+        <v>低速扭矩主力</v>
       </c>
       <c r="M11" t="str">
-        <v/>
+        <v>持ち得るすべてのテクニックを駆使して「フルコンタクト」する釣り。突如として訪れる一瞬のビッグチャンスを確実に手繰り寄せる。近年のマルチプレイングスタイルのバスフィッシングにおいて、ワンチャンスをものにする強靭なメンタリティと、「果敢な攻め」は、欠かせない。新剛体マシン、ロジウムは、アイティオーエンジニアリングによる屈強な超軽量メタルフレームを基本骨格とし、圧巻の巻き上げトルクを瞬時に叩きだすシルキードライブフィールの超精密ギアレイアウトパッケージと、リールビルドにおける最先端テクノロジーをあますことなく導入。その上で、タフなフィールドを多様なメソッドで制するための、「特別なファインチューン」の数々を随所に施している。アキュラシーを大幅にアップさせつつバックラッシュを極限まで低減化させた、「AIRブレーキシステム」。超軽量インダクトローターと超軽量・超々ジュラルミンSVスプール「メガバスブランキングエディション」とのシンクロナイズによって、ピッチングでは驚異的な低弾道キャストを実現。カバーのより奥の奥へと伸びていくスキッピングは圧巻だ。その上、ロングディスタンスキャストでは、わずか４gの軽量ルアーをストレスフリーで投げ込むことができるマルチプレイングパフォーマンスは、ストレスフリーの「フルコンタクト・バスフィッシング」を高次元で実現させている。デストロイヤーシリーズ、ヴァルキリーシリーズ、あらゆるロッドへの優れたマッチ・ザ・バランスも、ロジウムの多様なパフォーマンスのひとつである。 / ※The photograph is a prototype. / TシェイプレベルワインドがクラッチON・OFFに応じて半回転する「ターンアラウンドスタイル」のTWSを採用。キャスティング時にはレベルワインドが前方に回転し、ラインはTシェイプレベルワインドの幅広部を通ってスムーズに放出される。リトリーブ時にはレベルワインドが後ろ方向に倒れる形で半回転し、レベルワインド下部の溝にラインが誘導され、タイトかつ平行に巻き取られる。飛距離アップ＆トラブルフリーの特長はそのままに、タフさにもこだわる。 / 従来通りのルアーが使える事は当然として、軽量ルアーをもストレスなく投げることができ、しかもスプール強度も犠牲にしない。それが次世代のバーサタイル。メガバスのベイトリールはマグネット式のブレーキシステムを採用している。十分な耐久性はもちろん、瞬時にブレーキ設定が可能な外部調整ダイヤル、天候に左右されない安定したブレーキ力。ピンスポット値に調整できない限り最高出力を発揮しない、また時に意図に反する出力を生む他のシステムとは大きく異なり、マグネット式ブレーキならではの実戦メリットを最大限に引き出したSVは、最小限のマグダイヤルの調整だけで4g前後の軽量リグから重量級ルアーまでを文字通りストレスフリーで扱える。スプールを交換したり、サイドプレートを開けたりして、セッティングに時間を掛ける事もない。ルアーの守備範囲が一番広いSVは、陸っぱりからボートまでスタイルやフィールドを選ばない。マグネット式ブレーキの有効性を極限まで高めたSVコンセプトは、まさにバーサタイルリールの新スタンダードなのである。</v>
       </c>
       <c r="N11" t="str">
-        <v/>
+        <v>¥32,000</v>
       </c>
       <c r="O11" t="str">
-        <v/>
+        <v>在售</v>
+      </c>
+      <c r="P11" t="str">
+        <v>持ち得るすべてのテクニックを駆使して「フルコンタクト」する釣り。突如として訪れる一瞬のビッグチャンスを確実に手繰り寄せる。近年のマルチプレイングスタイルのバスフィッシングにおいて、ワンチャンスをものにする強靭なメンタリティと、「果敢な攻め」は、欠かせない。新剛体マシン、ロジウムは、アイティオーエンジニアリングによる屈強な超軽量メタルフレームを基本骨格とし、圧巻の巻き上げトルクを瞬時に叩きだすシルキードライブフィールの超精密ギアレイアウトパッケージと、リールビルドにおける最先端テクノロジーをあますことなく導入。その上で、タフなフィールドを多様なメソッドで制するための、「特別なファインチューン」の数々を随所に施している。アキュラシーを大幅にアップさせつつバックラッシュを極限まで低減化させた、「AIRブレーキシステム」。超軽量インダクトローターと超軽量・超々ジュラルミンSVスプール「メガバスブランキングエディション」とのシンクロナイズによって、ピッチングでは驚異的な低弾道キャストを実現。カバーのより奥の奥へと伸びていくスキッピングは圧巻だ。その上、ロングディスタンスキャストでは、わずか４gの軽量ルアーをストレスフリーで投げ込むことができるマルチプレイングパフォーマンスは、ストレスフリーの「フルコンタクト・バスフィッシング」を高次元で実現させている。デストロイヤーシリーズ、ヴァルキリーシリーズ、あらゆるロッドへの優れたマッチ・ザ・バランスも、ロジウムの多様なパフォーマンスのひとつである。 ※The photograph is a prototype. TシェイプレベルワインドがクラッチON・OFFに応じて半回転する「ターンアラウンドスタイル」のTWSを採用。キャスティング時にはレベルワインドが前方に回転し、ラインはTシェイプレベルワインドの幅広部を通ってスムーズに放出される。リトリーブ時にはレベルワインドが後ろ方向に倒れる形で半回転し、レベルワインド下部の溝にラインが誘導され、タイトかつ平行に巻き取られる。飛距離アップ＆トラブルフリーの特長はそのままに、タフさにもこだわる。 従来通りのルアーが使える事は当然として、軽量ルアーをもストレスなく投げることができ、しかもスプール強度も犠牲にしない。それが次世代のバーサタイル。メガバスのベイトリールはマグネット式のブレーキシステムを採用している。十分な耐久性はもちろん、瞬時にブレーキ設定が可能な外部調整ダイヤル、天候に左右されない安定したブレーキ力。ピンスポット値に調整できない限り最高出力を発揮しない、また時に意図に反する出力を生む他のシステムとは大きく異なり、マグネット式ブレーキならではの実戦メリットを最大限に引き出したSVは、最小限のマグダイヤルの調整だけで4g前後の軽量リグから重量級ルアーまでを文字通りストレスフリーで扱える。スプールを交換したり、サイドプレートを開けたりして、セッティングに時間を掛ける事もない。ルアーの守備範囲が一番広いSVは、陸っぱりからボートまでスタイルやフィールドを選ばない。マグネット式ブレーキの有効性を極限まで高めたSVコンセプトは、まさにバーサタイルリールの新スタンダードなのである。 超軽量かつ高精度なアイティオーエンジニアリング・ブランキングスプール。TWSとの相乗効果で高速回転のままトラブルなく低弾道キャストやスキッピングを可能に。わずか4gの軽量リグやルアーのストレスフリーのロングディスタンスキャストから、ビッグベイトアプローチまでマルチに対応する。</v>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
+        <v>卷阻饵与扭矩取向</v>
+      </c>
+      <c r="S11" t="str">
+        <v>低速高扭矩 / 卷阻饵稳定 / 力量感突出</v>
       </c>
     </row>
     <row r="12">
@@ -929,7 +1061,7 @@
         <v>Pagani R100</v>
       </c>
       <c r="D12" t="str">
-        <v>Pagani R100</v>
+        <v/>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -947,22 +1079,34 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/Pagani%20R100_main.jpg</v>
       </c>
       <c r="J12" t="str">
-        <v>2026-04-09T16:03:08.227Z</v>
+        <v>2026-04-21T12:03:00.881Z</v>
       </c>
       <c r="K12" t="str">
-        <v>2026-04-09T16:03:08.227Z</v>
+        <v>2026-04-21T12:03:00.881Z</v>
       </c>
       <c r="L12" t="str">
-        <v/>
+        <v>复古高端鼓轮</v>
       </c>
       <c r="M12" t="str">
-        <v/>
+        <v>スプールのリムひとつでさえ、すべて職人の手組みで制作。全ユニットをパーツ単体に細胞分解できてしまう究極のピラードリールが実現しました。R100は、オトナのトップウォータープラッガーのためだけに開発。 モノブロックよりもコンパクトかつ重厚なボディと、手書きのスケッチからそのまま起こしたデザインがもたらす圧倒的な美は、CAD/CAMで設計される最新のリールでは味わえないフィッシングハイをもたらします。 気持ちよくロングキャストできるクワトロサーボブレーキを搭載しています。 / Everything down to the spool rim is hand assembled by our expert craftsmen. The R100 was developed only for mature top water pluggers. It sports a body that is thicker and more compact than that of the Monoblock, and the design is taken from hand drawn sketches, resulting in a stunningly beautiful product that surpasses the elegance of the latest CAD/CAM designed reels. It features a quatro servo brake that allows for comfortable, long distance casting.</v>
       </c>
       <c r="N12" t="str">
-        <v/>
+        <v>¥42,800</v>
       </c>
       <c r="O12" t="str">
-        <v/>
+        <v>在售</v>
+      </c>
+      <c r="P12" t="str">
+        <v>スプールのリムひとつでさえ、すべて職人の手組みで制作。全ユニットをパーツ単体に細胞分解できてしまう究極のピラードリールが実現しました。R100は、オトナのトップウォータープラッガーのためだけに開発。 モノブロックよりもコンパクトかつ重厚なボディと、手書きのスケッチからそのまま起こしたデザインがもたらす圧倒的な美は、CAD/CAMで設計される最新のリールでは味わえないフィッシングハイをもたらします。 気持ちよくロングキャストできるクワトロサーボブレーキを搭載しています。 Everything down to the spool rim is hand assembled by our expert craftsmen. The R100 was developed only for mature top water pluggers. It sports a body that is thicker and more compact than that of the Monoblock, and the design is taken from hand drawn sketches, resulting in a stunningly beautiful product that surpasses the elegance of the latest CAD/CAM designed reels. It features a quatro servo brake that allows for comfortable, long distance casting.</v>
+      </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
+      <c r="R12" t="str">
+        <v>顶水与风格玩家</v>
+      </c>
+      <c r="S12" t="str">
+        <v>复古机体 / 顶水友好 / 造型与手感并重</v>
       </c>
     </row>
     <row r="13">
@@ -976,7 +1120,7 @@
         <v>Pagani P200</v>
       </c>
       <c r="D13" t="str">
-        <v>Pagani P200</v>
+        <v/>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -994,22 +1138,34 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/Pagani%20P200_main.jpg</v>
       </c>
       <c r="J13" t="str">
-        <v>2026-04-09T16:03:08.638Z</v>
+        <v>2026-04-21T12:03:01.354Z</v>
       </c>
       <c r="K13" t="str">
-        <v>2026-04-09T16:03:08.638Z</v>
+        <v>2026-04-21T12:03:01.354Z</v>
       </c>
       <c r="L13" t="str">
-        <v/>
+        <v>复古高端鼓轮</v>
       </c>
       <c r="M13" t="str">
-        <v/>
+        <v>メガバスリールは、現時点で考えうる最先端・工業技術を終結して製作しています。熟練のファクトリーマイスターが持てる技を駆使し、精巧に作り上げていくリールです。レースに勝つために凌ぎを削ってきた元レーシングエンジニアが在籍するメガバス・リールファクトリーの生産規模は、決して大きくありません。 マグネシウム、超々ジュラルミン、チタン、モリブデン、ハイエンドアルミニウム、カーボングラファイト、カーボンコンポジットマテリアル、ハイブリッドABSなどなど、あらゆる素材を導入し、大メーカーとは異なる、ガレージファクトリーならではの「ワンメイク」アプローチが頻発します。 フィールドに設計室を置き、実戦検証型の設計手法と大胆なチューニングメニューを即時編み出しながら、高度な新素材加工ノウハウの数々を大胆に注ぎ込むメガバス・リールファクトリーのスタッフは言います。「釣果が先。図面は、あと」だと。したがって、もう２度と作らないモデルや、使い手に一定以上の技量レベルを要求するピーキーなモデルさえ存在します。これは、メーカーを名乗るものとしてはどうかと思いますが、「絶対釣果」をたたき出すために、マーケティングを無視したマイスターたちのわがままでモノづくりがなされている、ガレージファクトリーならではの現場感覚です。 そんな「スペック至上主義」を主張するレースエンジニアが腕をふるう一方で、メガバス・リールファクトリーには、芸術性を深く追求するアーチストがいます。 彼らはいいます。「感動が先。図面は、あと」ここで彼らも、設計図があとになってしまうのですが、スケッチブックを手に絵を描き、美的主観を優先し、何度もモデリングします。彼らにとって作りたいのは、リールの姿をした「芸術作品」だからです。手にすればオーラを放ち、数学的に割り切れぬ交錯する微妙な直状線と、微妙な曲線が織り成す、「数奇屋づくり」の伝統美学がもたらす重厚な存在感。これらは、大人の休日において、質の高いフィッシングプレジャーを提供してくれると確信しているからです。ファクトリーのアーチストたちが直視するのは、レースエンジニアたちが重視する数学的なパフォーマンス・スペックではなく、官能的な感性スペックです。こうして、ISシリーズとは対極的ともいえる「パガーニリール」が誕生しました。 P200にいける、左右で異なる真円形と楕円形を、たった４本のピラーで連結し、異形構造がひとつの集合体を目指したときに見せる結合美は、建築構造物の美学に共通するものです。これらは、あなたの釣果を直接的に向上させるものではありませんが、手にしたあなたの心を躍らせ、フィッシングのモチベーションを大いに上げてくれる、重要なメンタリティのエレメントです。ファクトリーのアーチストたちは、パガーニリールの開発と製作を通じて、美の探究と表現に取り組んでいます。 / The Pagani P200 is a downsized model of the immensely popular Pagani Reel flagship model, the P300. Under its nostalgic stylings, the P200 incorporates various high tech elements such as a high gear, infinite mechanism, silky drive unit, and quatro servo brake. It's a light plugging model combining beauty and utility, and fully realizing the potential of modern tops.</v>
       </c>
       <c r="N13" t="str">
-        <v/>
+        <v>¥41,000</v>
       </c>
       <c r="O13" t="str">
-        <v/>
+        <v>在售</v>
+      </c>
+      <c r="P13" t="str">
+        <v>メガバスリールは、現時点で考えうる最先端・工業技術を終結して製作しています。熟練のファクトリーマイスターが持てる技を駆使し、精巧に作り上げていくリールです。レースに勝つために凌ぎを削ってきた元レーシングエンジニアが在籍するメガバス・リールファクトリーの生産規模は、決して大きくありません。 マグネシウム、超々ジュラルミン、チタン、モリブデン、ハイエンドアルミニウム、カーボングラファイト、カーボンコンポジットマテリアル、ハイブリッドABSなどなど、あらゆる素材を導入し、大メーカーとは異なる、ガレージファクトリーならではの「ワンメイク」アプローチが頻発します。 フィールドに設計室を置き、実戦検証型の設計手法と大胆なチューニングメニューを即時編み出しながら、高度な新素材加工ノウハウの数々を大胆に注ぎ込むメガバス・リールファクトリーのスタッフは言います。「釣果が先。図面は、あと」だと。したがって、もう２度と作らないモデルや、使い手に一定以上の技量レベルを要求するピーキーなモデルさえ存在します。これは、メーカーを名乗るものとしてはどうかと思いますが、「絶対釣果」をたたき出すために、マーケティングを無視したマイスターたちのわがままでモノづくりがなされている、ガレージファクトリーならではの現場感覚です。 そんな「スペック至上主義」を主張するレースエンジニアが腕をふるう一方で、メガバス・リールファクトリーには、芸術性を深く追求するアーチストがいます。 彼らはいいます。「感動が先。図面は、あと」ここで彼らも、設計図があとになってしまうのですが、スケッチブックを手に絵を描き、美的主観を優先し、何度もモデリングします。彼らにとって作りたいのは、リールの姿をした「芸術作品」だからです。手にすればオーラを放ち、数学的に割り切れぬ交錯する微妙な直状線と、微妙な曲線が織り成す、「数奇屋づくり」の伝統美学がもたらす重厚な存在感。これらは、大人の休日において、質の高いフィッシングプレジャーを提供してくれると確信しているからです。ファクトリーのアーチストたちが直視するのは、レースエンジニアたちが重視する数学的なパフォーマンス・スペックではなく、官能的な感性スペックです。こうして、ISシリーズとは対極的ともいえる「パガーニリール」が誕生しました。 P200にいける、左右で異なる真円形と楕円形を、たった４本のピラーで連結し、異形構造がひとつの集合体を目指したときに見せる結合美は、建築構造物の美学に共通するものです。これらは、あなたの釣果を直接的に向上させるものではありませんが、手にしたあなたの心を躍らせ、フィッシングのモチベーションを大いに上げてくれる、重要なメンタリティのエレメントです。ファクトリーのアーチストたちは、パガーニリールの開発と製作を通じて、美の探究と表現に取り組んでいます。 The Pagani P200 is a downsized model of the immensely popular Pagani Reel flagship model, the P300. Under its nostalgic stylings, the P200 incorporates various high tech elements such as a high gear, infinite mechanism, silky drive unit, and quatro servo brake. It's a light plugging model combining beauty and utility, and fully realizing the potential of modern tops.</v>
+      </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
+      <c r="R13" t="str">
+        <v>顶水与风格玩家</v>
+      </c>
+      <c r="S13" t="str">
+        <v>P300 缩小版 / 轻插饵友好 / 兼顾美感与实用</v>
       </c>
     </row>
     <row r="14">
@@ -1023,7 +1179,7 @@
         <v>Pagani P300</v>
       </c>
       <c r="D14" t="str">
-        <v>Pagani P300</v>
+        <v/>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -1041,22 +1197,34 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/Pagani%20P300_main.jpg</v>
       </c>
       <c r="J14" t="str">
-        <v>2026-04-09T16:03:09.002Z</v>
+        <v>2026-04-21T12:03:01.851Z</v>
       </c>
       <c r="K14" t="str">
-        <v>2026-04-09T16:03:09.002Z</v>
+        <v>2026-04-21T12:03:01.851Z</v>
       </c>
       <c r="L14" t="str">
-        <v/>
+        <v>复古高端鼓轮</v>
       </c>
       <c r="M14" t="str">
-        <v/>
+        <v>メガバス・モダンリールの雄、モノブロックとは対極的な、伝統的なリールづくりの製法にこだわって仕上げていく、パガーニのトラディショナルリール。日本の名工が丹念に作り上げていく、古き良き時代のモノづくりが、ソウルフルなプロダクツを目指すアイティオーエンジニアリングによって、現代に蘇ります。 パガーニP300は、音楽に例えると・・・jazz（ジャズ）のような感覚。使い手の感性よって、様々な表情をみせ、いつも異なるフィーリングで楽しませてくれる、 そんな、楽しいキカイです。クルマに例えたら・・・キャブレター時代のスポーツカーのようです。 / Unlike our modern reel, the Monoblock, the Pagani is built focusing on the process of authentic, traditional reel building. The masterful Japanese craftwork from years past is brought back to life by ITO ENGINEERING. If it were music, the Pagani would be jazz. If it were a car, it would be an old hot rod. Pagani P300 is an enjoyable tool that will deliver various experiences in response to each unique user, offering them an expressive and dynamic range of performance.</v>
       </c>
       <c r="N14" t="str">
-        <v/>
+        <v>¥40,000</v>
       </c>
       <c r="O14" t="str">
-        <v/>
+        <v>在售</v>
+      </c>
+      <c r="P14" t="str">
+        <v>メガバス・モダンリールの雄、モノブロックとは対極的な、伝統的なリールづくりの製法にこだわって仕上げていく、パガーニのトラディショナルリール。日本の名工が丹念に作り上げていく、古き良き時代のモノづくりが、ソウルフルなプロダクツを目指すアイティオーエンジニアリングによって、現代に蘇ります。 パガーニP300は、音楽に例えると・・・jazz（ジャズ）のような感覚。使い手の感性よって、様々な表情をみせ、いつも異なるフィーリングで楽しませてくれる、 そんな、楽しいキカイです。クルマに例えたら・・・キャブレター時代のスポーツカーのようです。 Unlike our modern reel, the Monoblock, the Pagani is built focusing on the process of authentic, traditional reel building. The masterful Japanese craftwork from years past is brought back to life by ITO ENGINEERING. If it were music, the Pagani would be jazz. If it were a car, it would be an old hot rod. Pagani P300 is an enjoyable tool that will deliver various experiences in response to each unique user, offering them an expressive and dynamic range of performance.</v>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+      <c r="R14" t="str">
+        <v>大尺寸顶水与风格玩家</v>
+      </c>
+      <c r="S14" t="str">
+        <v>Pagani 旗舰尺寸 / 风格化机体 / 复古鼓轮体验</v>
       </c>
     </row>
     <row r="15">
@@ -1070,7 +1238,7 @@
         <v>LAUDA58</v>
       </c>
       <c r="D15" t="str">
-        <v>LAUDA58</v>
+        <v/>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -1088,22 +1256,34 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/LAUDA58_main.jpg</v>
       </c>
       <c r="J15" t="str">
-        <v>2026-04-09T16:03:09.406Z</v>
+        <v>2026-04-21T12:03:02.339Z</v>
       </c>
       <c r="K15" t="str">
-        <v>2026-04-09T16:03:09.406Z</v>
+        <v>2026-04-21T12:03:02.339Z</v>
       </c>
       <c r="L15" t="str">
-        <v/>
+        <v>低速泛用主力</v>
       </c>
       <c r="M15" t="str">
-        <v/>
+        <v>バーサタイルシリーズ「Lauda」のローギアモデル、Lauda58。 / ギア比5.8：1のローギアだからこそできるリズミカルなリーリングによって、アクションの安定性やレンジキープの正確性が向上。意識してゆっくり巻くのとは一味違う生き生きしたルアーアクションを生み出します。 / さらに、パワーライトコルク・ラウンドノブを採用し、ディープクランクなどの引き抵抗の強いルアーでも、シルキーで軽やかなリーリングが可能。 / SVコンセプトが実現したのは、ライト〜ヘビーファストムービングまで快適に使用可能な対応力と、アゲインストでのロングキャスト。</v>
       </c>
       <c r="N15" t="str">
-        <v/>
+        <v>¥38,500</v>
       </c>
       <c r="O15" t="str">
-        <v/>
+        <v>在售</v>
+      </c>
+      <c r="P15" t="str">
+        <v>バーサタイルシリーズ「Lauda」のローギアモデル、Lauda58。 ギア比5.8：1のローギアだからこそできるリズミカルなリーリングによって、アクションの安定性やレンジキープの正確性が向上。意識してゆっくり巻くのとは一味違う生き生きしたルアーアクションを生み出します。 さらに、パワーライトコルク・ラウンドノブを採用し、ディープクランクなどの引き抵抗の強いルアーでも、シルキーで軽やかなリーリングが可能。 SVコンセプトが実現したのは、ライト〜ヘビーファストムービングまで快適に使用可能な対応力と、アゲインストでのロングキャスト。 Lauda 72とは対照的に、リズミカルなゲームを展開できる、「トルクフル」なバーサタイルモデルです。 LAUDA 58 is a workhorse, designed for applications requiring increased torque and control. Optimal 5.8:1 ratio allows for faster-tempo handle rotation for stable retrieve speeds, which is ideal for cranking and high-resistance applications. Lightweight, durable composite cork knobs are incredibly comfortable and provide secure grip in all conditions. SV Spool concept’s versatility allows for both finesse and heavyweight applications, placing effortless performance in the angler’s hands. The LAUDA 58 is a versatile high-torque model for applications requiring consistent control. ※The photograph is a prototype.</v>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <v>卷阻饵与稳定检索</v>
+      </c>
+      <c r="S15" t="str">
+        <v>5.8 低速比 / 深潜饵友好 / 扭矩导向</v>
       </c>
     </row>
     <row r="16">
@@ -1117,7 +1297,7 @@
         <v>LAUDA72</v>
       </c>
       <c r="D16" t="str">
-        <v>LAUDA72</v>
+        <v/>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1135,22 +1315,34 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/LAUDA72_main.jpg</v>
       </c>
       <c r="J16" t="str">
-        <v>2026-04-09T16:03:09.802Z</v>
+        <v>2026-04-21T12:03:02.843Z</v>
       </c>
       <c r="K16" t="str">
-        <v>2026-04-09T16:03:09.802Z</v>
+        <v>2026-04-21T12:03:02.843Z</v>
       </c>
       <c r="L16" t="str">
-        <v/>
+        <v>高速泛用主力</v>
       </c>
       <c r="M16" t="str">
-        <v/>
+        <v>7.2：1のハイギア・バーサタイルモデルLauda72。 / 超々ジュラルミン製軽量SVスプールのなめらかな初動により、低弾道で伸びのあるピッチングが可能。高次元のショートディスタンスゲームにはもちろん、強風下のロングキャストにおいても快適なキャストフィールを実現。 / また、高密度カーボンコンポジットマテリアルによる高感度ノブを搭載し、軽量かつ高感度にセッティング。 / 手返しの良さと水中の解像度を高めた「スピーディー」なバーサタイルモデルです。</v>
       </c>
       <c r="N16" t="str">
-        <v/>
+        <v>¥38,500</v>
       </c>
       <c r="O16" t="str">
-        <v/>
+        <v>在售</v>
+      </c>
+      <c r="P16" t="str">
+        <v>7.2：1のハイギア・バーサタイルモデルLauda72。 超々ジュラルミン製軽量SVスプールのなめらかな初動により、低弾道で伸びのあるピッチングが可能。高次元のショートディスタンスゲームにはもちろん、強風下のロングキャストにおいても快適なキャストフィールを実現。 また、高密度カーボンコンポジットマテリアルによる高感度ノブを搭載し、軽量かつ高感度にセッティング。 手返しの良さと水中の解像度を高めた「スピーディー」なバーサタイルモデルです。 The LAUDA 72 is a 7.2:1 high-speed model designed for versatility and performance. Extremely smooth start-up inertia of ultra-lightweight duralumin SV Spool allows for effortless long-distance pitching, and silky long-distance casts even against headwinds. Equipped with high sensitivity carbon composite knobs to maximize contact feel, a race-inspired clear side plate, and that distinctive Megabass fit and finish. ※The photograph is a prototype.</v>
+      </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
+      <c r="R16" t="str">
+        <v>全能快节奏鲈鱼</v>
+      </c>
+      <c r="S16" t="str">
+        <v>7.2 高速比 / 远投与短打兼顾 / 高感度设定</v>
       </c>
     </row>
     <row r="17">
@@ -1164,7 +1356,7 @@
         <v>LAUDA72 LIMITED EDITION</v>
       </c>
       <c r="D17" t="str">
-        <v>LAUDA72 LIMITED EDITION</v>
+        <v/>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1182,22 +1374,34 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/LAUDA72%20LIMITED%20EDITION_main.jpg</v>
       </c>
       <c r="J17" t="str">
-        <v>2026-04-09T16:03:10.384Z</v>
+        <v>2026-04-21T12:03:03.499Z</v>
       </c>
       <c r="K17" t="str">
-        <v>2026-04-09T16:03:10.384Z</v>
+        <v>2026-04-21T12:03:03.499Z</v>
       </c>
       <c r="L17" t="str">
-        <v/>
+        <v>限量高速泛用</v>
       </c>
       <c r="M17" t="str">
-        <v/>
+        <v>特別なアングラーに向けて開発された限定生産のリミテッドエディション。超軽量80mmカーボンハンドルを標準装備した上で、細部に渡るトータルウェイトバランシングを煮詰めたスペシャルモデルです。 / ギアハウジングには３層コートによる特殊ペイント、「富士レーシングホワイト」を大胆にあしらっています。 / The LAUDA 72 Limited Edition is inspired by the legendary Fuji Speedway in nearby Oyama, featuring a gear housing side-cover finished in three coats of the iconic Fuji Racing White. / In addition, this limited edition is equipped with a custom 80mm carbon fiber handle, reducing off-axis weight to improve the reel’s overall performance.</v>
       </c>
       <c r="N17" t="str">
-        <v/>
+        <v>¥42,500</v>
       </c>
       <c r="O17" t="str">
-        <v/>
+        <v>在售</v>
+      </c>
+      <c r="P17" t="str">
+        <v>特別なアングラーに向けて開発された限定生産のリミテッドエディション。超軽量80mmカーボンハンドルを標準装備した上で、細部に渡るトータルウェイトバランシングを煮詰めたスペシャルモデルです。 ギアハウジングには３層コートによる特殊ペイント、「富士レーシングホワイト」を大胆にあしらっています。 The LAUDA 72 Limited Edition is inspired by the legendary Fuji Speedway in nearby Oyama, featuring a gear housing side-cover finished in three coats of the iconic Fuji Racing White. In addition, this limited edition is equipped with a custom 80mm carbon fiber handle, reducing off-axis weight to improve the reel’s overall performance. ※The photograph is a prototype.</v>
+      </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
+      <c r="R17" t="str">
+        <v>高端轻量收藏实战</v>
+      </c>
+      <c r="S17" t="str">
+        <v>限量版本 / 80mm 碳手柄 / 轻量高感度</v>
       </c>
     </row>
     <row r="18">
@@ -1211,7 +1415,7 @@
         <v>IP79</v>
       </c>
       <c r="D18" t="str">
-        <v>IP79</v>
+        <v/>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1229,22 +1433,34 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/IP79_main.jpg</v>
       </c>
       <c r="J18" t="str">
-        <v>2026-04-09T16:03:10.796Z</v>
+        <v>2026-04-21T12:03:04.131Z</v>
       </c>
       <c r="K18" t="str">
-        <v>2026-04-09T16:03:10.796Z</v>
+        <v>2026-04-21T12:03:04.131Z</v>
       </c>
       <c r="L18" t="str">
-        <v/>
+        <v>高功率主力</v>
       </c>
       <c r="M18" t="str">
-        <v/>
+        <v>ストイックなリアルアングラーに絶賛の、IS（インターセプティング・スピーダー）シリーズに対し、パワープレイングゲームに対応しながら「快適な巻き上げトルク」を実現すべくスペックアップを施したスペシャルリールが、IP（インターセプティング・パワーズ）シリーズです。クランクベイトのハイピッチリトリーブ、ジグのマシンガンショットを実現する7.9のハイギアリールでありながら、「巻き重り」疲労感を軽減化。100mmにおよぶロング・パワーハンドルと、超軽量・超々ジュラルミンを大胆にも使用した「大口径ナロースプール」が、強大なトルクを発揮。軽量ルアーのフルキャストにおけるバックラッシュをとことん低減化させるために開発された「マグネットブレーキユニット」と、その絶妙な調律は、プロガイドたちを唸らせた至高のセッティング。高剛性・高剛性のフルメタル ハウジングボディ（※サイドプレートを除く）に密かに封じ込めた新感覚スペックが、快適なハイスピード・ハイパワープレイングゲームを実現させています。 / In contrast to the IS(Intercepting Speeder) series, popular with reserved, practical anglers, the IP(Intercepting Power) series has been improved with increased winding torque, allowing it to excel during high power struggles with big fish. The high 7.9 gear ratio allows for speedy crank bait retrieves and machine gun shots with jigs while alleviating much of the fatigue from use. The newly designed 100mm long power handle and uniquely designed large diameter narrow spool, which uses ample amounts of lightweight super duralumin, generate massive amounts of torque. To reduce the backlash from the full power casting of lightweight lures, an improved magnetic braking unit has been incorporated and tuned to the settings demanded by our exacting Pro Guides. The new performance contained in this high rigidity full metal housing(*not including the side plate) will help you realize comfortable high speed and high power games.</v>
       </c>
       <c r="N18" t="str">
-        <v/>
+        <v>¥45,000</v>
       </c>
       <c r="O18" t="str">
-        <v/>
+        <v>在售</v>
+      </c>
+      <c r="P18" t="str">
+        <v>ストイックなリアルアングラーに絶賛の、IS（インターセプティング・スピーダー）シリーズに対し、パワープレイングゲームに対応しながら「快適な巻き上げトルク」を実現すべくスペックアップを施したスペシャルリールが、IP（インターセプティング・パワーズ）シリーズです。クランクベイトのハイピッチリトリーブ、ジグのマシンガンショットを実現する7.9のハイギアリールでありながら、「巻き重り」疲労感を軽減化。100mmにおよぶロング・パワーハンドルと、超軽量・超々ジュラルミンを大胆にも使用した「大口径ナロースプール」が、強大なトルクを発揮。軽量ルアーのフルキャストにおけるバックラッシュをとことん低減化させるために開発された「マグネットブレーキユニット」と、その絶妙な調律は、プロガイドたちを唸らせた至高のセッティング。高剛性・高剛性のフルメタル ハウジングボディ（※サイドプレートを除く）に密かに封じ込めた新感覚スペックが、快適なハイスピード・ハイパワープレイングゲームを実現させています。 In contrast to the IS(Intercepting Speeder) series, popular with reserved, practical anglers, the IP(Intercepting Power) series has been improved with increased winding torque, allowing it to excel during high power struggles with big fish. The high 7.9 gear ratio allows for speedy crank bait retrieves and machine gun shots with jigs while alleviating much of the fatigue from use. The newly designed 100mm long power handle and uniquely designed large diameter narrow spool, which uses ample amounts of lightweight super duralumin, generate massive amounts of torque. To reduce the backlash from the full power casting of lightweight lures, an improved magnetic braking unit has been incorporated and tuned to the settings demanded by our exacting Pro Guides. The new performance contained in this high rigidity full metal housing(*not including the side plate) will help you realize comfortable high speed and high power games.</v>
+      </c>
+      <c r="Q18" t="str">
+        <v/>
+      </c>
+      <c r="R18" t="str">
+        <v>Power Fishing 主力</v>
+      </c>
+      <c r="S18" t="str">
+        <v>大口径窄线杯 / 强扭矩 / 快节奏 power game</v>
       </c>
     </row>
     <row r="19">
@@ -1258,7 +1474,7 @@
         <v>IP68</v>
       </c>
       <c r="D19" t="str">
-        <v>IP68</v>
+        <v/>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1276,34 +1492,46 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/IP68_main.jpg</v>
       </c>
       <c r="J19" t="str">
-        <v>2026-04-09T16:03:11.194Z</v>
+        <v>2026-04-21T12:03:04.627Z</v>
       </c>
       <c r="K19" t="str">
-        <v>2026-04-09T16:03:11.194Z</v>
+        <v>2026-04-21T12:03:04.627Z</v>
       </c>
       <c r="L19" t="str">
-        <v/>
+        <v>高功率主力</v>
       </c>
       <c r="M19" t="str">
-        <v/>
+        <v>デビューと同時に全国のビッグゲーマーをまたたく間に虜にしてしまったIPシリーズに、待望の6.8:1ギアモデルが登場。ド級のウルトラトルクがカヴァーモンスターをヘヴィカヴァーから引き剥がし、ウィードカットやハングオフカットを多用するカヴァークランキングで快適性能を発揮。マットカヴァーのフロッグゲームやスピナーベイティングなど、手返しと巻き上げパワーを両立させたい場面でストレスフリーなパワープレイングゲームを実現します。 / At the same time that the L/R debuted, the IP series also captivated the hearts of big-time anglers from around the country. Now a much anticipated 6:8 gear ratio model is added to the lineup. The ultra high torque pulls monsters out of cover and rips through weeds, making this the perfect reel for cover cranking. Whether attacking cover with frogs or spinner baits, this reel will give you the power you require to make stress-free power fishing a reality.</v>
       </c>
       <c r="N19" t="str">
-        <v/>
+        <v>¥45,000</v>
       </c>
       <c r="O19" t="str">
-        <v/>
+        <v>在售</v>
+      </c>
+      <c r="P19" t="str">
+        <v>デビューと同時に全国のビッグゲーマーをまたたく間に虜にしてしまったIPシリーズに、待望の6.8:1ギアモデルが登場。ド級のウルトラトルクがカヴァーモンスターをヘヴィカヴァーから引き剥がし、ウィードカットやハングオフカットを多用するカヴァークランキングで快適性能を発揮。マットカヴァーのフロッグゲームやスピナーベイティングなど、手返しと巻き上げパワーを両立させたい場面でストレスフリーなパワープレイングゲームを実現します。 At the same time that the L/R debuted, the IP series also captivated the hearts of big-time anglers from around the country. Now a much anticipated 6:8 gear ratio model is added to the lineup. The ultra high torque pulls monsters out of cover and rips through weeds, making this the perfect reel for cover cranking. Whether attacking cover with frogs or spinner baits, this reel will give you the power you require to make stress-free power fishing a reality.</v>
+      </c>
+      <c r="Q19" t="str">
+        <v/>
+      </c>
+      <c r="R19" t="str">
+        <v>Power Fishing 扭矩取向</v>
+      </c>
+      <c r="S19" t="str">
+        <v>6.8 低一档速度 / 更强卷阻承受 / Cover 与 power bait 友好</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S19"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AS3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1331,70 +1559,115 @@
         <v>spool_diameter_per_turn_mm</v>
       </c>
       <c r="I1" t="str">
+        <v>spool_diameter_mm</v>
+      </c>
+      <c r="J1" t="str">
         <v>Nylon_no_m</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>Nylon_lb_m</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>fluorocarbon_no_m</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>fluorocarbon_lb_m</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>pe_no_m</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>cm_per_turn</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>handle_length_mm</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>bearing_count_roller</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
+        <v>body_material</v>
+      </c>
+      <c r="S1" t="str">
+        <v>body_material_tech</v>
+      </c>
+      <c r="T1" t="str">
+        <v>gear_material</v>
+      </c>
+      <c r="U1" t="str">
+        <v>handle_knob_type</v>
+      </c>
+      <c r="V1" t="str">
+        <v>official_environment</v>
+      </c>
+      <c r="W1" t="str">
+        <v>line_capacity_display</v>
+      </c>
+      <c r="X1" t="str">
         <v>market_reference_price</v>
       </c>
-      <c r="R1" t="str">
+      <c r="Y1" t="str">
         <v>product_code</v>
       </c>
-      <c r="S1" t="str">
+      <c r="Z1" t="str">
         <v>created_at</v>
       </c>
-      <c r="T1" t="str">
+      <c r="AA1" t="str">
         <v>updated_at</v>
       </c>
-      <c r="U1" t="str">
+      <c r="AB1" t="str">
         <v>drag_click</v>
       </c>
-      <c r="V1" t="str">
+      <c r="AC1" t="str">
         <v>spool_depth_normalized</v>
       </c>
-      <c r="W1" t="str">
+      <c r="AD1" t="str">
         <v>gear_ratio_normalized</v>
       </c>
-      <c r="X1" t="str">
+      <c r="AE1" t="str">
         <v>brake_type_normalized</v>
       </c>
-      <c r="Y1" t="str">
+      <c r="AF1" t="str">
         <v>fit_style_tags</v>
       </c>
-      <c r="Z1" t="str">
+      <c r="AG1" t="str">
         <v>min_lure_weight_hint</v>
       </c>
-      <c r="AA1" t="str">
+      <c r="AH1" t="str">
         <v>is_compact_body</v>
       </c>
-      <c r="AB1" t="str">
+      <c r="AI1" t="str">
         <v>handle_style</v>
       </c>
-      <c r="AC1" t="str">
+      <c r="AJ1" t="str">
         <v>MAX_DURABILITY</v>
       </c>
-      <c r="AD1" t="str">
+      <c r="AK1" t="str">
         <v>type</v>
+      </c>
+      <c r="AL1" t="str">
+        <v>is_sw_edition</v>
+      </c>
+      <c r="AM1" t="str">
+        <v>variant_description</v>
+      </c>
+      <c r="AN1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="AO1" t="str">
+        <v>player_environment</v>
+      </c>
+      <c r="AP1" t="str">
+        <v>is_handle_double</v>
+      </c>
+      <c r="AQ1" t="str">
+        <v>EV_link</v>
+      </c>
+      <c r="AR1" t="str">
+        <v>Specs_link</v>
+      </c>
+      <c r="AS1" t="str">
+        <v>spool_weight_g</v>
       </c>
     </row>
     <row r="2">
@@ -1408,7 +1681,7 @@
         <v>GAUS 20X</v>
       </c>
       <c r="D2" t="str">
-        <v>4.8:1</v>
+        <v>4.8</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -1426,10 +1699,10 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>3lb./140m , 4lb./100m</v>
+        <v/>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>3lb./140m / 4lb./100m</v>
       </c>
       <c r="L2" t="str">
         <v/>
@@ -1438,28 +1711,100 @@
         <v/>
       </c>
       <c r="N2" t="str">
-        <v>63cm</v>
+        <v/>
       </c>
       <c r="O2" t="str">
-        <v/>
+        <v>63</v>
       </c>
       <c r="P2" t="str">
-        <v>6BB,1RB</v>
+        <v/>
       </c>
       <c r="Q2" t="str">
-        <v>38000</v>
+        <v>6/1</v>
       </c>
       <c r="R2" t="str">
-        <v/>
+        <v>高密度碳纤复合</v>
       </c>
       <c r="S2" t="str">
-        <v>2026-04-09T16:03:04.387Z</v>
+        <v>磁性流体密封 / X-GRAPHITE 复合转子</v>
       </c>
       <c r="T2" t="str">
-        <v>2026-04-09T16:03:04.387Z</v>
+        <v/>
+      </c>
+      <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="str">
+        <v>淡水路亚</v>
+      </c>
+      <c r="W2" t="str">
+        <v/>
+      </c>
+      <c r="X2" t="str">
+        <v>¥38,000</v>
+      </c>
+      <c r="Y2" t="str">
+        <v/>
+      </c>
+      <c r="Z2" t="str">
+        <v>2026-04-21T12:02:54.928Z</v>
+      </c>
+      <c r="AA2" t="str">
+        <v>2026-04-21T12:02:54.928Z</v>
+      </c>
+      <c r="AB2" t="str">
+        <v/>
+      </c>
+      <c r="AC2" t="str">
+        <v/>
       </c>
       <c r="AD2" t="str">
+        <v/>
+      </c>
+      <c r="AE2" t="str">
+        <v/>
+      </c>
+      <c r="AF2" t="str">
+        <v>溪流,精细,轻量</v>
+      </c>
+      <c r="AG2" t="str">
+        <v>约 2g+</v>
+      </c>
+      <c r="AH2" t="str">
+        <v/>
+      </c>
+      <c r="AI2" t="str">
+        <v>单摇臂</v>
+      </c>
+      <c r="AJ2" t="str">
+        <v/>
+      </c>
+      <c r="AK2" t="str">
         <v>spinning</v>
+      </c>
+      <c r="AL2" t="str">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="str">
+        <v/>
+      </c>
+      <c r="AN2" t="str">
+        <v>その名のとおり、あらゆるものを引き付けてしまう魔性を発揮する、スーパーコンパクトリールが、ついにベールを脱ぎました。 ガウスは、見た目のコンパクトな風貌からは想像できない強靭さと、これまでの基準を覆すハイパワーをスモールボディで発揮する、新世代のスピニングマシンとして開発されています。LIN258HMで高い評価を得た「磁性流体シールドシステム」を、そのコンパクトボディに搭載。大切なギアユニット内部をクリーンな状態に保つだけでなく、ボディとローターは実質無接点のため、シルキーな回転性能が長期間持続。羽の軽さとも評される「X-GRAPHITE COMPSITEROTER」は、スピニングリールにおける回転レスポンスを格段に引き上げると同時に、感度感知にも貢献。また、ハイパワーゲームにおいてローターの変形を抑えるため、ビッグフィッシュのファイトによる負荷をローター全体に分散するために開発した。「高密度カーボンコンポジットボディ」は、恐るべき軽さを実現しただけでなく、ついにその剛性は、マグネシウムを上回るレベルへと昇華。モンスターフィッシュとのドッグファイトでも、ボディのタワミがないから、ギア間が正確に噛み合うシルキーな回転性能と、それらが相まって生み出すトルクフルな巻き上げ性能が確実に維持されます。すべてが、いままでのスピニングリールの基準を覆すオーバースペックリール、GAUSが、いよいよスピニング新時代への扉を開きます。 The "High Metal Honeycomb Spool" embodies the ultimate in robust and lightweight construction, made possible with Megabass' original carved metal manufacturing process. With the development of the "Magnetic Fluid Shield System," it creates the ideal head balance for spinning reels. The unlikely power generated from the super lightweight micro body gives it the extreme specs needed to combat record breaking fish with the ultimate finesse approach. The perpendicular 45mm crank handle excels at maintaining a steady and constant high speed retrieve with just a slight snapping motion of the wrist. This small superstar displays great ease of use with fast paced finesse rigs and light plugging in streams. もはやこれ以上はない堅牢さと軽量化を高次元で両立させた、メガバス独自のメタル削り出し構造による「ハイメタル・ハニカムスプール」は、「磁性流体シールドシステム」の開発によって、スピニングリールにおける理想的なヘッドバランスを実現。その超軽量マイクロボディが発揮してしまう、およそ似合わないハイパワーは、究極のフィネスアプローチでレコードフィッシュと真っ向からわたり合うためのエクストリームなスペック。45mmの垂直クランクハンドルは、手首のわずかなスナップモーションで、ブレなく一定スピードを保持した高速リーリングに最適。フィネスリグの素早いピックアップや、ストリームにおけるライトプラッギングで至極の快適性能を発揮する、小さな超新星です。</v>
+      </c>
+      <c r="AO2" t="str">
+        <v>溪流 / 轻量精细</v>
+      </c>
+      <c r="AP2" t="str">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="str">
+        <v/>
+      </c>
+      <c r="AR2" t="str">
+        <v/>
+      </c>
+      <c r="AS2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -1473,7 +1818,7 @@
         <v>GAUS 30X</v>
       </c>
       <c r="D3" t="str">
-        <v>4.7:1</v>
+        <v>4.7</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -1491,10 +1836,10 @@
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>10lb./195m , 12lb./150m</v>
+        <v/>
       </c>
       <c r="K3" t="str">
-        <v/>
+        <v>10lb./195m / 12lb./150m</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -1503,40 +1848,112 @@
         <v/>
       </c>
       <c r="N3" t="str">
-        <v>79cm</v>
+        <v/>
       </c>
       <c r="O3" t="str">
-        <v/>
+        <v>79</v>
       </c>
       <c r="P3" t="str">
-        <v>6BB , 1RB</v>
+        <v/>
       </c>
       <c r="Q3" t="str">
-        <v>44000</v>
+        <v>6/1</v>
       </c>
       <c r="R3" t="str">
-        <v/>
+        <v>高密度碳纤复合</v>
       </c>
       <c r="S3" t="str">
-        <v>2026-04-09T16:03:04.751Z</v>
+        <v>磁性流体密封 / 高扭矩小机身</v>
       </c>
       <c r="T3" t="str">
-        <v>2026-04-09T16:03:04.751Z</v>
+        <v/>
+      </c>
+      <c r="U3" t="str">
+        <v/>
+      </c>
+      <c r="V3" t="str">
+        <v>淡海水泛用</v>
+      </c>
+      <c r="W3" t="str">
+        <v/>
+      </c>
+      <c r="X3" t="str">
+        <v>¥44,000</v>
+      </c>
+      <c r="Y3" t="str">
+        <v/>
+      </c>
+      <c r="Z3" t="str">
+        <v>2026-04-21T12:02:55.416Z</v>
+      </c>
+      <c r="AA3" t="str">
+        <v>2026-04-21T12:02:55.416Z</v>
+      </c>
+      <c r="AB3" t="str">
+        <v/>
+      </c>
+      <c r="AC3" t="str">
+        <v/>
       </c>
       <c r="AD3" t="str">
+        <v/>
+      </c>
+      <c r="AE3" t="str">
+        <v/>
+      </c>
+      <c r="AF3" t="str">
+        <v>轻盐,快收,泛用</v>
+      </c>
+      <c r="AG3" t="str">
+        <v>约 5g+</v>
+      </c>
+      <c r="AH3" t="str">
+        <v/>
+      </c>
+      <c r="AI3" t="str">
+        <v>单摇臂</v>
+      </c>
+      <c r="AJ3" t="str">
+        <v/>
+      </c>
+      <c r="AK3" t="str">
         <v>spinning</v>
+      </c>
+      <c r="AL3" t="str">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="str">
+        <v/>
+      </c>
+      <c r="AN3" t="str">
+        <v>その名のとおり、あらゆるものを引き付けてしまう魔性を発揮する、スーパーコンパクトリールが、ついにベールを脱ぎました。 ガウスは、見た目のコンパクトな風貌からは想像できない強靭さと、これまでの基準を覆すハイパワーをスモールボディで発揮する、新世代のスピニングマシンとして開発されています。LIN258HMで高い評価を得た「磁性流体シールドシステム」を、そのコンパクトボディに搭載。大切なギアユニット内部をクリーンな状態に保つだけでなく、ボディとローターは実質無接点のため、シルキーな回転性能が長期間持続。羽の軽さとも評される「X-GRAPHITE COMPSITEROTER」は、スピニングリールにおける回転レスポンスを格段に引き上げると同時に、感度感知にも貢献。また、ハイパワーゲームにおいてローターの変形を抑えるため、ビッグフィッシュのファイトによる負荷をローター全体に分散するために開発した。「高密度カーボンコンポジットボディ」は、恐るべき軽さを実現しただけでなく、ついにその剛性は、マグネシウムを上回るレベルへと昇華。モンスターフィッシュとのドッグファイトでも、ボディのタワミがないから、ギア間が正確に噛み合うシルキーな回転性能と、それらが相まって生み出すトルクフルな巻き上げ性能が確実に維持されます。すべてが、いままでのスピニングリールの基準を覆すオーバースペックリール、GAUSが、いよいよスピニング新時代への扉を開きます。 The GAUS30X is a model tuned for active salt water games. The GAUS's solid high rigidity body and instantaneous torque generation will handle big fish with ease. Megabass' unique "Super Lightweight Carbon Hybrid Spool" reduces spool deflection by spreading out the massive weight loads that can occur during heavy line use. The GAUS is equipped with many cutting edge technologies and features to give it the edge in high power games, such as the magnetic fluid system, the powerful 55m machine cut handle, the design that allows for smooth initial rotation and control, the M Drag System, the high power gear system, etc. Once you use it, you won't be able to put it down. That's the power of the GAUS. ガウス30Xは、シーバスゲームをはじめ、アクティブなソルトゲームにアジャストするモデルです。ガウスが身につけた圧倒的な高剛性ボディと、瞬時に太いトルクを立ち上げるシルキードライブフィールがビッグフィッシュゲームを快適にこなします。メガバス独自の「超軽量カーボン・ハイブリットスプール」は、太いラインにかかる多大な負荷がもたらすスプールのたわみや高荷重を分散して低減化。磁性流体システム、55mmの強靭なマシンカットハンドル、緻密に計算されたスムースな滑り出しとその制御について、徹底追及されたＭドラグシステム、ハイパワーギアシステムなどなど・・数え上げたらキリがありませんが、スピニングリールにおける新次元のハイパワーゲームは、ガウスが武装した最新テクノロジーによって、ついに具現化。一度お使いいただくと、手放せなくなる快適性能こそが、ガウスの魔力を物語ります。</v>
+      </c>
+      <c r="AO3" t="str">
+        <v>轻盐 / 近海轻中型</v>
+      </c>
+      <c r="AP3" t="str">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="str">
+        <v/>
+      </c>
+      <c r="AR3" t="str">
+        <v/>
+      </c>
+      <c r="AS3" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AD3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AS3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AN17"/>
+  <dimension ref="A1:AU17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1597,67 +2014,88 @@
         <v>spool_width_mm</v>
       </c>
       <c r="T1" t="str">
+        <v>spool_weight_g</v>
+      </c>
+      <c r="U1" t="str">
         <v>handle_knob_type</v>
       </c>
-      <c r="U1" t="str">
+      <c r="V1" t="str">
         <v>handle_knob_exchange_size</v>
       </c>
-      <c r="V1" t="str">
+      <c r="W1" t="str">
         <v>body_material</v>
       </c>
-      <c r="W1" t="str">
+      <c r="X1" t="str">
+        <v>body_material_tech</v>
+      </c>
+      <c r="Y1" t="str">
         <v>gear_material</v>
       </c>
-      <c r="X1" t="str">
+      <c r="Z1" t="str">
         <v>battery_capacity</v>
       </c>
-      <c r="Y1" t="str">
+      <c r="AA1" t="str">
         <v>battery_charge_time</v>
       </c>
-      <c r="Z1" t="str">
+      <c r="AB1" t="str">
         <v>continuous_cast_count</v>
       </c>
-      <c r="AA1" t="str">
+      <c r="AC1" t="str">
         <v>usage_environment</v>
       </c>
-      <c r="AB1" t="str">
+      <c r="AD1" t="str">
         <v>DRAG</v>
       </c>
-      <c r="AC1" t="str">
+      <c r="AE1" t="str">
         <v>Nylon_no_m</v>
       </c>
-      <c r="AD1" t="str">
+      <c r="AF1" t="str">
         <v>fluorocarbon_no_m</v>
       </c>
-      <c r="AE1" t="str">
+      <c r="AG1" t="str">
         <v>drag_click</v>
       </c>
-      <c r="AF1" t="str">
+      <c r="AH1" t="str">
         <v>spool_depth_normalized</v>
       </c>
-      <c r="AG1" t="str">
+      <c r="AI1" t="str">
         <v>gear_ratio_normalized</v>
       </c>
-      <c r="AH1" t="str">
+      <c r="AJ1" t="str">
         <v>brake_type_normalized</v>
       </c>
-      <c r="AI1" t="str">
+      <c r="AK1" t="str">
         <v>fit_style_tags</v>
       </c>
-      <c r="AJ1" t="str">
+      <c r="AL1" t="str">
         <v>min_lure_weight_hint</v>
       </c>
-      <c r="AK1" t="str">
+      <c r="AM1" t="str">
         <v>is_compact_body</v>
       </c>
-      <c r="AL1" t="str">
+      <c r="AN1" t="str">
         <v>handle_style</v>
       </c>
-      <c r="AM1" t="str">
+      <c r="AO1" t="str">
         <v>MAX_DURABILITY</v>
       </c>
-      <c r="AN1" t="str">
+      <c r="AP1" t="str">
         <v>type</v>
+      </c>
+      <c r="AQ1" t="str">
+        <v>official_environment</v>
+      </c>
+      <c r="AR1" t="str">
+        <v>player_environment</v>
+      </c>
+      <c r="AS1" t="str">
+        <v>is_handle_double</v>
+      </c>
+      <c r="AT1" t="str">
+        <v>is_sw_edition</v>
+      </c>
+      <c r="AU1" t="str">
+        <v>line_capacity_display</v>
       </c>
     </row>
     <row r="2">
@@ -1671,19 +2109,19 @@
         <v>LIN258HM</v>
       </c>
       <c r="D2" t="str">
-        <v>6.0:1</v>
+        <v>6.0</v>
       </c>
       <c r="E2" t="str">
         <v>7.0</v>
       </c>
       <c r="F2" t="str">
-        <v>8.8oz.(248)</v>
+        <v>248</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>6lb./210m, 8lb/150m</v>
+        <v>6lb./210m / 8lb/150m</v>
       </c>
       <c r="I2" t="str">
         <v/>
@@ -1692,25 +2130,25 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>34.7in(91cm)</v>
+        <v>91</v>
       </c>
       <c r="L2" t="str">
         <v/>
       </c>
       <c r="M2" t="str">
-        <v>12BB / 1RB</v>
+        <v>12/1</v>
       </c>
       <c r="N2" t="str">
-        <v>55000</v>
+        <v>¥55,000</v>
       </c>
       <c r="O2" t="str">
         <v/>
       </c>
       <c r="P2" t="str">
-        <v>2026-04-09T16:03:05.113Z</v>
+        <v>2026-04-21T12:02:55.901Z</v>
       </c>
       <c r="Q2" t="str">
-        <v>2026-04-09T16:03:05.113Z</v>
+        <v>2026-04-21T12:02:55.901Z</v>
       </c>
       <c r="R2" t="str">
         <v/>
@@ -1718,8 +2156,89 @@
       <c r="S2" t="str">
         <v/>
       </c>
+      <c r="T2" t="str">
+        <v/>
+      </c>
+      <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="str">
+        <v/>
+      </c>
+      <c r="W2" t="str">
+        <v>铝</v>
+      </c>
+      <c r="X2" t="str">
+        <v>高精度金属机身 / 磁性流体密封</v>
+      </c>
+      <c r="Y2" t="str">
+        <v/>
+      </c>
+      <c r="Z2" t="str">
+        <v/>
+      </c>
+      <c r="AA2" t="str">
+        <v/>
+      </c>
+      <c r="AB2" t="str">
+        <v/>
+      </c>
+      <c r="AC2" t="str">
+        <v/>
+      </c>
+      <c r="AD2" t="str">
+        <v/>
+      </c>
+      <c r="AE2" t="str">
+        <v/>
+      </c>
+      <c r="AF2" t="str">
+        <v/>
+      </c>
+      <c r="AG2" t="str">
+        <v/>
+      </c>
+      <c r="AH2" t="str">
+        <v/>
+      </c>
+      <c r="AI2" t="str">
+        <v/>
+      </c>
+      <c r="AJ2" t="str">
+        <v/>
+      </c>
+      <c r="AK2" t="str">
+        <v>重装,高刚性,精细</v>
+      </c>
+      <c r="AL2" t="str">
+        <v>约 3g+</v>
+      </c>
+      <c r="AM2" t="str">
+        <v/>
+      </c>
       <c r="AN2" t="str">
+        <v>单摇臂</v>
+      </c>
+      <c r="AO2" t="str">
+        <v/>
+      </c>
+      <c r="AP2" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AQ2" t="str">
+        <v>淡水路亚</v>
+      </c>
+      <c r="AR2" t="str">
+        <v>Cover / 精细重装</v>
+      </c>
+      <c r="AS2" t="str">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -1733,7 +2252,7 @@
         <v>RC-IDATEN 256</v>
       </c>
       <c r="D3" t="str">
-        <v>5.66:1</v>
+        <v>5.66</v>
       </c>
       <c r="E3" t="str">
         <v>3.0</v>
@@ -1745,7 +2264,7 @@
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>4lb./190m, 5lb/150m</v>
+        <v>4lb./190m / 5lb/150m</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -1754,25 +2273,25 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>84cm</v>
+        <v>84</v>
       </c>
       <c r="L3" t="str">
         <v/>
       </c>
       <c r="M3" t="str">
-        <v>7BB / 1RB</v>
+        <v>7/1</v>
       </c>
       <c r="N3" t="str">
-        <v>59800</v>
+        <v>¥59,800</v>
       </c>
       <c r="O3" t="str">
         <v/>
       </c>
       <c r="P3" t="str">
-        <v>2026-04-09T16:03:05.419Z</v>
+        <v>2026-04-21T12:02:56.380Z</v>
       </c>
       <c r="Q3" t="str">
-        <v>2026-04-09T16:03:05.419Z</v>
+        <v>2026-04-21T12:02:56.380Z</v>
       </c>
       <c r="R3" t="str">
         <v/>
@@ -1780,8 +2299,89 @@
       <c r="S3" t="str">
         <v/>
       </c>
+      <c r="T3" t="str">
+        <v/>
+      </c>
+      <c r="U3" t="str">
+        <v/>
+      </c>
+      <c r="V3" t="str">
+        <v/>
+      </c>
+      <c r="W3" t="str">
+        <v>铝</v>
+      </c>
+      <c r="X3" t="str">
+        <v>高速回收平台</v>
+      </c>
+      <c r="Y3" t="str">
+        <v/>
+      </c>
+      <c r="Z3" t="str">
+        <v/>
+      </c>
+      <c r="AA3" t="str">
+        <v/>
+      </c>
+      <c r="AB3" t="str">
+        <v/>
+      </c>
+      <c r="AC3" t="str">
+        <v/>
+      </c>
+      <c r="AD3" t="str">
+        <v/>
+      </c>
+      <c r="AE3" t="str">
+        <v/>
+      </c>
+      <c r="AF3" t="str">
+        <v/>
+      </c>
+      <c r="AG3" t="str">
+        <v/>
+      </c>
+      <c r="AH3" t="str">
+        <v/>
+      </c>
+      <c r="AI3" t="str">
+        <v/>
+      </c>
+      <c r="AJ3" t="str">
+        <v/>
+      </c>
+      <c r="AK3" t="str">
+        <v>高速,精细,泛用</v>
+      </c>
+      <c r="AL3" t="str">
+        <v>约 2g+</v>
+      </c>
+      <c r="AM3" t="str">
+        <v/>
+      </c>
       <c r="AN3" t="str">
+        <v>单摇臂</v>
+      </c>
+      <c r="AO3" t="str">
+        <v/>
+      </c>
+      <c r="AP3" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AQ3" t="str">
+        <v>淡水路亚</v>
+      </c>
+      <c r="AR3" t="str">
+        <v>快节奏精细</v>
+      </c>
+      <c r="AS3" t="str">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -1795,7 +2395,7 @@
         <v>MONOBLOCK SPECIALE GRIGIO STONE</v>
       </c>
       <c r="D4" t="str">
-        <v>6.8:1</v>
+        <v>6.8</v>
       </c>
       <c r="E4" t="str">
         <v>4.0</v>
@@ -1807,7 +2407,7 @@
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>14lb./120m , 16lb./105m</v>
+        <v>14lb./120m / 16lb./105m</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -1816,25 +2416,25 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>72cm</v>
+        <v>72</v>
       </c>
       <c r="L4" t="str">
         <v/>
       </c>
       <c r="M4" t="str">
-        <v>10BB , 1RB</v>
+        <v>10/1</v>
       </c>
       <c r="N4" t="str">
-        <v>92500</v>
+        <v>¥92,500</v>
       </c>
       <c r="O4" t="str">
         <v/>
       </c>
       <c r="P4" t="str">
-        <v>2026-04-09T16:03:05.733Z</v>
+        <v>2026-04-21T12:02:57.077Z</v>
       </c>
       <c r="Q4" t="str">
-        <v>2026-04-09T16:03:05.733Z</v>
+        <v>2026-04-21T12:02:57.077Z</v>
       </c>
       <c r="R4" t="str">
         <v/>
@@ -1842,8 +2442,89 @@
       <c r="S4" t="str">
         <v/>
       </c>
+      <c r="T4" t="str">
+        <v/>
+      </c>
+      <c r="U4" t="str">
+        <v/>
+      </c>
+      <c r="V4" t="str">
+        <v>L/R</v>
+      </c>
+      <c r="W4" t="str">
+        <v>铝</v>
+      </c>
+      <c r="X4" t="str">
+        <v>Monoblock 进化平台</v>
+      </c>
+      <c r="Y4" t="str">
+        <v/>
+      </c>
+      <c r="Z4" t="str">
+        <v/>
+      </c>
+      <c r="AA4" t="str">
+        <v/>
+      </c>
+      <c r="AB4" t="str">
+        <v/>
+      </c>
+      <c r="AC4" t="str">
+        <v/>
+      </c>
+      <c r="AD4" t="str">
+        <v/>
+      </c>
+      <c r="AE4" t="str">
+        <v/>
+      </c>
+      <c r="AF4" t="str">
+        <v/>
+      </c>
+      <c r="AG4" t="str">
+        <v/>
+      </c>
+      <c r="AH4" t="str">
+        <v/>
+      </c>
+      <c r="AI4" t="str">
+        <v/>
+      </c>
+      <c r="AJ4" t="str">
+        <v/>
+      </c>
+      <c r="AK4" t="str">
+        <v>复古,收藏,顶水</v>
+      </c>
+      <c r="AL4" t="str">
+        <v>约 7g+</v>
+      </c>
+      <c r="AM4" t="str">
+        <v/>
+      </c>
       <c r="AN4" t="str">
+        <v>单摇臂</v>
+      </c>
+      <c r="AO4" t="str">
+        <v/>
+      </c>
+      <c r="AP4" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AQ4" t="str">
+        <v>淡水路亚</v>
+      </c>
+      <c r="AR4" t="str">
+        <v>顶水 / 收藏</v>
+      </c>
+      <c r="AS4" t="str">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -1857,7 +2538,7 @@
         <v>MONOBLOCK SPECIALE ITO-GAMBLER</v>
       </c>
       <c r="D5" t="str">
-        <v>6.8:1</v>
+        <v>6.8</v>
       </c>
       <c r="E5" t="str">
         <v>4.0</v>
@@ -1869,7 +2550,7 @@
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>14lb./120m , 16lb./105m</v>
+        <v>14lb./120m / 16lb./105m</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -1878,25 +2559,25 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>72cm</v>
+        <v>72</v>
       </c>
       <c r="L5" t="str">
         <v/>
       </c>
       <c r="M5" t="str">
-        <v>10BB , 1RB</v>
+        <v>10/1</v>
       </c>
       <c r="N5" t="str">
-        <v>92500</v>
+        <v>¥92,500</v>
       </c>
       <c r="O5" t="str">
         <v/>
       </c>
       <c r="P5" t="str">
-        <v>2026-04-09T16:03:06.104Z</v>
+        <v>2026-04-21T12:02:57.755Z</v>
       </c>
       <c r="Q5" t="str">
-        <v>2026-04-09T16:03:06.104Z</v>
+        <v>2026-04-21T12:02:57.755Z</v>
       </c>
       <c r="R5" t="str">
         <v/>
@@ -1904,8 +2585,89 @@
       <c r="S5" t="str">
         <v/>
       </c>
+      <c r="T5" t="str">
+        <v/>
+      </c>
+      <c r="U5" t="str">
+        <v/>
+      </c>
+      <c r="V5" t="str">
+        <v>L/R</v>
+      </c>
+      <c r="W5" t="str">
+        <v>铝</v>
+      </c>
+      <c r="X5" t="str">
+        <v>Monoblock 进化平台</v>
+      </c>
+      <c r="Y5" t="str">
+        <v/>
+      </c>
+      <c r="Z5" t="str">
+        <v/>
+      </c>
+      <c r="AA5" t="str">
+        <v/>
+      </c>
+      <c r="AB5" t="str">
+        <v/>
+      </c>
+      <c r="AC5" t="str">
+        <v/>
+      </c>
+      <c r="AD5" t="str">
+        <v/>
+      </c>
+      <c r="AE5" t="str">
+        <v/>
+      </c>
+      <c r="AF5" t="str">
+        <v/>
+      </c>
+      <c r="AG5" t="str">
+        <v/>
+      </c>
+      <c r="AH5" t="str">
+        <v/>
+      </c>
+      <c r="AI5" t="str">
+        <v/>
+      </c>
+      <c r="AJ5" t="str">
+        <v/>
+      </c>
+      <c r="AK5" t="str">
+        <v>复古,收藏,顶水</v>
+      </c>
+      <c r="AL5" t="str">
+        <v>约 7g+</v>
+      </c>
+      <c r="AM5" t="str">
+        <v/>
+      </c>
       <c r="AN5" t="str">
+        <v>单摇臂</v>
+      </c>
+      <c r="AO5" t="str">
+        <v/>
+      </c>
+      <c r="AP5" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AQ5" t="str">
+        <v>淡水路亚</v>
+      </c>
+      <c r="AR5" t="str">
+        <v>顶水 / 收藏</v>
+      </c>
+      <c r="AS5" t="str">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -1919,7 +2681,7 @@
         <v>MONOBLOCK SPECIALE</v>
       </c>
       <c r="D6" t="str">
-        <v>6.8:1</v>
+        <v>6.8</v>
       </c>
       <c r="E6" t="str">
         <v>4.0</v>
@@ -1931,7 +2693,7 @@
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>14lb./120m , 16lb./105m</v>
+        <v>14lb./120m / 16lb./105m</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -1940,25 +2702,25 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>72cm</v>
+        <v>72</v>
       </c>
       <c r="L6" t="str">
         <v/>
       </c>
       <c r="M6" t="str">
-        <v>10BB , 1RB</v>
+        <v>10/1</v>
       </c>
       <c r="N6" t="str">
-        <v>92500</v>
+        <v>¥92,500</v>
       </c>
       <c r="O6" t="str">
         <v/>
       </c>
       <c r="P6" t="str">
-        <v>2026-04-09T16:03:06.704Z</v>
+        <v>2026-04-21T12:02:58.400Z</v>
       </c>
       <c r="Q6" t="str">
-        <v>2026-04-09T16:03:06.704Z</v>
+        <v>2026-04-21T12:02:58.400Z</v>
       </c>
       <c r="R6" t="str">
         <v/>
@@ -1966,8 +2728,89 @@
       <c r="S6" t="str">
         <v/>
       </c>
+      <c r="T6" t="str">
+        <v/>
+      </c>
+      <c r="U6" t="str">
+        <v/>
+      </c>
+      <c r="V6" t="str">
+        <v>L/R</v>
+      </c>
+      <c r="W6" t="str">
+        <v>铝</v>
+      </c>
+      <c r="X6" t="str">
+        <v>高性能 Monoblock 平台</v>
+      </c>
+      <c r="Y6" t="str">
+        <v/>
+      </c>
+      <c r="Z6" t="str">
+        <v/>
+      </c>
+      <c r="AA6" t="str">
+        <v/>
+      </c>
+      <c r="AB6" t="str">
+        <v/>
+      </c>
+      <c r="AC6" t="str">
+        <v/>
+      </c>
+      <c r="AD6" t="str">
+        <v/>
+      </c>
+      <c r="AE6" t="str">
+        <v/>
+      </c>
+      <c r="AF6" t="str">
+        <v/>
+      </c>
+      <c r="AG6" t="str">
+        <v/>
+      </c>
+      <c r="AH6" t="str">
+        <v/>
+      </c>
+      <c r="AI6" t="str">
+        <v/>
+      </c>
+      <c r="AJ6" t="str">
+        <v/>
+      </c>
+      <c r="AK6" t="str">
+        <v>高端,重装,快饵</v>
+      </c>
+      <c r="AL6" t="str">
+        <v>约 7g+</v>
+      </c>
+      <c r="AM6" t="str">
+        <v/>
+      </c>
       <c r="AN6" t="str">
+        <v>单摇臂</v>
+      </c>
+      <c r="AO6" t="str">
+        <v/>
+      </c>
+      <c r="AP6" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AQ6" t="str">
+        <v>淡水路亚</v>
+      </c>
+      <c r="AR6" t="str">
+        <v>快饵 / 重装</v>
+      </c>
+      <c r="AS6" t="str">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1981,7 +2824,7 @@
         <v>RHODIUM 73</v>
       </c>
       <c r="D7" t="str">
-        <v>7.3:1</v>
+        <v>7.3</v>
       </c>
       <c r="E7" t="str">
         <v>5.0</v>
@@ -2002,25 +2845,25 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>74cm</v>
+        <v>74</v>
       </c>
       <c r="L7" t="str">
         <v/>
       </c>
       <c r="M7" t="str">
-        <v>6BB:1RB</v>
+        <v>6/1</v>
       </c>
       <c r="N7" t="str">
-        <v>32000</v>
+        <v>¥32,000</v>
       </c>
       <c r="O7" t="str">
         <v/>
       </c>
       <c r="P7" t="str">
-        <v>2026-04-09T16:03:07.101Z</v>
+        <v>2026-04-21T12:02:59.044Z</v>
       </c>
       <c r="Q7" t="str">
-        <v>2026-04-09T16:03:07.101Z</v>
+        <v>2026-04-21T12:02:59.044Z</v>
       </c>
       <c r="R7" t="str">
         <v/>
@@ -2028,8 +2871,89 @@
       <c r="S7" t="str">
         <v/>
       </c>
+      <c r="T7" t="str">
+        <v/>
+      </c>
+      <c r="U7" t="str">
+        <v/>
+      </c>
+      <c r="V7" t="str">
+        <v/>
+      </c>
+      <c r="W7" t="str">
+        <v>金属机身</v>
+      </c>
+      <c r="X7" t="str">
+        <v>AIR 制动系统 / 超轻量SV线杯</v>
+      </c>
+      <c r="Y7" t="str">
+        <v/>
+      </c>
+      <c r="Z7" t="str">
+        <v/>
+      </c>
+      <c r="AA7" t="str">
+        <v/>
+      </c>
+      <c r="AB7" t="str">
+        <v/>
+      </c>
+      <c r="AC7" t="str">
+        <v/>
+      </c>
+      <c r="AD7" t="str">
+        <v/>
+      </c>
+      <c r="AE7" t="str">
+        <v/>
+      </c>
+      <c r="AF7" t="str">
+        <v/>
+      </c>
+      <c r="AG7" t="str">
+        <v/>
+      </c>
+      <c r="AH7" t="str">
+        <v/>
+      </c>
+      <c r="AI7" t="str">
+        <v/>
+      </c>
+      <c r="AJ7" t="str">
+        <v/>
+      </c>
+      <c r="AK7" t="str">
+        <v>鲈鱼,高速,cover</v>
+      </c>
+      <c r="AL7" t="str">
+        <v>约 5g+</v>
+      </c>
+      <c r="AM7" t="str">
+        <v/>
+      </c>
       <c r="AN7" t="str">
+        <v>单摇臂</v>
+      </c>
+      <c r="AO7" t="str">
+        <v/>
+      </c>
+      <c r="AP7" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AQ7" t="str">
+        <v>淡水路亚</v>
+      </c>
+      <c r="AR7" t="str">
+        <v>鲈鱼 / Cover</v>
+      </c>
+      <c r="AS7" t="str">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -2043,7 +2967,7 @@
         <v>RHODIUM 81</v>
       </c>
       <c r="D8" t="str">
-        <v>8.1:1</v>
+        <v>8.1</v>
       </c>
       <c r="E8" t="str">
         <v>5.0</v>
@@ -2064,25 +2988,25 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>83cm</v>
+        <v>83</v>
       </c>
       <c r="L8" t="str">
         <v/>
       </c>
       <c r="M8" t="str">
-        <v>6BB:1RB</v>
+        <v>6/1</v>
       </c>
       <c r="N8" t="str">
-        <v>32000</v>
+        <v>¥32,000</v>
       </c>
       <c r="O8" t="str">
         <v/>
       </c>
       <c r="P8" t="str">
-        <v>2026-04-09T16:03:07.457Z</v>
+        <v>2026-04-21T12:02:59.672Z</v>
       </c>
       <c r="Q8" t="str">
-        <v>2026-04-09T16:03:07.457Z</v>
+        <v>2026-04-21T12:02:59.672Z</v>
       </c>
       <c r="R8" t="str">
         <v/>
@@ -2090,8 +3014,89 @@
       <c r="S8" t="str">
         <v/>
       </c>
+      <c r="T8" t="str">
+        <v/>
+      </c>
+      <c r="U8" t="str">
+        <v/>
+      </c>
+      <c r="V8" t="str">
+        <v/>
+      </c>
+      <c r="W8" t="str">
+        <v>金属机身</v>
+      </c>
+      <c r="X8" t="str">
+        <v>AIR 制动系统 / 超轻量SV线杯</v>
+      </c>
+      <c r="Y8" t="str">
+        <v/>
+      </c>
+      <c r="Z8" t="str">
+        <v/>
+      </c>
+      <c r="AA8" t="str">
+        <v/>
+      </c>
+      <c r="AB8" t="str">
+        <v/>
+      </c>
+      <c r="AC8" t="str">
+        <v/>
+      </c>
+      <c r="AD8" t="str">
+        <v/>
+      </c>
+      <c r="AE8" t="str">
+        <v/>
+      </c>
+      <c r="AF8" t="str">
+        <v/>
+      </c>
+      <c r="AG8" t="str">
+        <v/>
+      </c>
+      <c r="AH8" t="str">
+        <v/>
+      </c>
+      <c r="AI8" t="str">
+        <v/>
+      </c>
+      <c r="AJ8" t="str">
+        <v/>
+      </c>
+      <c r="AK8" t="str">
+        <v>鲈鱼,超高速,cover</v>
+      </c>
+      <c r="AL8" t="str">
+        <v>约 5g+</v>
+      </c>
+      <c r="AM8" t="str">
+        <v/>
+      </c>
       <c r="AN8" t="str">
+        <v>单摇臂</v>
+      </c>
+      <c r="AO8" t="str">
+        <v/>
+      </c>
+      <c r="AP8" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AQ8" t="str">
+        <v>淡水路亚</v>
+      </c>
+      <c r="AR8" t="str">
+        <v>鲈鱼 / 快搜</v>
+      </c>
+      <c r="AS8" t="str">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -2105,7 +3110,7 @@
         <v>RHODIUM 63</v>
       </c>
       <c r="D9" t="str">
-        <v>6.3:1</v>
+        <v>6.3</v>
       </c>
       <c r="E9" t="str">
         <v>5.0</v>
@@ -2126,25 +3131,25 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>65cm</v>
+        <v>65</v>
       </c>
       <c r="L9" t="str">
         <v/>
       </c>
       <c r="M9" t="str">
-        <v>6BB:1RB</v>
+        <v>6/1</v>
       </c>
       <c r="N9" t="str">
-        <v>32000</v>
+        <v>¥32,000</v>
       </c>
       <c r="O9" t="str">
         <v/>
       </c>
       <c r="P9" t="str">
-        <v>2026-04-09T16:03:07.869Z</v>
+        <v>2026-04-21T12:03:00.367Z</v>
       </c>
       <c r="Q9" t="str">
-        <v>2026-04-09T16:03:07.869Z</v>
+        <v>2026-04-21T12:03:00.367Z</v>
       </c>
       <c r="R9" t="str">
         <v/>
@@ -2152,8 +3157,89 @@
       <c r="S9" t="str">
         <v/>
       </c>
+      <c r="T9" t="str">
+        <v/>
+      </c>
+      <c r="U9" t="str">
+        <v/>
+      </c>
+      <c r="V9" t="str">
+        <v/>
+      </c>
+      <c r="W9" t="str">
+        <v>金属机身</v>
+      </c>
+      <c r="X9" t="str">
+        <v>AIR 制动系统 / 超轻量SV线杯</v>
+      </c>
+      <c r="Y9" t="str">
+        <v/>
+      </c>
+      <c r="Z9" t="str">
+        <v/>
+      </c>
+      <c r="AA9" t="str">
+        <v/>
+      </c>
+      <c r="AB9" t="str">
+        <v/>
+      </c>
+      <c r="AC9" t="str">
+        <v/>
+      </c>
+      <c r="AD9" t="str">
+        <v/>
+      </c>
+      <c r="AE9" t="str">
+        <v/>
+      </c>
+      <c r="AF9" t="str">
+        <v/>
+      </c>
+      <c r="AG9" t="str">
+        <v/>
+      </c>
+      <c r="AH9" t="str">
+        <v/>
+      </c>
+      <c r="AI9" t="str">
+        <v/>
+      </c>
+      <c r="AJ9" t="str">
+        <v/>
+      </c>
+      <c r="AK9" t="str">
+        <v>低速,扭矩,卷阻饵</v>
+      </c>
+      <c r="AL9" t="str">
+        <v>约 7g+</v>
+      </c>
+      <c r="AM9" t="str">
+        <v/>
+      </c>
       <c r="AN9" t="str">
+        <v>单摇臂</v>
+      </c>
+      <c r="AO9" t="str">
+        <v/>
+      </c>
+      <c r="AP9" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AQ9" t="str">
+        <v>淡水路亚</v>
+      </c>
+      <c r="AR9" t="str">
+        <v>卷阻饵 / 扭矩</v>
+      </c>
+      <c r="AS9" t="str">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -2170,7 +3256,7 @@
         <v>5.1 : 1</v>
       </c>
       <c r="E10" t="str">
-        <v>5.5lb.</v>
+        <v>2.5</v>
       </c>
       <c r="F10" t="str">
         <v>255</v>
@@ -2179,7 +3265,7 @@
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>8lb./100yd , 10lb./75yd</v>
+        <v>8lb./100yd / 10lb./75yd</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -2194,19 +3280,19 @@
         <v/>
       </c>
       <c r="M10" t="str">
-        <v>5BB</v>
+        <v>5/0</v>
       </c>
       <c r="N10" t="str">
-        <v>42800</v>
+        <v>¥42,800</v>
       </c>
       <c r="O10" t="str">
         <v/>
       </c>
       <c r="P10" t="str">
-        <v>2026-04-09T16:03:08.227Z</v>
+        <v>2026-04-21T12:03:00.881Z</v>
       </c>
       <c r="Q10" t="str">
-        <v>2026-04-09T16:03:08.227Z</v>
+        <v>2026-04-21T12:03:00.881Z</v>
       </c>
       <c r="R10" t="str">
         <v/>
@@ -2214,8 +3300,89 @@
       <c r="S10" t="str">
         <v/>
       </c>
+      <c r="T10" t="str">
+        <v/>
+      </c>
+      <c r="U10" t="str">
+        <v/>
+      </c>
+      <c r="V10" t="str">
+        <v>L/R</v>
+      </c>
+      <c r="W10" t="str">
+        <v>复古金属机体</v>
+      </c>
+      <c r="X10" t="str">
+        <v>Quatro Servo Brake</v>
+      </c>
+      <c r="Y10" t="str">
+        <v/>
+      </c>
+      <c r="Z10" t="str">
+        <v/>
+      </c>
+      <c r="AA10" t="str">
+        <v/>
+      </c>
+      <c r="AB10" t="str">
+        <v/>
+      </c>
+      <c r="AC10" t="str">
+        <v/>
+      </c>
+      <c r="AD10" t="str">
+        <v/>
+      </c>
+      <c r="AE10" t="str">
+        <v/>
+      </c>
+      <c r="AF10" t="str">
+        <v/>
+      </c>
+      <c r="AG10" t="str">
+        <v/>
+      </c>
+      <c r="AH10" t="str">
+        <v/>
+      </c>
+      <c r="AI10" t="str">
+        <v/>
+      </c>
+      <c r="AJ10" t="str">
+        <v/>
+      </c>
+      <c r="AK10" t="str">
+        <v>复古,顶水,收藏</v>
+      </c>
+      <c r="AL10" t="str">
+        <v>约 7g+</v>
+      </c>
+      <c r="AM10" t="str">
+        <v/>
+      </c>
       <c r="AN10" t="str">
+        <v>单摇臂</v>
+      </c>
+      <c r="AO10" t="str">
+        <v/>
+      </c>
+      <c r="AP10" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AQ10" t="str">
+        <v>淡水路亚</v>
+      </c>
+      <c r="AR10" t="str">
+        <v>顶水 / 风格</v>
+      </c>
+      <c r="AS10" t="str">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -2229,7 +3396,7 @@
         <v>Pagani P200</v>
       </c>
       <c r="D11" t="str">
-        <v>6.1:1</v>
+        <v>6.1</v>
       </c>
       <c r="E11" t="str">
         <v>3.0</v>
@@ -2241,7 +3408,7 @@
         <v/>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>8lb./155yards、10lb./123yards</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -2250,25 +3417,25 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>8lb./155yards、10lb./123yards</v>
+        <v/>
       </c>
       <c r="L11" t="str">
         <v/>
       </c>
       <c r="M11" t="str">
-        <v>5BB</v>
+        <v>5/0</v>
       </c>
       <c r="N11" t="str">
-        <v>41000</v>
+        <v>¥41,000</v>
       </c>
       <c r="O11" t="str">
         <v/>
       </c>
       <c r="P11" t="str">
-        <v>2026-04-09T16:03:08.638Z</v>
+        <v>2026-04-21T12:03:01.354Z</v>
       </c>
       <c r="Q11" t="str">
-        <v>2026-04-09T16:03:08.638Z</v>
+        <v>2026-04-21T12:03:01.354Z</v>
       </c>
       <c r="R11" t="str">
         <v/>
@@ -2276,8 +3443,89 @@
       <c r="S11" t="str">
         <v/>
       </c>
+      <c r="T11" t="str">
+        <v/>
+      </c>
+      <c r="U11" t="str">
+        <v/>
+      </c>
+      <c r="V11" t="str">
+        <v>L/R</v>
+      </c>
+      <c r="W11" t="str">
+        <v>复古金属机体</v>
+      </c>
+      <c r="X11" t="str">
+        <v>Quatro Servo Brake</v>
+      </c>
+      <c r="Y11" t="str">
+        <v/>
+      </c>
+      <c r="Z11" t="str">
+        <v/>
+      </c>
+      <c r="AA11" t="str">
+        <v/>
+      </c>
+      <c r="AB11" t="str">
+        <v/>
+      </c>
+      <c r="AC11" t="str">
+        <v/>
+      </c>
+      <c r="AD11" t="str">
+        <v/>
+      </c>
+      <c r="AE11" t="str">
+        <v/>
+      </c>
+      <c r="AF11" t="str">
+        <v/>
+      </c>
+      <c r="AG11" t="str">
+        <v/>
+      </c>
+      <c r="AH11" t="str">
+        <v/>
+      </c>
+      <c r="AI11" t="str">
+        <v/>
+      </c>
+      <c r="AJ11" t="str">
+        <v/>
+      </c>
+      <c r="AK11" t="str">
+        <v>复古,轻插,收藏</v>
+      </c>
+      <c r="AL11" t="str">
+        <v>约 5g+</v>
+      </c>
+      <c r="AM11" t="str">
+        <v/>
+      </c>
       <c r="AN11" t="str">
+        <v>单摇臂</v>
+      </c>
+      <c r="AO11" t="str">
+        <v/>
+      </c>
+      <c r="AP11" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AQ11" t="str">
+        <v>淡水路亚</v>
+      </c>
+      <c r="AR11" t="str">
+        <v>顶水 / 风格</v>
+      </c>
+      <c r="AS11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -2291,10 +3539,10 @@
         <v>Pagani P300</v>
       </c>
       <c r="D12" t="str">
-        <v>6.1:1</v>
+        <v>6.1</v>
       </c>
       <c r="E12" t="str">
-        <v>6.6lb(3)</v>
+        <v>3</v>
       </c>
       <c r="F12" t="str">
         <v>250</v>
@@ -2303,7 +3551,7 @@
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>8lb./200yd , 10lb./160yd , 12lb./135yd</v>
+        <v>8lb./200yd / 10lb./160yd / 12lb./135yd</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -2318,19 +3566,19 @@
         <v/>
       </c>
       <c r="M12" t="str">
-        <v>5BB</v>
+        <v>5/0</v>
       </c>
       <c r="N12" t="str">
-        <v>40000</v>
+        <v>¥40,000</v>
       </c>
       <c r="O12" t="str">
         <v/>
       </c>
       <c r="P12" t="str">
-        <v>2026-04-09T16:03:09.002Z</v>
+        <v>2026-04-21T12:03:01.851Z</v>
       </c>
       <c r="Q12" t="str">
-        <v>2026-04-09T16:03:09.002Z</v>
+        <v>2026-04-21T12:03:01.851Z</v>
       </c>
       <c r="R12" t="str">
         <v/>
@@ -2338,8 +3586,89 @@
       <c r="S12" t="str">
         <v/>
       </c>
+      <c r="T12" t="str">
+        <v/>
+      </c>
+      <c r="U12" t="str">
+        <v/>
+      </c>
+      <c r="V12" t="str">
+        <v>L/R</v>
+      </c>
+      <c r="W12" t="str">
+        <v>复古金属机体</v>
+      </c>
+      <c r="X12" t="str">
+        <v>Pagani 旗舰平台</v>
+      </c>
+      <c r="Y12" t="str">
+        <v/>
+      </c>
+      <c r="Z12" t="str">
+        <v/>
+      </c>
+      <c r="AA12" t="str">
+        <v/>
+      </c>
+      <c r="AB12" t="str">
+        <v/>
+      </c>
+      <c r="AC12" t="str">
+        <v/>
+      </c>
+      <c r="AD12" t="str">
+        <v/>
+      </c>
+      <c r="AE12" t="str">
+        <v/>
+      </c>
+      <c r="AF12" t="str">
+        <v/>
+      </c>
+      <c r="AG12" t="str">
+        <v/>
+      </c>
+      <c r="AH12" t="str">
+        <v/>
+      </c>
+      <c r="AI12" t="str">
+        <v/>
+      </c>
+      <c r="AJ12" t="str">
+        <v/>
+      </c>
+      <c r="AK12" t="str">
+        <v>复古,顶水,大尺寸</v>
+      </c>
+      <c r="AL12" t="str">
+        <v>约 10g+</v>
+      </c>
+      <c r="AM12" t="str">
+        <v/>
+      </c>
       <c r="AN12" t="str">
+        <v>单摇臂</v>
+      </c>
+      <c r="AO12" t="str">
+        <v/>
+      </c>
+      <c r="AP12" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AQ12" t="str">
+        <v>淡水路亚</v>
+      </c>
+      <c r="AR12" t="str">
+        <v>顶水 / 风格</v>
+      </c>
+      <c r="AS12" t="str">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -2353,7 +3682,7 @@
         <v>LAUDA58</v>
       </c>
       <c r="D13" t="str">
-        <v>5.8:1</v>
+        <v>5.8</v>
       </c>
       <c r="E13" t="str">
         <v>4.0</v>
@@ -2365,7 +3694,7 @@
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>12lb./40-80m , 14lb./35-70m</v>
+        <v>12lb./40-80m / 14lb./35-70m</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -2374,25 +3703,25 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>60cm</v>
+        <v>60</v>
       </c>
       <c r="L13" t="str">
         <v/>
       </c>
       <c r="M13" t="str">
-        <v>6BB , 1RB</v>
+        <v>6/1</v>
       </c>
       <c r="N13" t="str">
-        <v>38500</v>
+        <v>¥38,500</v>
       </c>
       <c r="O13" t="str">
         <v/>
       </c>
       <c r="P13" t="str">
-        <v>2026-04-09T16:03:09.406Z</v>
+        <v>2026-04-21T12:03:02.339Z</v>
       </c>
       <c r="Q13" t="str">
-        <v>2026-04-09T16:03:09.406Z</v>
+        <v>2026-04-21T12:03:02.339Z</v>
       </c>
       <c r="R13" t="str">
         <v/>
@@ -2400,8 +3729,89 @@
       <c r="S13" t="str">
         <v/>
       </c>
+      <c r="T13" t="str">
+        <v/>
+      </c>
+      <c r="U13" t="str">
+        <v/>
+      </c>
+      <c r="V13" t="str">
+        <v>L/R</v>
+      </c>
+      <c r="W13" t="str">
+        <v>铝合金机体</v>
+      </c>
+      <c r="X13" t="str">
+        <v>SV spool / 低速扭矩</v>
+      </c>
+      <c r="Y13" t="str">
+        <v/>
+      </c>
+      <c r="Z13" t="str">
+        <v/>
+      </c>
+      <c r="AA13" t="str">
+        <v/>
+      </c>
+      <c r="AB13" t="str">
+        <v/>
+      </c>
+      <c r="AC13" t="str">
+        <v/>
+      </c>
+      <c r="AD13" t="str">
+        <v/>
+      </c>
+      <c r="AE13" t="str">
+        <v/>
+      </c>
+      <c r="AF13" t="str">
+        <v/>
+      </c>
+      <c r="AG13" t="str">
+        <v/>
+      </c>
+      <c r="AH13" t="str">
+        <v/>
+      </c>
+      <c r="AI13" t="str">
+        <v/>
+      </c>
+      <c r="AJ13" t="str">
+        <v/>
+      </c>
+      <c r="AK13" t="str">
+        <v>低速,卷阻饵,扭矩</v>
+      </c>
+      <c r="AL13" t="str">
+        <v>约 5g+</v>
+      </c>
+      <c r="AM13" t="str">
+        <v/>
+      </c>
       <c r="AN13" t="str">
+        <v>单摇臂</v>
+      </c>
+      <c r="AO13" t="str">
+        <v/>
+      </c>
+      <c r="AP13" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AQ13" t="str">
+        <v>淡水路亚</v>
+      </c>
+      <c r="AR13" t="str">
+        <v>卷阻饵 / 稳定检索</v>
+      </c>
+      <c r="AS13" t="str">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -2415,7 +3825,7 @@
         <v>LAUDA72</v>
       </c>
       <c r="D14" t="str">
-        <v>7.2:1</v>
+        <v>7.2</v>
       </c>
       <c r="E14" t="str">
         <v>4.0</v>
@@ -2427,7 +3837,7 @@
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>12lb./40-80m , 14lb./35-70m</v>
+        <v>12lb./40-80m / 14lb./35-70m</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -2436,25 +3846,25 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>73cm</v>
+        <v>73</v>
       </c>
       <c r="L14" t="str">
         <v/>
       </c>
       <c r="M14" t="str">
-        <v>6BB , 1RB</v>
+        <v>6/1</v>
       </c>
       <c r="N14" t="str">
-        <v>38500</v>
+        <v>¥38,500</v>
       </c>
       <c r="O14" t="str">
         <v/>
       </c>
       <c r="P14" t="str">
-        <v>2026-04-09T16:03:09.802Z</v>
+        <v>2026-04-21T12:03:02.843Z</v>
       </c>
       <c r="Q14" t="str">
-        <v>2026-04-09T16:03:09.802Z</v>
+        <v>2026-04-21T12:03:02.843Z</v>
       </c>
       <c r="R14" t="str">
         <v/>
@@ -2462,8 +3872,89 @@
       <c r="S14" t="str">
         <v/>
       </c>
+      <c r="T14" t="str">
+        <v/>
+      </c>
+      <c r="U14" t="str">
+        <v/>
+      </c>
+      <c r="V14" t="str">
+        <v>L/R</v>
+      </c>
+      <c r="W14" t="str">
+        <v>铝合金机体</v>
+      </c>
+      <c r="X14" t="str">
+        <v>超轻量 duralumin SV spool / 高感度旋钮</v>
+      </c>
+      <c r="Y14" t="str">
+        <v/>
+      </c>
+      <c r="Z14" t="str">
+        <v/>
+      </c>
+      <c r="AA14" t="str">
+        <v/>
+      </c>
+      <c r="AB14" t="str">
+        <v/>
+      </c>
+      <c r="AC14" t="str">
+        <v/>
+      </c>
+      <c r="AD14" t="str">
+        <v/>
+      </c>
+      <c r="AE14" t="str">
+        <v/>
+      </c>
+      <c r="AF14" t="str">
+        <v/>
+      </c>
+      <c r="AG14" t="str">
+        <v/>
+      </c>
+      <c r="AH14" t="str">
+        <v/>
+      </c>
+      <c r="AI14" t="str">
+        <v/>
+      </c>
+      <c r="AJ14" t="str">
+        <v/>
+      </c>
+      <c r="AK14" t="str">
+        <v>高速,远投,鲈鱼</v>
+      </c>
+      <c r="AL14" t="str">
+        <v>约 5g+</v>
+      </c>
+      <c r="AM14" t="str">
+        <v/>
+      </c>
       <c r="AN14" t="str">
+        <v>单摇臂</v>
+      </c>
+      <c r="AO14" t="str">
+        <v/>
+      </c>
+      <c r="AP14" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AQ14" t="str">
+        <v>淡水路亚</v>
+      </c>
+      <c r="AR14" t="str">
+        <v>鲈鱼 / 快节奏泛用</v>
+      </c>
+      <c r="AS14" t="str">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -2477,7 +3968,7 @@
         <v>LAUDA72 LIMITED EDITION</v>
       </c>
       <c r="D15" t="str">
-        <v>7.2:1</v>
+        <v>7.2</v>
       </c>
       <c r="E15" t="str">
         <v>4.0</v>
@@ -2489,7 +3980,7 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>12lb./40-80m , 14lb./35-70m</v>
+        <v>12lb./40-80m / 14lb./35-70m</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -2498,25 +3989,25 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>73cm</v>
+        <v>73</v>
       </c>
       <c r="L15" t="str">
         <v/>
       </c>
       <c r="M15" t="str">
-        <v>6BB , 1RB</v>
+        <v>6/1</v>
       </c>
       <c r="N15" t="str">
-        <v>42500</v>
+        <v>¥42,500</v>
       </c>
       <c r="O15" t="str">
         <v/>
       </c>
       <c r="P15" t="str">
-        <v>2026-04-09T16:03:10.384Z</v>
+        <v>2026-04-21T12:03:03.499Z</v>
       </c>
       <c r="Q15" t="str">
-        <v>2026-04-09T16:03:10.384Z</v>
+        <v>2026-04-21T12:03:03.499Z</v>
       </c>
       <c r="R15" t="str">
         <v/>
@@ -2524,8 +4015,89 @@
       <c r="S15" t="str">
         <v/>
       </c>
+      <c r="T15" t="str">
+        <v/>
+      </c>
+      <c r="U15" t="str">
+        <v/>
+      </c>
+      <c r="V15" t="str">
+        <v>L/R</v>
+      </c>
+      <c r="W15" t="str">
+        <v>铝合金机体</v>
+      </c>
+      <c r="X15" t="str">
+        <v>80mm 碳手柄 / 限量轻量版</v>
+      </c>
+      <c r="Y15" t="str">
+        <v/>
+      </c>
+      <c r="Z15" t="str">
+        <v/>
+      </c>
+      <c r="AA15" t="str">
+        <v/>
+      </c>
+      <c r="AB15" t="str">
+        <v/>
+      </c>
+      <c r="AC15" t="str">
+        <v/>
+      </c>
+      <c r="AD15" t="str">
+        <v/>
+      </c>
+      <c r="AE15" t="str">
+        <v/>
+      </c>
+      <c r="AF15" t="str">
+        <v/>
+      </c>
+      <c r="AG15" t="str">
+        <v/>
+      </c>
+      <c r="AH15" t="str">
+        <v/>
+      </c>
+      <c r="AI15" t="str">
+        <v/>
+      </c>
+      <c r="AJ15" t="str">
+        <v/>
+      </c>
+      <c r="AK15" t="str">
+        <v>限量,轻量,高速</v>
+      </c>
+      <c r="AL15" t="str">
+        <v>约 5g+</v>
+      </c>
+      <c r="AM15" t="str">
+        <v/>
+      </c>
       <c r="AN15" t="str">
+        <v>单摇臂</v>
+      </c>
+      <c r="AO15" t="str">
+        <v/>
+      </c>
+      <c r="AP15" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AQ15" t="str">
+        <v>淡水路亚</v>
+      </c>
+      <c r="AR15" t="str">
+        <v>鲈鱼 / 轻量高端</v>
+      </c>
+      <c r="AS15" t="str">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -2539,7 +4111,7 @@
         <v>IP79</v>
       </c>
       <c r="D16" t="str">
-        <v>7.9:1</v>
+        <v>7.9</v>
       </c>
       <c r="E16" t="str">
         <v>5.0</v>
@@ -2551,7 +4123,7 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>12lb./135m , 16lb./100m</v>
+        <v>12lb./135m / 16lb./100m</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -2560,25 +4132,25 @@
         <v/>
       </c>
       <c r="K16" t="str">
-        <v>89cm</v>
+        <v>89</v>
       </c>
       <c r="L16" t="str">
         <v/>
       </c>
       <c r="M16" t="str">
-        <v>10BB , 1RB</v>
+        <v>10/1</v>
       </c>
       <c r="N16" t="str">
-        <v>45000</v>
+        <v>¥45,000</v>
       </c>
       <c r="O16" t="str">
         <v/>
       </c>
       <c r="P16" t="str">
-        <v>2026-04-09T16:03:10.796Z</v>
+        <v>2026-04-21T12:03:04.131Z</v>
       </c>
       <c r="Q16" t="str">
-        <v>2026-04-09T16:03:10.796Z</v>
+        <v>2026-04-21T12:03:04.131Z</v>
       </c>
       <c r="R16" t="str">
         <v/>
@@ -2586,8 +4158,89 @@
       <c r="S16" t="str">
         <v/>
       </c>
+      <c r="T16" t="str">
+        <v/>
+      </c>
+      <c r="U16" t="str">
+        <v/>
+      </c>
+      <c r="V16" t="str">
+        <v>L/R</v>
+      </c>
+      <c r="W16" t="str">
+        <v>全金属机身</v>
+      </c>
+      <c r="X16" t="str">
+        <v>大口径窄线杯 / 长柄 Power handle</v>
+      </c>
+      <c r="Y16" t="str">
+        <v/>
+      </c>
+      <c r="Z16" t="str">
+        <v/>
+      </c>
+      <c r="AA16" t="str">
+        <v/>
+      </c>
+      <c r="AB16" t="str">
+        <v/>
+      </c>
+      <c r="AC16" t="str">
+        <v/>
+      </c>
+      <c r="AD16" t="str">
+        <v/>
+      </c>
+      <c r="AE16" t="str">
+        <v/>
+      </c>
+      <c r="AF16" t="str">
+        <v/>
+      </c>
+      <c r="AG16" t="str">
+        <v/>
+      </c>
+      <c r="AH16" t="str">
+        <v/>
+      </c>
+      <c r="AI16" t="str">
+        <v/>
+      </c>
+      <c r="AJ16" t="str">
+        <v/>
+      </c>
+      <c r="AK16" t="str">
+        <v>power,高速,重装</v>
+      </c>
+      <c r="AL16" t="str">
+        <v>约 10g+</v>
+      </c>
+      <c r="AM16" t="str">
+        <v/>
+      </c>
       <c r="AN16" t="str">
+        <v>单摇臂</v>
+      </c>
+      <c r="AO16" t="str">
+        <v/>
+      </c>
+      <c r="AP16" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AQ16" t="str">
+        <v>淡水路亚</v>
+      </c>
+      <c r="AR16" t="str">
+        <v>Power Fishing</v>
+      </c>
+      <c r="AS16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -2601,7 +4254,7 @@
         <v>IP68</v>
       </c>
       <c r="D17" t="str">
-        <v>6.8:1</v>
+        <v>6.8</v>
       </c>
       <c r="E17" t="str">
         <v>5.0</v>
@@ -2613,7 +4266,7 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>12lb./135m , 16lb./100m</v>
+        <v>12lb./135m / 16lb./100m</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -2622,25 +4275,25 @@
         <v/>
       </c>
       <c r="K17" t="str">
-        <v>77cm</v>
+        <v>77</v>
       </c>
       <c r="L17" t="str">
         <v/>
       </c>
       <c r="M17" t="str">
-        <v>10BB , 1RB</v>
+        <v>10/1</v>
       </c>
       <c r="N17" t="str">
-        <v>45000</v>
+        <v>¥45,000</v>
       </c>
       <c r="O17" t="str">
         <v/>
       </c>
       <c r="P17" t="str">
-        <v>2026-04-09T16:03:11.194Z</v>
+        <v>2026-04-21T12:03:04.627Z</v>
       </c>
       <c r="Q17" t="str">
-        <v>2026-04-09T16:03:11.194Z</v>
+        <v>2026-04-21T12:03:04.627Z</v>
       </c>
       <c r="R17" t="str">
         <v/>
@@ -2648,13 +4301,94 @@
       <c r="S17" t="str">
         <v/>
       </c>
+      <c r="T17" t="str">
+        <v/>
+      </c>
+      <c r="U17" t="str">
+        <v/>
+      </c>
+      <c r="V17" t="str">
+        <v>L/R</v>
+      </c>
+      <c r="W17" t="str">
+        <v>全金属机身</v>
+      </c>
+      <c r="X17" t="str">
+        <v>高扭矩平台 / Cover cranking</v>
+      </c>
+      <c r="Y17" t="str">
+        <v/>
+      </c>
+      <c r="Z17" t="str">
+        <v/>
+      </c>
+      <c r="AA17" t="str">
+        <v/>
+      </c>
+      <c r="AB17" t="str">
+        <v/>
+      </c>
+      <c r="AC17" t="str">
+        <v/>
+      </c>
+      <c r="AD17" t="str">
+        <v/>
+      </c>
+      <c r="AE17" t="str">
+        <v/>
+      </c>
+      <c r="AF17" t="str">
+        <v/>
+      </c>
+      <c r="AG17" t="str">
+        <v/>
+      </c>
+      <c r="AH17" t="str">
+        <v/>
+      </c>
+      <c r="AI17" t="str">
+        <v/>
+      </c>
+      <c r="AJ17" t="str">
+        <v/>
+      </c>
+      <c r="AK17" t="str">
+        <v>power,扭矩,cover</v>
+      </c>
+      <c r="AL17" t="str">
+        <v>约 10g+</v>
+      </c>
+      <c r="AM17" t="str">
+        <v/>
+      </c>
       <c r="AN17" t="str">
+        <v>单摇臂</v>
+      </c>
+      <c r="AO17" t="str">
+        <v/>
+      </c>
+      <c r="AP17" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AQ17" t="str">
+        <v>淡水路亚</v>
+      </c>
+      <c r="AR17" t="str">
+        <v>Power Fishing</v>
+      </c>
+      <c r="AS17" t="str">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AN17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AU17"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/pkgGear/data_raw/megabass_reel_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/megabass_reel_import.xlsx
@@ -34,11 +34,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">
@@ -489,14 +485,11 @@
       <c r="G2" t="str">
         <v/>
       </c>
-      <c r="H2" t="str">
-        <v>精细,轻量</v>
-      </c>
       <c r="I2" t="str">
         <v>spinning</v>
       </c>
       <c r="J2" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/GAUS%2020X_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_GAUS_20X-2.jpg</v>
       </c>
       <c r="K2" t="str">
         <v>2026-04-21T12:02:54.928Z</v>
@@ -505,7 +498,7 @@
         <v>2026-04-21T12:02:54.928Z</v>
       </c>
       <c r="M2" t="str">
-        <v>小型高端纺车</v>
+        <v/>
       </c>
       <c r="N2" t="str">
         <v>その名のとおり、あらゆるものを引き付けてしまう魔性を発揮する、スーパーコンパクトリールが、ついにベールを脱ぎました。 ガウスは、見た目のコンパクトな風貌からは想像できない強靭さと、これまでの基準を覆すハイパワーをスモールボディで発揮する、新世代のスピニングマシンとして開発されています。LIN258HMで高い評価を得た「磁性流体シールドシステム」を、そのコンパクトボディに搭載。大切なギアユニット内部をクリーンな状態に保つだけでなく、ボディとローターは実質無接点のため、シルキーな回転性能が長期間持続。羽の軽さとも評される「X-GRAPHITE COMPSITEROTER」は、スピニングリールにおける回転レスポンスを格段に引き上げると同時に、感度感知にも貢献。また、ハイパワーゲームにおいてローターの変形を抑えるため、ビッグフィッシュのファイトによる負荷をローター全体に分散するために開発した。「高密度カーボンコンポジットボディ」は、恐るべき軽さを実現しただけでなく、ついにその剛性は、マグネシウムを上回るレベルへと昇華。モンスターフィッシュとのドッグファイトでも、ボディのタワミがないから、ギア間が正確に噛み合うシルキーな回転性能と、それらが相まって生み出すトルクフルな巻き上げ性能が確実に維持されます。すべてが、いままでのスピニングリールの基準を覆すオーバースペックリール、GAUSが、いよいよスピニング新時代への扉を開きます。 / The "High Metal Honeycomb Spool" embodies the ultimate in robust and lightweight construction, made possible with Megabass' original carved metal manufacturing process. With the development of the "Magnetic Fluid Shield System," it creates the ideal head balance for spinning reels. The unlikely power generated from the super lightweight micro body gives it the extreme specs needed to combat record breaking fish with the ultimate finesse approach. The perpendicular 45mm crank handle excels at maintaining a steady and constant high speed retrieve with just a slight snapping motion of the wrist. This small superstar displays great ease of use with fast paced finesse rigs and light plugging in streams. / もはやこれ以上はない堅牢さと軽量化を高次元で両立させた、メガバス独自のメタル削り出し構造による「ハイメタル・ハニカムスプール」は、「磁性流体シールドシステム」の開発によって、スピニングリールにおける理想的なヘッドバランスを実現。その超軽量マイクロボディが発揮してしまう、およそ似合わないハイパワーは、究極のフィネスアプローチでレコードフィッシュと真っ向からわたり合うためのエクストリームなスペック。45mmの垂直クランクハンドルは、手首のわずかなスナップモーションで、ブレなく一定スピードを保持した高速リーリングに最適。フィネスリグの素早いピックアップや、ストリームにおけるライトプラッギングで至極の快適性能を発揮する、小さな超新星です。</v>
@@ -523,10 +516,10 @@
         <v/>
       </c>
       <c r="S2" t="str">
-        <v>溪流与轻量精细</v>
+        <v/>
       </c>
       <c r="T2" t="str">
-        <v>超小机身 / 高响应 / 微饵与溪流操控友好</v>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -551,14 +544,11 @@
       <c r="G3" t="str">
         <v/>
       </c>
-      <c r="H3" t="str">
-        <v>泛用,海鲈,近海</v>
-      </c>
       <c r="I3" t="str">
         <v>spinning</v>
       </c>
       <c r="J3" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/GAUS%2030X_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_GAUS_30X-1.jpg</v>
       </c>
       <c r="K3" t="str">
         <v>2026-04-21T12:02:55.416Z</v>
@@ -567,7 +557,7 @@
         <v>2026-04-21T12:02:55.416Z</v>
       </c>
       <c r="M3" t="str">
-        <v>高扭矩纺车</v>
+        <v/>
       </c>
       <c r="N3" t="str">
         <v>その名のとおり、あらゆるものを引き付けてしまう魔性を発揮する、スーパーコンパクトリールが、ついにベールを脱ぎました。 ガウスは、見た目のコンパクトな風貌からは想像できない強靭さと、これまでの基準を覆すハイパワーをスモールボディで発揮する、新世代のスピニングマシンとして開発されています。LIN258HMで高い評価を得た「磁性流体シールドシステム」を、そのコンパクトボディに搭載。大切なギアユニット内部をクリーンな状態に保つだけでなく、ボディとローターは実質無接点のため、シルキーな回転性能が長期間持続。羽の軽さとも評される「X-GRAPHITE COMPSITEROTER」は、スピニングリールにおける回転レスポンスを格段に引き上げると同時に、感度感知にも貢献。また、ハイパワーゲームにおいてローターの変形を抑えるため、ビッグフィッシュのファイトによる負荷をローター全体に分散するために開発した。「高密度カーボンコンポジットボディ」は、恐るべき軽さを実現しただけでなく、ついにその剛性は、マグネシウムを上回るレベルへと昇華。モンスターフィッシュとのドッグファイトでも、ボディのタワミがないから、ギア間が正確に噛み合うシルキーな回転性能と、それらが相まって生み出すトルクフルな巻き上げ性能が確実に維持されます。すべてが、いままでのスピニングリールの基準を覆すオーバースペックリール、GAUSが、いよいよスピニング新時代への扉を開きます。 / The GAUS30X is a model tuned for active salt water games. The GAUS's solid high rigidity body and instantaneous torque generation will handle big fish with ease. Megabass' unique "Super Lightweight Carbon Hybrid Spool" reduces spool deflection by spreading out the massive weight loads that can occur during heavy line use. The GAUS is equipped with many cutting edge technologies and features to give it the edge in high power games, such as the magnetic fluid system, the powerful 55m machine cut handle, the design that allows for smooth initial rotation and control, the M Drag System, the high power gear system, etc. Once you use it, you won't be able to put it down. That's the power of the GAUS. / ガウス30Xは、シーバスゲームをはじめ、アクティブなソルトゲームにアジャストするモデルです。ガウスが身につけた圧倒的な高剛性ボディと、瞬時に太いトルクを立ち上げるシルキードライブフィールがビッグフィッシュゲームを快適にこなします。メガバス独自の「超軽量カーボン・ハイブリットスプール」は、太いラインにかかる多大な負荷がもたらすスプールのたわみや高荷重を分散して低減化。磁性流体システム、55mmの強靭なマシンカットハンドル、緻密に計算されたスムースな滑り出しとその制御について、徹底追及されたＭドラグシステム、ハイパワーギアシステムなどなど・・数え上げたらキリがありませんが、スピニングリールにおける新次元のハイパワーゲームは、ガウスが武装した最新テクノロジーによって、ついに具現化。一度お使いいただくと、手放せなくなる快適性能こそが、ガウスの魔力を物語ります。</v>
@@ -585,10 +575,10 @@
         <v/>
       </c>
       <c r="S3" t="str">
-        <v>海水轻中型纺车</v>
+        <v/>
       </c>
       <c r="T3" t="str">
-        <v>小机身高扭矩 / 轻盐到近海兼顾 / 快速回收友好</v>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -613,14 +603,11 @@
       <c r="G4" t="str">
         <v/>
       </c>
-      <c r="H4" t="str">
-        <v>泛用,bass</v>
-      </c>
       <c r="I4" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="J4" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/LIN258HM_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_LIN258HM.jpg</v>
       </c>
       <c r="K4" t="str">
         <v>2026-04-21T12:02:55.901Z</v>
@@ -629,7 +616,7 @@
         <v>2026-04-21T12:02:55.901Z</v>
       </c>
       <c r="M4" t="str">
-        <v>高刚性BF/泛用</v>
+        <v/>
       </c>
       <c r="N4" t="str">
         <v>カヴァーフィネスゲームをはじめ、ラフウォーターでのバスボートゲームなど、激しい釣りに耐えうるタフな野外戦用スピニングがLIN258HMである。アルミメタル製のドライブギアは、超高精度マシンカットで「一個一個」「一歯一歯」の工程で歯面の最終仕上げを施すという念の入れ様。噛み合うピニオンギアのデジタル数値に、ドライブギアをミクロンの精度で適合させるという極みの技。リンのシームレスなシルキードライブは、これに加えてギアを支えるハウジングもたわみの発生しない高精度・高剛性のアルミメタル製なのだ。勘合部さえもすべて「一個一個」ミクロンの精度で削り出す。クラフツマンの魂を込めたこの丹念な工程こそが、リンのまるでガタのない強靭な駆動部分を造り出している。リンのハンドルを回せば「噛み合い接触」の感触よりも「スベリ接触」の感触が強めに出ていることが感じていただけると思う。このシルキーな噛み合いこそが、回せば瞬時に立ち上がるロスのないハイパワーと、高次元の感度伝達性を生み出すのだ。なお、メカハウジングとして、可動部には最新の磁性流体シールドで保護。極限の遠心力低減化を追求したローター部分はグラファイトコンポジット製。スプールも限界まで肉抜きされたハニカム構造で耐久性を両立。ハンドルは、最新のメカニカルパワーアシストを施し、もはやワンランク上の機種として使用可能なオーバーパワースペックを持つリールなのだ。世界記録バスのパワーランに耐え得るために、Ｍドラグシステムはスムーズで耐久性・耐力のある高荷重カーボンの多重構造を採用。卓越した追撃性能を具現化したLIN258HMは、バスフィッシングはもちろんのこと、シーバスゲームやノースエリアの巨大鱒族を相手にも存分に威力を発揮。その名のとおり、凛として戦うモンスタースペックのスピニングリールなのだ。 / The LIN258HM is a battle reel made to withstand tough and intense fishing. The aluminum gear drive is finished off by carefully machining each gear tooth with extreme precision. The extreme engineering skills employed allow the drive gear to be fitted to the pinion gear with only microns to spare. The seamless silky drive of the LIN is made of high-precision high-rigidity aluminum, which prevents deflection of the supporting gear housing. The precision manufacturing process combined with the soul of the craftsmen who assemble the product are what make the LIN what it is. This silky gear engagement of the LIN is what creates its sensitivity and creates the high power that engages immediately when turning the handle. Furthermore, in the mechanical housing, the moving parts are protected with the latest magnetic fluid shield. The rotor is made from lightweight graphite composites to reduce centrifugal force and increase stability. The spool also has also undergone weight reduction, implementing a durable honeycomb construction. The mechanical power assist of the handle gives it power equal to higher spec'd models. In order to withstand the power of world record size bass, the M drag system is incorporated with its multiple structured, smooth, durable, heavyweight carbon. The LIN258HM is a powerful spinning reel that shows excellent performance when dealing with bass, sea bass, and large trout species.</v>
@@ -647,10 +634,10 @@
         <v/>
       </c>
       <c r="S4" t="str">
-        <v>重视刚性的高端泛用</v>
+        <v/>
       </c>
       <c r="T4" t="str">
-        <v>金属机身 / 丝滑卷收 / 重视耐久与力量</v>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -675,14 +662,11 @@
       <c r="G5" t="str">
         <v/>
       </c>
-      <c r="H5" t="str">
-        <v>精细,泛用,bass</v>
-      </c>
       <c r="I5" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="J5" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/RC-IDATEN%20256_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_megabass_idaten-x_256.jpg</v>
       </c>
       <c r="K5" t="str">
         <v>2026-04-21T12:02:56.380Z</v>
@@ -691,7 +675,7 @@
         <v>2026-04-21T12:02:56.380Z</v>
       </c>
       <c r="M5" t="str">
-        <v>高速精细</v>
+        <v/>
       </c>
       <c r="N5" t="str">
         <v>「レーシングコンディション256」の軽量コンセプトとパッケージングレイアウトを踏襲し、ハンドル一回転におけるローター回転を高速化。ハンドル一巻きのライン巻き上げ量を大幅にアップした高速リールが、「IDATENプロジェクト」の最新形態として、遂に具現化。ハイスピードスピニングリールで痩せがちだった巻き上げトルクは、IDATEN256が過去のものとしています。「スピード」と「パワー」、この相反する要素の最大公約数にジャストミートさせた新たなIDATENが、効率よく釣り勝つためのハイテンポなフィネスゲームを展開します。 / RC-IDATEN 256 inherits the Racing Condition 256 model’s lightweight concept, while at the same time delivering faster rotor rotation per handle turn.RC-IDATEN 256 has been tuned for blazing speed without stripping away underlying power, bringing a new standard of high-speed gearing and power. Increased retrieve speed without the loss of lightness or power: this is the latest core incarnation of the IDATEN reel project.Experience the perfect combination of speed and power with the new IDATEN 256. / * The photograph is a prototype / もはやこれ以上はない堅牢さと軽量化を高次元で両立させた、メガバス独自のメタル削り出し構造による「ハイメタル・ハニカムスプール」は、「磁性流体シールドシステム」の開発によって、スピニングリールにおける理想的なヘッドバランスを実現。その超軽量マイクロボディが発揮してしまう、およそ似合わないハイパワーは、究極のフィネスアプローチでレコードフィッシュと真っ向からわたり合うためのエクストリームなスペック。</v>
@@ -709,10 +693,10 @@
         <v/>
       </c>
       <c r="S5" t="str">
-        <v>快节奏精细回收</v>
+        <v/>
       </c>
       <c r="T5" t="str">
-        <v>高速回收 / 精细与效率兼顾 / 轻量路亚友好</v>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -737,14 +721,11 @@
       <c r="G6" t="str">
         <v/>
       </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
       <c r="I6" t="str">
         <v>drum</v>
       </c>
       <c r="J6" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/MONOBLOCK%20SPECIALE%20GRIGIO%20STONE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_MONOBLOCK_SPECIALE_GRIGIO_STONE.jpg</v>
       </c>
       <c r="K6" t="str">
         <v>2026-04-21T12:02:57.077Z</v>
@@ -753,7 +734,7 @@
         <v>2026-04-21T12:02:57.077Z</v>
       </c>
       <c r="M6" t="str">
-        <v>高端收藏机</v>
+        <v/>
       </c>
       <c r="N6" t="str">
         <v>進化するモノブロック / An Evolving Monoblock.</v>
@@ -771,10 +752,10 @@
         <v/>
       </c>
       <c r="S6" t="str">
-        <v>重视造型与把玩的玩家</v>
+        <v/>
       </c>
       <c r="T6" t="str">
-        <v>Monoblock 进化版 / 收藏属性强 / 传统高端鼓轮美学</v>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -799,14 +780,11 @@
       <c r="G7" t="str">
         <v/>
       </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
       <c r="I7" t="str">
         <v>drum</v>
       </c>
       <c r="J7" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/MONOBLOCK%20SPECIALE%20ITO-GAMBLER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_MONOBLOCK_SPECIALE_ITO-GAMBLER.jpg</v>
       </c>
       <c r="K7" t="str">
         <v>2026-04-21T12:02:57.755Z</v>
@@ -815,7 +793,7 @@
         <v>2026-04-21T12:02:57.755Z</v>
       </c>
       <c r="M7" t="str">
-        <v>高端收藏机</v>
+        <v/>
       </c>
       <c r="N7" t="str">
         <v>進化するモノブロック / An Evolving Monoblock.</v>
@@ -833,10 +811,10 @@
         <v/>
       </c>
       <c r="S7" t="str">
-        <v>重视造型与把玩的玩家</v>
+        <v/>
       </c>
       <c r="T7" t="str">
-        <v>Monoblock 进化版 / 收藏属性强 / 传统高端鼓轮美学</v>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -861,14 +839,11 @@
       <c r="G8" t="str">
         <v/>
       </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
       <c r="I8" t="str">
         <v>drum</v>
       </c>
       <c r="J8" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/MONOBLOCK%20SPECIALE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_MONOBLOCK_SPECIALE.jpg</v>
       </c>
       <c r="K8" t="str">
         <v>2026-04-21T12:02:58.400Z</v>
@@ -877,7 +852,7 @@
         <v>2026-04-21T12:02:58.400Z</v>
       </c>
       <c r="M8" t="str">
-        <v>高性能旗舰鼓轮</v>
+        <v/>
       </c>
       <c r="N8" t="str">
         <v>スペチアーレとは、イタリア語で「特別」の意味。その名の通り、スペックアップされた数々の先進的スペシャルファンクションを満載された究極のハイパフォーマンスマシンです。 / ファストムービングルアーの引き抵抗と、カヴァーゲームのハイパワーファイトがもたらす高荷重ストレスを極限まで低減化させ、ストレスフリーを徹底追求した絶妙なギアユニットでセッティング。 / 堅牢素材の分子レベルでの結束構造を破壊させないため、あえて無垢の高強度アルミブロックから一品一品削り出す、超軽量・高剛性モノコックフレームとサイドプレートパーツ、ダイヤルユニットフレーム、ギアボックスとギアハウジングは圧巻。 / もはや悦楽の境地に至る「ゼロフリクション・シルキーハンドル・ドライビング」と極限まで同調最適化させた、究極のレベルワインド・セッティング。</v>
@@ -895,10 +870,10 @@
         <v/>
       </c>
       <c r="S8" t="str">
-        <v>高端快饵与重装</v>
+        <v/>
       </c>
       <c r="T8" t="str">
-        <v>高性能机体 / 高刚性与顺滑并重 / 旗舰鼓轮路线</v>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -923,14 +898,11 @@
       <c r="G9" t="str">
         <v/>
       </c>
-      <c r="H9" t="str">
-        <v>泛用,远投,bass</v>
-      </c>
       <c r="I9" t="str">
         <v>baitcasting</v>
       </c>
       <c r="J9" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/RHODIUM%2073_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_megabass_rhodium_73.jpg</v>
       </c>
       <c r="K9" t="str">
         <v>2026-04-21T12:02:59.044Z</v>
@@ -939,7 +911,7 @@
         <v>2026-04-21T12:02:59.044Z</v>
       </c>
       <c r="M9" t="str">
-        <v>高速泛用主力</v>
+        <v/>
       </c>
       <c r="N9" t="str">
         <v>持ち得るすべてのテクニックを駆使して「フルコンタクト」する釣り。突如として訪れる一瞬のビッグチャンスを確実に手繰り寄せる。近年のマルチプレイングスタイルのバスフィッシングにおいて、ワンチャンスをものにする強靭なメンタリティと、「果敢な攻め」は、欠かせない。新剛体マシン、ロジウムは、アイティオーエンジニアリングによる屈強な超軽量メタルフレームを基本骨格とし、圧巻の巻き上げトルクを瞬時に叩きだすシルキードライブフィールの超精密ギアレイアウトパッケージと、リールビルドにおける最先端テクノロジーをあますことなく導入。その上で、タフなフィールドを多様なメソッドで制するための、「特別なファインチューン」の数々を随所に施している。アキュラシーを大幅にアップさせつつバックラッシュを極限まで低減化させた、「AIRブレーキシステム」。超軽量インダクトローターと超軽量・超々ジュラルミンSVスプール「メガバスブランキングエディション」とのシンクロナイズによって、ピッチングでは驚異的な低弾道キャストを実現。カバーのより奥の奥へと伸びていくスキッピングは圧巻だ。その上、ロングディスタンスキャストでは、わずか４gの軽量ルアーをストレスフリーで投げ込むことができるマルチプレイングパフォーマンスは、ストレスフリーの「フルコンタクト・バスフィッシング」を高次元で実現させている。デストロイヤーシリーズ、ヴァルキリーシリーズ、あらゆるロッドへの優れたマッチ・ザ・バランスも、ロジウムの多様なパフォーマンスのひとつである。 / ※The photograph is a prototype. / TシェイプレベルワインドがクラッチON・OFFに応じて半回転する「ターンアラウンドスタイル」のTWSを採用。キャスティング時にはレベルワインドが前方に回転し、ラインはTシェイプレベルワインドの幅広部を通ってスムーズに放出される。リトリーブ時にはレベルワインドが後ろ方向に倒れる形で半回転し、レベルワインド下部の溝にラインが誘導され、タイトかつ平行に巻き取られる。飛距離アップ＆トラブルフリーの特長はそのままに、タフさにもこだわる。 / 従来通りのルアーが使える事は当然として、軽量ルアーをもストレスなく投げることができ、しかもスプール強度も犠牲にしない。それが次世代のバーサタイル。メガバスのベイトリールはマグネット式のブレーキシステムを採用している。十分な耐久性はもちろん、瞬時にブレーキ設定が可能な外部調整ダイヤル、天候に左右されない安定したブレーキ力。ピンスポット値に調整できない限り最高出力を発揮しない、また時に意図に反する出力を生む他のシステムとは大きく異なり、マグネット式ブレーキならではの実戦メリットを最大限に引き出したSVは、最小限のマグダイヤルの調整だけで4g前後の軽量リグから重量級ルアーまでを文字通りストレスフリーで扱える。スプールを交換したり、サイドプレートを開けたりして、セッティングに時間を掛ける事もない。ルアーの守備範囲が一番広いSVは、陸っぱりからボートまでスタイルやフィールドを選ばない。マグネット式ブレーキの有効性を極限まで高めたSVコンセプトは、まさにバーサタイルリールの新スタンダードなのである。</v>
@@ -957,10 +929,10 @@
         <v/>
       </c>
       <c r="S9" t="str">
-        <v>鲈鱼泛用与快饵</v>
+        <v/>
       </c>
       <c r="T9" t="str">
-        <v>高速比 / 低弹道操控 / Cover 游戏友好</v>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -985,14 +957,11 @@
       <c r="G10" t="str">
         <v/>
       </c>
-      <c r="H10" t="str">
-        <v>泛用,远投,bass</v>
-      </c>
       <c r="I10" t="str">
         <v>baitcasting</v>
       </c>
       <c r="J10" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/RHODIUM%2081_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_RHODIUM_81.jpg</v>
       </c>
       <c r="K10" t="str">
         <v>2026-04-21T12:02:59.672Z</v>
@@ -1001,7 +970,7 @@
         <v>2026-04-21T12:02:59.672Z</v>
       </c>
       <c r="M10" t="str">
-        <v>超高速泛用主力</v>
+        <v/>
       </c>
       <c r="N10" t="str">
         <v>持ち得るすべてのテクニックを駆使して「フルコンタクト」する釣り。突如として訪れる一瞬のビッグチャンスを確実に手繰り寄せる。近年のマルチプレイングスタイルのバスフィッシングにおいて、ワンチャンスをものにする強靭なメンタリティと、「果敢な攻め」は、欠かせない。新剛体マシン、ロジウムは、アイティオーエンジニアリングによる屈強な超軽量メタルフレームを基本骨格とし、圧巻の巻き上げトルクを瞬時に叩きだすシルキードライブフィールの超精密ギアレイアウトパッケージと、リールビルドにおける最先端テクノロジーをあますことなく導入。その上で、タフなフィールドを多様なメソッドで制するための、「特別なファインチューン」の数々を随所に施している。アキュラシーを大幅にアップさせつつバックラッシュを極限まで低減化させた、「AIRブレーキシステム」。超軽量インダクトローターと超軽量・超々ジュラルミンSVスプール「メガバスブランキングエディション」とのシンクロナイズによって、ピッチングでは驚異的な低弾道キャストを実現。カバーのより奥の奥へと伸びていくスキッピングは圧巻だ。その上、ロングディスタンスキャストでは、わずか４gの軽量ルアーをストレスフリーで投げ込むことができるマルチプレイングパフォーマンスは、ストレスフリーの「フルコンタクト・バスフィッシング」を高次元で実現させている。デストロイヤーシリーズ、ヴァルキリーシリーズ、あらゆるロッドへの優れたマッチ・ザ・バランスも、ロジウムの多様なパフォーマンスのひとつである。 / ※The photograph is a prototype. / TシェイプレベルワインドがクラッチON・OFFに応じて半回転する「ターンアラウンドスタイル」のTWSを採用。キャスティング時にはレベルワインドが前方に回転し、ラインはTシェイプレベルワインドの幅広部を通ってスムーズに放出される。リトリーブ時にはレベルワインドが後ろ方向に倒れる形で半回転し、レベルワインド下部の溝にラインが誘導され、タイトかつ平行に巻き取られる。飛距離アップ＆トラブルフリーの特長はそのままに、タフさにもこだわる。 / 従来通りのルアーが使える事は当然として、軽量ルアーをもストレスなく投げることができ、しかもスプール強度も犠牲にしない。それが次世代のバーサタイル。メガバスのベイトリールはマグネット式のブレーキシステムを採用している。十分な耐久性はもちろん、瞬時にブレーキ設定が可能な外部調整ダイヤル、天候に左右されない安定したブレーキ力。ピンスポット値に調整できない限り最高出力を発揮しない、また時に意図に反する出力を生む他のシステムとは大きく異なり、マグネット式ブレーキならではの実戦メリットを最大限に引き出したSVは、最小限のマグダイヤルの調整だけで4g前後の軽量リグから重量級ルアーまでを文字通りストレスフリーで扱える。スプールを交換したり、サイドプレートを開けたりして、セッティングに時間を掛ける事もない。ルアーの守備範囲が一番広いSVは、陸っぱりからボートまでスタイルやフィールドを選ばない。マグネット式ブレーキの有効性を極限まで高めたSVコンセプトは、まさにバーサタイルリールの新スタンダードなのである。</v>
@@ -1019,10 +988,10 @@
         <v/>
       </c>
       <c r="S10" t="str">
-        <v>快节奏鲈鱼路亚</v>
+        <v/>
       </c>
       <c r="T10" t="str">
-        <v>更高回收速度 / 快节奏搜索 / 快饵友好</v>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1047,14 +1016,11 @@
       <c r="G11" t="str">
         <v/>
       </c>
-      <c r="H11" t="str">
-        <v>泛用,强力,bass</v>
-      </c>
       <c r="I11" t="str">
         <v>baitcasting</v>
       </c>
       <c r="J11" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/RHODIUM%2063_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_RHODIUM_63.jpg</v>
       </c>
       <c r="K11" t="str">
         <v>2026-04-21T12:03:00.367Z</v>
@@ -1063,7 +1029,7 @@
         <v>2026-04-21T12:03:00.367Z</v>
       </c>
       <c r="M11" t="str">
-        <v>低速扭矩主力</v>
+        <v/>
       </c>
       <c r="N11" t="str">
         <v>持ち得るすべてのテクニックを駆使して「フルコンタクト」する釣り。突如として訪れる一瞬のビッグチャンスを確実に手繰り寄せる。近年のマルチプレイングスタイルのバスフィッシングにおいて、ワンチャンスをものにする強靭なメンタリティと、「果敢な攻め」は、欠かせない。新剛体マシン、ロジウムは、アイティオーエンジニアリングによる屈強な超軽量メタルフレームを基本骨格とし、圧巻の巻き上げトルクを瞬時に叩きだすシルキードライブフィールの超精密ギアレイアウトパッケージと、リールビルドにおける最先端テクノロジーをあますことなく導入。その上で、タフなフィールドを多様なメソッドで制するための、「特別なファインチューン」の数々を随所に施している。アキュラシーを大幅にアップさせつつバックラッシュを極限まで低減化させた、「AIRブレーキシステム」。超軽量インダクトローターと超軽量・超々ジュラルミンSVスプール「メガバスブランキングエディション」とのシンクロナイズによって、ピッチングでは驚異的な低弾道キャストを実現。カバーのより奥の奥へと伸びていくスキッピングは圧巻だ。その上、ロングディスタンスキャストでは、わずか４gの軽量ルアーをストレスフリーで投げ込むことができるマルチプレイングパフォーマンスは、ストレスフリーの「フルコンタクト・バスフィッシング」を高次元で実現させている。デストロイヤーシリーズ、ヴァルキリーシリーズ、あらゆるロッドへの優れたマッチ・ザ・バランスも、ロジウムの多様なパフォーマンスのひとつである。 / ※The photograph is a prototype. / TシェイプレベルワインドがクラッチON・OFFに応じて半回転する「ターンアラウンドスタイル」のTWSを採用。キャスティング時にはレベルワインドが前方に回転し、ラインはTシェイプレベルワインドの幅広部を通ってスムーズに放出される。リトリーブ時にはレベルワインドが後ろ方向に倒れる形で半回転し、レベルワインド下部の溝にラインが誘導され、タイトかつ平行に巻き取られる。飛距離アップ＆トラブルフリーの特長はそのままに、タフさにもこだわる。 / 従来通りのルアーが使える事は当然として、軽量ルアーをもストレスなく投げることができ、しかもスプール強度も犠牲にしない。それが次世代のバーサタイル。メガバスのベイトリールはマグネット式のブレーキシステムを採用している。十分な耐久性はもちろん、瞬時にブレーキ設定が可能な外部調整ダイヤル、天候に左右されない安定したブレーキ力。ピンスポット値に調整できない限り最高出力を発揮しない、また時に意図に反する出力を生む他のシステムとは大きく異なり、マグネット式ブレーキならではの実戦メリットを最大限に引き出したSVは、最小限のマグダイヤルの調整だけで4g前後の軽量リグから重量級ルアーまでを文字通りストレスフリーで扱える。スプールを交換したり、サイドプレートを開けたりして、セッティングに時間を掛ける事もない。ルアーの守備範囲が一番広いSVは、陸っぱりからボートまでスタイルやフィールドを選ばない。マグネット式ブレーキの有効性を極限まで高めたSVコンセプトは、まさにバーサタイルリールの新スタンダードなのである。</v>
@@ -1081,10 +1047,10 @@
         <v/>
       </c>
       <c r="S11" t="str">
-        <v>卷阻饵与扭矩取向</v>
+        <v/>
       </c>
       <c r="T11" t="str">
-        <v>低速高扭矩 / 卷阻饵稳定 / 力量感突出</v>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -1109,14 +1075,11 @@
       <c r="G12" t="str">
         <v/>
       </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
       <c r="I12" t="str">
         <v>drum</v>
       </c>
       <c r="J12" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/Pagani%20R100_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_Pagani_R100-1.jpg</v>
       </c>
       <c r="K12" t="str">
         <v>2026-04-21T12:03:00.881Z</v>
@@ -1125,7 +1088,7 @@
         <v>2026-04-21T12:03:00.881Z</v>
       </c>
       <c r="M12" t="str">
-        <v>复古高端鼓轮</v>
+        <v/>
       </c>
       <c r="N12" t="str">
         <v>スプールのリムひとつでさえ、すべて職人の手組みで制作。全ユニットをパーツ単体に細胞分解できてしまう究極のピラードリールが実現しました。R100は、オトナのトップウォータープラッガーのためだけに開発。 モノブロックよりもコンパクトかつ重厚なボディと、手書きのスケッチからそのまま起こしたデザインがもたらす圧倒的な美は、CAD/CAMで設計される最新のリールでは味わえないフィッシングハイをもたらします。 気持ちよくロングキャストできるクワトロサーボブレーキを搭載しています。 / Everything down to the spool rim is hand assembled by our expert craftsmen. The R100 was developed only for mature top water pluggers. It sports a body that is thicker and more compact than that of the Monoblock, and the design is taken from hand drawn sketches, resulting in a stunningly beautiful product that surpasses the elegance of the latest CAD/CAM designed reels. It features a quatro servo brake that allows for comfortable, long distance casting.</v>
@@ -1143,10 +1106,10 @@
         <v/>
       </c>
       <c r="S12" t="str">
-        <v>顶水与风格玩家</v>
+        <v/>
       </c>
       <c r="T12" t="str">
-        <v>复古机体 / 顶水友好 / 造型与手感并重</v>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1171,14 +1134,11 @@
       <c r="G13" t="str">
         <v/>
       </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
       <c r="I13" t="str">
         <v>drum</v>
       </c>
       <c r="J13" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/Pagani%20P200_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_Pagani_P200_black-chrome.jpg</v>
       </c>
       <c r="K13" t="str">
         <v>2026-04-21T12:03:01.354Z</v>
@@ -1187,7 +1147,7 @@
         <v>2026-04-21T12:03:01.354Z</v>
       </c>
       <c r="M13" t="str">
-        <v>复古高端鼓轮</v>
+        <v/>
       </c>
       <c r="N13" t="str">
         <v>メガバスリールは、現時点で考えうる最先端・工業技術を終結して製作しています。熟練のファクトリーマイスターが持てる技を駆使し、精巧に作り上げていくリールです。レースに勝つために凌ぎを削ってきた元レーシングエンジニアが在籍するメガバス・リールファクトリーの生産規模は、決して大きくありません。 マグネシウム、超々ジュラルミン、チタン、モリブデン、ハイエンドアルミニウム、カーボングラファイト、カーボンコンポジットマテリアル、ハイブリッドABSなどなど、あらゆる素材を導入し、大メーカーとは異なる、ガレージファクトリーならではの「ワンメイク」アプローチが頻発します。 フィールドに設計室を置き、実戦検証型の設計手法と大胆なチューニングメニューを即時編み出しながら、高度な新素材加工ノウハウの数々を大胆に注ぎ込むメガバス・リールファクトリーのスタッフは言います。「釣果が先。図面は、あと」だと。したがって、もう２度と作らないモデルや、使い手に一定以上の技量レベルを要求するピーキーなモデルさえ存在します。これは、メーカーを名乗るものとしてはどうかと思いますが、「絶対釣果」をたたき出すために、マーケティングを無視したマイスターたちのわがままでモノづくりがなされている、ガレージファクトリーならではの現場感覚です。 そんな「スペック至上主義」を主張するレースエンジニアが腕をふるう一方で、メガバス・リールファクトリーには、芸術性を深く追求するアーチストがいます。 彼らはいいます。「感動が先。図面は、あと」ここで彼らも、設計図があとになってしまうのですが、スケッチブックを手に絵を描き、美的主観を優先し、何度もモデリングします。彼らにとって作りたいのは、リールの姿をした「芸術作品」だからです。手にすればオーラを放ち、数学的に割り切れぬ交錯する微妙な直状線と、微妙な曲線が織り成す、「数奇屋づくり」の伝統美学がもたらす重厚な存在感。これらは、大人の休日において、質の高いフィッシングプレジャーを提供してくれると確信しているからです。ファクトリーのアーチストたちが直視するのは、レースエンジニアたちが重視する数学的なパフォーマンス・スペックではなく、官能的な感性スペックです。こうして、ISシリーズとは対極的ともいえる「パガーニリール」が誕生しました。 P200にいける、左右で異なる真円形と楕円形を、たった４本のピラーで連結し、異形構造がひとつの集合体を目指したときに見せる結合美は、建築構造物の美学に共通するものです。これらは、あなたの釣果を直接的に向上させるものではありませんが、手にしたあなたの心を躍らせ、フィッシングのモチベーションを大いに上げてくれる、重要なメンタリティのエレメントです。ファクトリーのアーチストたちは、パガーニリールの開発と製作を通じて、美の探究と表現に取り組んでいます。 / The Pagani P200 is a downsized model of the immensely popular Pagani Reel flagship model, the P300. Under its nostalgic stylings, the P200 incorporates various high tech elements such as a high gear, infinite mechanism, silky drive unit, and quatro servo brake. It's a light plugging model combining beauty and utility, and fully realizing the potential of modern tops.</v>
@@ -1205,10 +1165,10 @@
         <v/>
       </c>
       <c r="S13" t="str">
-        <v>顶水与风格玩家</v>
+        <v/>
       </c>
       <c r="T13" t="str">
-        <v>P300 缩小版 / 轻插饵友好 / 兼顾美感与实用</v>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1233,14 +1193,11 @@
       <c r="G14" t="str">
         <v/>
       </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
       <c r="I14" t="str">
         <v>drum</v>
       </c>
       <c r="J14" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/Pagani%20P300_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_Pagani_P300_01_CHAMPAGNE_GOLD.jpg</v>
       </c>
       <c r="K14" t="str">
         <v>2026-04-21T12:03:01.851Z</v>
@@ -1249,7 +1206,7 @@
         <v>2026-04-21T12:03:01.851Z</v>
       </c>
       <c r="M14" t="str">
-        <v>复古高端鼓轮</v>
+        <v/>
       </c>
       <c r="N14" t="str">
         <v>メガバス・モダンリールの雄、モノブロックとは対極的な、伝統的なリールづくりの製法にこだわって仕上げていく、パガーニのトラディショナルリール。日本の名工が丹念に作り上げていく、古き良き時代のモノづくりが、ソウルフルなプロダクツを目指すアイティオーエンジニアリングによって、現代に蘇ります。 パガーニP300は、音楽に例えると・・・jazz（ジャズ）のような感覚。使い手の感性よって、様々な表情をみせ、いつも異なるフィーリングで楽しませてくれる、 そんな、楽しいキカイです。クルマに例えたら・・・キャブレター時代のスポーツカーのようです。 / Unlike our modern reel, the Monoblock, the Pagani is built focusing on the process of authentic, traditional reel building. The masterful Japanese craftwork from years past is brought back to life by ITO ENGINEERING. If it were music, the Pagani would be jazz. If it were a car, it would be an old hot rod. Pagani P300 is an enjoyable tool that will deliver various experiences in response to each unique user, offering them an expressive and dynamic range of performance.</v>
@@ -1267,10 +1224,10 @@
         <v/>
       </c>
       <c r="S14" t="str">
-        <v>大尺寸顶水与风格玩家</v>
+        <v/>
       </c>
       <c r="T14" t="str">
-        <v>Pagani 旗舰尺寸 / 风格化机体 / 复古鼓轮体验</v>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1295,14 +1252,11 @@
       <c r="G15" t="str">
         <v/>
       </c>
-      <c r="H15" t="str">
-        <v>精细,bass</v>
-      </c>
       <c r="I15" t="str">
         <v>baitcasting</v>
       </c>
       <c r="J15" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/LAUDA58_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_LAUDA_58.jpg</v>
       </c>
       <c r="K15" t="str">
         <v>2026-04-21T12:03:02.339Z</v>
@@ -1311,7 +1265,7 @@
         <v>2026-04-21T12:03:02.339Z</v>
       </c>
       <c r="M15" t="str">
-        <v>低速泛用主力</v>
+        <v/>
       </c>
       <c r="N15" t="str">
         <v>バーサタイルシリーズ「Lauda」のローギアモデル、Lauda58。 / ギア比5.8：1のローギアだからこそできるリズミカルなリーリングによって、アクションの安定性やレンジキープの正確性が向上。意識してゆっくり巻くのとは一味違う生き生きしたルアーアクションを生み出します。 / さらに、パワーライトコルク・ラウンドノブを採用し、ディープクランクなどの引き抵抗の強いルアーでも、シルキーで軽やかなリーリングが可能。 / SVコンセプトが実現したのは、ライト〜ヘビーファストムービングまで快適に使用可能な対応力と、アゲインストでのロングキャスト。</v>
@@ -1329,10 +1283,10 @@
         <v/>
       </c>
       <c r="S15" t="str">
-        <v>卷阻饵与稳定检索</v>
+        <v/>
       </c>
       <c r="T15" t="str">
-        <v>5.8 低速比 / 深潜饵友好 / 扭矩导向</v>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -1357,14 +1311,11 @@
       <c r="G16" t="str">
         <v/>
       </c>
-      <c r="H16" t="str">
-        <v>精细,bass</v>
-      </c>
       <c r="I16" t="str">
         <v>baitcasting</v>
       </c>
       <c r="J16" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/LAUDA72_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_LAUDA_72.jpg</v>
       </c>
       <c r="K16" t="str">
         <v>2026-04-21T12:03:02.843Z</v>
@@ -1373,7 +1324,7 @@
         <v>2026-04-21T12:03:02.843Z</v>
       </c>
       <c r="M16" t="str">
-        <v>高速泛用主力</v>
+        <v/>
       </c>
       <c r="N16" t="str">
         <v>7.2：1のハイギア・バーサタイルモデルLauda72。 / 超々ジュラルミン製軽量SVスプールのなめらかな初動により、低弾道で伸びのあるピッチングが可能。高次元のショートディスタンスゲームにはもちろん、強風下のロングキャストにおいても快適なキャストフィールを実現。 / また、高密度カーボンコンポジットマテリアルによる高感度ノブを搭載し、軽量かつ高感度にセッティング。 / 手返しの良さと水中の解像度を高めた「スピーディー」なバーサタイルモデルです。</v>
@@ -1391,10 +1342,10 @@
         <v/>
       </c>
       <c r="S16" t="str">
-        <v>全能快节奏鲈鱼</v>
+        <v/>
       </c>
       <c r="T16" t="str">
-        <v>7.2 高速比 / 远投与短打兼顾 / 高感度设定</v>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -1419,14 +1370,11 @@
       <c r="G17" t="str">
         <v/>
       </c>
-      <c r="H17" t="str">
-        <v>精细,bass</v>
-      </c>
       <c r="I17" t="str">
         <v>baitcasting</v>
       </c>
       <c r="J17" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/LAUDA72%20LIMITED%20EDITION_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_LAUDA_72_LIMITED-EDITION.jpg</v>
       </c>
       <c r="K17" t="str">
         <v>2026-04-21T12:03:03.499Z</v>
@@ -1435,7 +1383,7 @@
         <v>2026-04-21T12:03:03.499Z</v>
       </c>
       <c r="M17" t="str">
-        <v>限量高速泛用</v>
+        <v/>
       </c>
       <c r="N17" t="str">
         <v>特別なアングラーに向けて開発された限定生産のリミテッドエディション。超軽量80mmカーボンハンドルを標準装備した上で、細部に渡るトータルウェイトバランシングを煮詰めたスペシャルモデルです。 / ギアハウジングには３層コートによる特殊ペイント、「富士レーシングホワイト」を大胆にあしらっています。 / The LAUDA 72 Limited Edition is inspired by the legendary Fuji Speedway in nearby Oyama, featuring a gear housing side-cover finished in three coats of the iconic Fuji Racing White. / In addition, this limited edition is equipped with a custom 80mm carbon fiber handle, reducing off-axis weight to improve the reel’s overall performance.</v>
@@ -1453,10 +1401,10 @@
         <v/>
       </c>
       <c r="S17" t="str">
-        <v>高端轻量收藏实战</v>
+        <v/>
       </c>
       <c r="T17" t="str">
-        <v>限量版本 / 80mm 碳手柄 / 轻量高感度</v>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -1481,14 +1429,11 @@
       <c r="G18" t="str">
         <v/>
       </c>
-      <c r="H18" t="str">
-        <v>泛用,强力,bass</v>
-      </c>
       <c r="I18" t="str">
         <v>baitcasting</v>
       </c>
       <c r="J18" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/IP79_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_IP79.jpg</v>
       </c>
       <c r="K18" t="str">
         <v>2026-04-21T12:03:04.131Z</v>
@@ -1497,7 +1442,7 @@
         <v>2026-04-21T12:03:04.131Z</v>
       </c>
       <c r="M18" t="str">
-        <v>高功率主力</v>
+        <v/>
       </c>
       <c r="N18" t="str">
         <v>ストイックなリアルアングラーに絶賛の、IS（インターセプティング・スピーダー）シリーズに対し、パワープレイングゲームに対応しながら「快適な巻き上げトルク」を実現すべくスペックアップを施したスペシャルリールが、IP（インターセプティング・パワーズ）シリーズです。クランクベイトのハイピッチリトリーブ、ジグのマシンガンショットを実現する7.9のハイギアリールでありながら、「巻き重り」疲労感を軽減化。100mmにおよぶロング・パワーハンドルと、超軽量・超々ジュラルミンを大胆にも使用した「大口径ナロースプール」が、強大なトルクを発揮。軽量ルアーのフルキャストにおけるバックラッシュをとことん低減化させるために開発された「マグネットブレーキユニット」と、その絶妙な調律は、プロガイドたちを唸らせた至高のセッティング。高剛性・高剛性のフルメタル ハウジングボディ（※サイドプレートを除く）に密かに封じ込めた新感覚スペックが、快適なハイスピード・ハイパワープレイングゲームを実現させています。 / In contrast to the IS(Intercepting Speeder) series, popular with reserved, practical anglers, the IP(Intercepting Power) series has been improved with increased winding torque, allowing it to excel during high power struggles with big fish. The high 7.9 gear ratio allows for speedy crank bait retrieves and machine gun shots with jigs while alleviating much of the fatigue from use. The newly designed 100mm long power handle and uniquely designed large diameter narrow spool, which uses ample amounts of lightweight super duralumin, generate massive amounts of torque. To reduce the backlash from the full power casting of lightweight lures, an improved magnetic braking unit has been incorporated and tuned to the settings demanded by our exacting Pro Guides. The new performance contained in this high rigidity full metal housing(*not including the side plate) will help you realize comfortable high speed and high power games.</v>
@@ -1515,10 +1460,10 @@
         <v/>
       </c>
       <c r="S18" t="str">
-        <v>Power Fishing 主力</v>
+        <v/>
       </c>
       <c r="T18" t="str">
-        <v>大口径窄线杯 / 强扭矩 / 快节奏 power game</v>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1543,14 +1488,11 @@
       <c r="G19" t="str">
         <v/>
       </c>
-      <c r="H19" t="str">
-        <v>泛用,强力,bass</v>
-      </c>
       <c r="I19" t="str">
         <v>baitcasting</v>
       </c>
       <c r="J19" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/IP68_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_IP68.jpg</v>
       </c>
       <c r="K19" t="str">
         <v>2026-04-21T12:03:04.627Z</v>
@@ -1559,7 +1501,7 @@
         <v>2026-04-21T12:03:04.627Z</v>
       </c>
       <c r="M19" t="str">
-        <v>高功率主力</v>
+        <v/>
       </c>
       <c r="N19" t="str">
         <v>デビューと同時に全国のビッグゲーマーをまたたく間に虜にしてしまったIPシリーズに、待望の6.8:1ギアモデルが登場。ド級のウルトラトルクがカヴァーモンスターをヘヴィカヴァーから引き剥がし、ウィードカットやハングオフカットを多用するカヴァークランキングで快適性能を発揮。マットカヴァーのフロッグゲームやスピナーベイティングなど、手返しと巻き上げパワーを両立させたい場面でストレスフリーなパワープレイングゲームを実現します。 / At the same time that the L/R debuted, the IP series also captivated the hearts of big-time anglers from around the country. Now a much anticipated 6:8 gear ratio model is added to the lineup. The ultra high torque pulls monsters out of cover and rips through weeds, making this the perfect reel for cover cranking. Whether attacking cover with frogs or spinner baits, this reel will give you the power you require to make stress-free power fishing a reality.</v>
@@ -1577,10 +1519,10 @@
         <v/>
       </c>
       <c r="S19" t="str">
-        <v>Power Fishing 扭矩取向</v>
+        <v/>
       </c>
       <c r="T19" t="str">
-        <v>6.8 低一档速度 / 更强卷阻承受 / Cover 与 power bait 友好</v>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1592,7 +1534,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AS3"/>
+  <dimension ref="A1:AS5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1784,10 +1726,10 @@
         <v>6/1</v>
       </c>
       <c r="R2" t="str">
-        <v>高密度碳纤复合</v>
+        <v/>
       </c>
       <c r="S2" t="str">
-        <v>磁性流体密封 / X-GRAPHITE 复合转子</v>
+        <v/>
       </c>
       <c r="T2" t="str">
         <v/>
@@ -1796,7 +1738,7 @@
         <v/>
       </c>
       <c r="V2" t="str">
-        <v>淡水路亚</v>
+        <v/>
       </c>
       <c r="W2" t="str">
         <v/>
@@ -1826,16 +1768,16 @@
         <v/>
       </c>
       <c r="AF2" t="str">
-        <v>溪流,精细,轻量</v>
+        <v/>
       </c>
       <c r="AG2" t="str">
-        <v>约 2g+</v>
+        <v/>
       </c>
       <c r="AH2" t="str">
         <v/>
       </c>
       <c r="AI2" t="str">
-        <v>单摇臂</v>
+        <v/>
       </c>
       <c r="AJ2" t="str">
         <v/>
@@ -1844,7 +1786,7 @@
         <v>spinning</v>
       </c>
       <c r="AL2" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="AM2" t="str">
         <v/>
@@ -1853,10 +1795,10 @@
         <v>その名のとおり、あらゆるものを引き付けてしまう魔性を発揮する、スーパーコンパクトリールが、ついにベールを脱ぎました。 ガウスは、見た目のコンパクトな風貌からは想像できない強靭さと、これまでの基準を覆すハイパワーをスモールボディで発揮する、新世代のスピニングマシンとして開発されています。LIN258HMで高い評価を得た「磁性流体シールドシステム」を、そのコンパクトボディに搭載。大切なギアユニット内部をクリーンな状態に保つだけでなく、ボディとローターは実質無接点のため、シルキーな回転性能が長期間持続。羽の軽さとも評される「X-GRAPHITE COMPSITEROTER」は、スピニングリールにおける回転レスポンスを格段に引き上げると同時に、感度感知にも貢献。また、ハイパワーゲームにおいてローターの変形を抑えるため、ビッグフィッシュのファイトによる負荷をローター全体に分散するために開発した。「高密度カーボンコンポジットボディ」は、恐るべき軽さを実現しただけでなく、ついにその剛性は、マグネシウムを上回るレベルへと昇華。モンスターフィッシュとのドッグファイトでも、ボディのタワミがないから、ギア間が正確に噛み合うシルキーな回転性能と、それらが相まって生み出すトルクフルな巻き上げ性能が確実に維持されます。すべてが、いままでのスピニングリールの基準を覆すオーバースペックリール、GAUSが、いよいよスピニング新時代への扉を開きます。 The "High Metal Honeycomb Spool" embodies the ultimate in robust and lightweight construction, made possible with Megabass' original carved metal manufacturing process. With the development of the "Magnetic Fluid Shield System," it creates the ideal head balance for spinning reels. The unlikely power generated from the super lightweight micro body gives it the extreme specs needed to combat record breaking fish with the ultimate finesse approach. The perpendicular 45mm crank handle excels at maintaining a steady and constant high speed retrieve with just a slight snapping motion of the wrist. This small superstar displays great ease of use with fast paced finesse rigs and light plugging in streams. もはやこれ以上はない堅牢さと軽量化を高次元で両立させた、メガバス独自のメタル削り出し構造による「ハイメタル・ハニカムスプール」は、「磁性流体シールドシステム」の開発によって、スピニングリールにおける理想的なヘッドバランスを実現。その超軽量マイクロボディが発揮してしまう、およそ似合わないハイパワーは、究極のフィネスアプローチでレコードフィッシュと真っ向からわたり合うためのエクストリームなスペック。45mmの垂直クランクハンドルは、手首のわずかなスナップモーションで、ブレなく一定スピードを保持した高速リーリングに最適。フィネスリグの素早いピックアップや、ストリームにおけるライトプラッギングで至極の快適性能を発揮する、小さな超新星です。</v>
       </c>
       <c r="AO2" t="str">
-        <v>溪流 / 轻量精细</v>
+        <v/>
       </c>
       <c r="AP2" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="AQ2" t="str">
         <v/>
@@ -1921,10 +1863,10 @@
         <v>6/1</v>
       </c>
       <c r="R3" t="str">
-        <v>高密度碳纤复合</v>
+        <v/>
       </c>
       <c r="S3" t="str">
-        <v>磁性流体密封 / 高扭矩小机身</v>
+        <v/>
       </c>
       <c r="T3" t="str">
         <v/>
@@ -1933,7 +1875,7 @@
         <v/>
       </c>
       <c r="V3" t="str">
-        <v>淡海水泛用</v>
+        <v/>
       </c>
       <c r="W3" t="str">
         <v/>
@@ -1963,16 +1905,16 @@
         <v/>
       </c>
       <c r="AF3" t="str">
-        <v>轻盐,快收,泛用</v>
+        <v/>
       </c>
       <c r="AG3" t="str">
-        <v>约 5g+</v>
+        <v/>
       </c>
       <c r="AH3" t="str">
         <v/>
       </c>
       <c r="AI3" t="str">
-        <v>单摇臂</v>
+        <v/>
       </c>
       <c r="AJ3" t="str">
         <v/>
@@ -1981,7 +1923,7 @@
         <v>spinning</v>
       </c>
       <c r="AL3" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="AM3" t="str">
         <v/>
@@ -1990,10 +1932,10 @@
         <v>その名のとおり、あらゆるものを引き付けてしまう魔性を発揮する、スーパーコンパクトリールが、ついにベールを脱ぎました。 ガウスは、見た目のコンパクトな風貌からは想像できない強靭さと、これまでの基準を覆すハイパワーをスモールボディで発揮する、新世代のスピニングマシンとして開発されています。LIN258HMで高い評価を得た「磁性流体シールドシステム」を、そのコンパクトボディに搭載。大切なギアユニット内部をクリーンな状態に保つだけでなく、ボディとローターは実質無接点のため、シルキーな回転性能が長期間持続。羽の軽さとも評される「X-GRAPHITE COMPSITEROTER」は、スピニングリールにおける回転レスポンスを格段に引き上げると同時に、感度感知にも貢献。また、ハイパワーゲームにおいてローターの変形を抑えるため、ビッグフィッシュのファイトによる負荷をローター全体に分散するために開発した。「高密度カーボンコンポジットボディ」は、恐るべき軽さを実現しただけでなく、ついにその剛性は、マグネシウムを上回るレベルへと昇華。モンスターフィッシュとのドッグファイトでも、ボディのタワミがないから、ギア間が正確に噛み合うシルキーな回転性能と、それらが相まって生み出すトルクフルな巻き上げ性能が確実に維持されます。すべてが、いままでのスピニングリールの基準を覆すオーバースペックリール、GAUSが、いよいよスピニング新時代への扉を開きます。 The GAUS30X is a model tuned for active salt water games. The GAUS's solid high rigidity body and instantaneous torque generation will handle big fish with ease. Megabass' unique "Super Lightweight Carbon Hybrid Spool" reduces spool deflection by spreading out the massive weight loads that can occur during heavy line use. The GAUS is equipped with many cutting edge technologies and features to give it the edge in high power games, such as the magnetic fluid system, the powerful 55m machine cut handle, the design that allows for smooth initial rotation and control, the M Drag System, the high power gear system, etc. Once you use it, you won't be able to put it down. That's the power of the GAUS. ガウス30Xは、シーバスゲームをはじめ、アクティブなソルトゲームにアジャストするモデルです。ガウスが身につけた圧倒的な高剛性ボディと、瞬時に太いトルクを立ち上げるシルキードライブフィールがビッグフィッシュゲームを快適にこなします。メガバス独自の「超軽量カーボン・ハイブリットスプール」は、太いラインにかかる多大な負荷がもたらすスプールのたわみや高荷重を分散して低減化。磁性流体システム、55mmの強靭なマシンカットハンドル、緻密に計算されたスムースな滑り出しとその制御について、徹底追及されたＭドラグシステム、ハイパワーギアシステムなどなど・・数え上げたらキリがありませんが、スピニングリールにおける新次元のハイパワーゲームは、ガウスが武装した最新テクノロジーによって、ついに具現化。一度お使いいただくと、手放せなくなる快適性能こそが、ガウスの魔力を物語ります。</v>
       </c>
       <c r="AO3" t="str">
-        <v>轻盐 / 近海轻中型</v>
+        <v/>
       </c>
       <c r="AP3" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="AQ3" t="str">
         <v/>
@@ -2002,20 +1944,293 @@
         <v/>
       </c>
       <c r="AS3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>MRED50002</v>
+      </c>
+      <c r="B4" t="str">
+        <v>MRE5002</v>
+      </c>
+      <c r="C4" t="str">
+        <v>LIN258HM</v>
+      </c>
+      <c r="D4" t="str">
+        <v>6.0</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>7.0</v>
+      </c>
+      <c r="G4" t="str">
+        <v>248</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v>6lb./210m / 8lb/150m</v>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v>91</v>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v>12/1</v>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
+        <v/>
+      </c>
+      <c r="U4" t="str">
+        <v/>
+      </c>
+      <c r="V4" t="str">
+        <v/>
+      </c>
+      <c r="W4" t="str">
+        <v/>
+      </c>
+      <c r="X4" t="str">
+        <v>¥55,000</v>
+      </c>
+      <c r="Y4" t="str">
+        <v/>
+      </c>
+      <c r="Z4" t="str">
+        <v>2026-04-21T12:02:55.901Z</v>
+      </c>
+      <c r="AA4" t="str">
+        <v>2026-04-21T12:02:55.901Z</v>
+      </c>
+      <c r="AB4" t="str">
+        <v/>
+      </c>
+      <c r="AC4" t="str">
+        <v/>
+      </c>
+      <c r="AD4" t="str">
+        <v/>
+      </c>
+      <c r="AE4" t="str">
+        <v/>
+      </c>
+      <c r="AF4" t="str">
+        <v/>
+      </c>
+      <c r="AG4" t="str">
+        <v/>
+      </c>
+      <c r="AH4" t="str">
+        <v/>
+      </c>
+      <c r="AI4" t="str">
+        <v/>
+      </c>
+      <c r="AJ4" t="str">
+        <v/>
+      </c>
+      <c r="AK4" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="AL4" t="str">
+        <v/>
+      </c>
+      <c r="AM4" t="str">
+        <v/>
+      </c>
+      <c r="AN4" t="str">
+        <v>カヴァーフィネスゲームをはじめ、ラフウォーターでのバスボートゲームなど、激しい釣りに耐えうるタフな野外戦用スピニングがLIN258HMである。アルミメタル製のドライブギアは、超高精度マシンカットで「一個一個」「一歯一歯」の工程で歯面の最終仕上げを施すという念の入れ様。噛み合うピニオンギアのデジタル数値に、ドライブギアをミクロンの精度で適合させるという極みの技。リンのシームレスなシルキードライブは、これに加えてギアを支えるハウジングもたわみの発生しない高精度・高剛性のアルミメタル製なのだ。勘合部さえもすべて「一個一個」ミクロンの精度で削り出す。クラフツマンの魂を込めたこの丹念な工程こそが、リンのまるでガタのない強靭な駆動部分を造り出している。リンのハンドルを回せば「噛み合い接触」の感触よりも「スベリ接触」の感触が強めに出ていることが感じていただけると思う。このシルキーな噛み合いこそが、回せば瞬時に立ち上がるロスのないハイパワーと、高次元の感度伝達性を生み出すのだ。なお、メカハウジングとして、可動部には最新の磁性流体シールドで保護。極限の遠心力低減化を追求したローター部分はグラファイトコンポジット製。スプールも限界まで肉抜きされたハニカム構造で耐久性を両立。ハンドルは、最新のメカニカルパワーアシストを施し、もはやワンランク上の機種として使用可能なオーバーパワースペックを持つリールなのだ。世界記録バスのパワーランに耐え得るために、Ｍドラグシステムはスムーズで耐久性・耐力のある高荷重カーボンの多重構造を採用。卓越した追撃性能を具現化したLIN258HMは、バスフィッシングはもちろんのこと、シーバスゲームやノースエリアの巨大鱒族を相手にも存分に威力を発揮。その名のとおり、凛として戦うモンスタースペックのスピニングリールなのだ。 The LIN258HM is a battle reel made to withstand tough and intense fishing. The aluminum gear drive is finished off by carefully machining each gear tooth with extreme precision. The extreme engineering skills employed allow the drive gear to be fitted to the pinion gear with only microns to spare. The seamless silky drive of the LIN is made of high-precision high-rigidity aluminum, which prevents deflection of the supporting gear housing. The precision manufacturing process combined with the soul of the craftsmen who assemble the product are what make the LIN what it is. This silky gear engagement of the LIN is what creates its sensitivity and creates the high power that engages immediately when turning the handle. Furthermore, in the mechanical housing, the moving parts are protected with the latest magnetic fluid shield. The rotor is made from lightweight graphite composites to reduce centrifugal force and increase stability. The spool also has also undergone weight reduction, implementing a durable honeycomb construction. The mechanical power assist of the handle gives it power equal to higher spec'd models. In order to withstand the power of world record size bass, the M drag system is incorporated with its multiple structured, smooth, durable, heavyweight carbon. The LIN258HM is a powerful spinning reel that shows excellent performance when dealing with bass, sea bass, and large trout species.</v>
+      </c>
+      <c r="AO4" t="str">
+        <v/>
+      </c>
+      <c r="AP4" t="str">
+        <v/>
+      </c>
+      <c r="AQ4" t="str">
+        <v/>
+      </c>
+      <c r="AR4" t="str">
+        <v/>
+      </c>
+      <c r="AS4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>MRED50003</v>
+      </c>
+      <c r="B5" t="str">
+        <v>MRE5003</v>
+      </c>
+      <c r="C5" t="str">
+        <v>RC-IDATEN 256</v>
+      </c>
+      <c r="D5" t="str">
+        <v>5.66</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v>3.0</v>
+      </c>
+      <c r="G5" t="str">
+        <v>215</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v>4lb./190m / 5lb/150m</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v>84</v>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v>7/1</v>
+      </c>
+      <c r="R5" t="str">
+        <v/>
+      </c>
+      <c r="S5" t="str">
+        <v/>
+      </c>
+      <c r="T5" t="str">
+        <v/>
+      </c>
+      <c r="U5" t="str">
+        <v/>
+      </c>
+      <c r="V5" t="str">
+        <v/>
+      </c>
+      <c r="W5" t="str">
+        <v/>
+      </c>
+      <c r="X5" t="str">
+        <v>¥59,800</v>
+      </c>
+      <c r="Y5" t="str">
+        <v/>
+      </c>
+      <c r="Z5" t="str">
+        <v>2026-04-21T12:02:56.380Z</v>
+      </c>
+      <c r="AA5" t="str">
+        <v>2026-04-21T12:02:56.380Z</v>
+      </c>
+      <c r="AB5" t="str">
+        <v/>
+      </c>
+      <c r="AC5" t="str">
+        <v/>
+      </c>
+      <c r="AD5" t="str">
+        <v/>
+      </c>
+      <c r="AE5" t="str">
+        <v/>
+      </c>
+      <c r="AF5" t="str">
+        <v/>
+      </c>
+      <c r="AG5" t="str">
+        <v/>
+      </c>
+      <c r="AH5" t="str">
+        <v/>
+      </c>
+      <c r="AI5" t="str">
+        <v/>
+      </c>
+      <c r="AJ5" t="str">
+        <v/>
+      </c>
+      <c r="AK5" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="AL5" t="str">
+        <v/>
+      </c>
+      <c r="AM5" t="str">
+        <v/>
+      </c>
+      <c r="AN5" t="str">
+        <v>「レーシングコンディション256」の軽量コンセプトとパッケージングレイアウトを踏襲し、ハンドル一回転におけるローター回転を高速化。ハンドル一巻きのライン巻き上げ量を大幅にアップした高速リールが、「IDATENプロジェクト」の最新形態として、遂に具現化。ハイスピードスピニングリールで痩せがちだった巻き上げトルクは、IDATEN256が過去のものとしています。「スピード」と「パワー」、この相反する要素の最大公約数にジャストミートさせた新たなIDATENが、効率よく釣り勝つためのハイテンポなフィネスゲームを展開します。 RC-IDATEN 256 inherits the Racing Condition 256 model’s lightweight concept, while at the same time delivering faster rotor rotation per handle turn.RC-IDATEN 256 has been tuned for blazing speed without stripping away underlying power, bringing a new standard of high-speed gearing and power. Increased retrieve speed without the loss of lightness or power: this is the latest core incarnation of the IDATEN reel project.Experience the perfect combination of speed and power with the new IDATEN 256. * The photograph is a prototype もはやこれ以上はない堅牢さと軽量化を高次元で両立させた、メガバス独自のメタル削り出し構造による「ハイメタル・ハニカムスプール」は、「磁性流体シールドシステム」の開発によって、スピニングリールにおける理想的なヘッドバランスを実現。その超軽量マイクロボディが発揮してしまう、およそ似合わないハイパワーは、究極のフィネスアプローチでレコードフィッシュと真っ向からわたり合うためのエクストリームなスペック。</v>
+      </c>
+      <c r="AO5" t="str">
+        <v/>
+      </c>
+      <c r="AP5" t="str">
+        <v/>
+      </c>
+      <c r="AQ5" t="str">
+        <v/>
+      </c>
+      <c r="AR5" t="str">
+        <v/>
+      </c>
+      <c r="AS5" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AS3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AS5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU17"/>
+  <dimension ref="A1:BI15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2079,111 +2294,153 @@
         <v>spool_weight_g</v>
       </c>
       <c r="U1" t="str">
+        <v>spool_axis_type</v>
+      </c>
+      <c r="V1" t="str">
+        <v>knob_size</v>
+      </c>
+      <c r="W1" t="str">
+        <v>knob_bearing_spec</v>
+      </c>
+      <c r="X1" t="str">
+        <v>custom_spool_compatibility</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>custom_knob_compatibility</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>official_environment</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>line_capacity_display</v>
+      </c>
+      <c r="AB1" t="str">
         <v>handle_knob_type</v>
       </c>
-      <c r="V1" t="str">
+      <c r="AC1" t="str">
         <v>handle_knob_exchange_size</v>
       </c>
-      <c r="W1" t="str">
+      <c r="AD1" t="str">
         <v>body_material</v>
       </c>
-      <c r="X1" t="str">
+      <c r="AE1" t="str">
         <v>body_material_tech</v>
       </c>
-      <c r="Y1" t="str">
+      <c r="AF1" t="str">
         <v>gear_material</v>
       </c>
-      <c r="Z1" t="str">
+      <c r="AG1" t="str">
         <v>battery_capacity</v>
       </c>
-      <c r="AA1" t="str">
+      <c r="AH1" t="str">
         <v>battery_charge_time</v>
       </c>
-      <c r="AB1" t="str">
+      <c r="AI1" t="str">
         <v>continuous_cast_count</v>
       </c>
-      <c r="AC1" t="str">
+      <c r="AJ1" t="str">
         <v>usage_environment</v>
       </c>
-      <c r="AD1" t="str">
+      <c r="AK1" t="str">
         <v>DRAG</v>
       </c>
-      <c r="AE1" t="str">
+      <c r="AL1" t="str">
         <v>Nylon_no_m</v>
       </c>
-      <c r="AF1" t="str">
+      <c r="AM1" t="str">
         <v>fluorocarbon_no_m</v>
       </c>
-      <c r="AG1" t="str">
+      <c r="AN1" t="str">
         <v>drag_click</v>
       </c>
-      <c r="AH1" t="str">
+      <c r="AO1" t="str">
         <v>spool_depth_normalized</v>
       </c>
-      <c r="AI1" t="str">
+      <c r="AP1" t="str">
         <v>gear_ratio_normalized</v>
       </c>
-      <c r="AJ1" t="str">
+      <c r="AQ1" t="str">
         <v>brake_type_normalized</v>
       </c>
-      <c r="AK1" t="str">
+      <c r="AR1" t="str">
         <v>fit_style_tags</v>
       </c>
-      <c r="AL1" t="str">
+      <c r="AS1" t="str">
         <v>min_lure_weight_hint</v>
       </c>
-      <c r="AM1" t="str">
+      <c r="AT1" t="str">
         <v>is_compact_body</v>
       </c>
-      <c r="AN1" t="str">
+      <c r="AU1" t="str">
         <v>handle_style</v>
       </c>
-      <c r="AO1" t="str">
+      <c r="AV1" t="str">
         <v>MAX_DURABILITY</v>
       </c>
-      <c r="AP1" t="str">
+      <c r="AW1" t="str">
         <v>type</v>
       </c>
-      <c r="AQ1" t="str">
-        <v>official_environment</v>
-      </c>
-      <c r="AR1" t="str">
+      <c r="AX1" t="str">
+        <v>is_sw_edition</v>
+      </c>
+      <c r="AY1" t="str">
+        <v>variant_description</v>
+      </c>
+      <c r="AZ1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="BA1" t="str">
+        <v>EV_link</v>
+      </c>
+      <c r="BB1" t="str">
+        <v>Specs_link</v>
+      </c>
+      <c r="BC1" t="str">
+        <v>handle_knob_material</v>
+      </c>
+      <c r="BD1" t="str">
+        <v>handle_hole_spec</v>
+      </c>
+      <c r="BE1" t="str">
+        <v>main_gear_material</v>
+      </c>
+      <c r="BF1" t="str">
+        <v>main_gear_size</v>
+      </c>
+      <c r="BG1" t="str">
+        <v>minor_gear_material</v>
+      </c>
+      <c r="BH1" t="str">
         <v>player_environment</v>
       </c>
-      <c r="AS1" t="str">
+      <c r="BI1" t="str">
         <v>is_handle_double</v>
-      </c>
-      <c r="AT1" t="str">
-        <v>is_sw_edition</v>
-      </c>
-      <c r="AU1" t="str">
-        <v>line_capacity_display</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>MRED50002</v>
+        <v>MRED50004</v>
       </c>
       <c r="B2" t="str">
-        <v>MRE5002</v>
+        <v>MRE5004</v>
       </c>
       <c r="C2" t="str">
-        <v>LIN258HM</v>
+        <v>MONOBLOCK SPECIALE GRIGIO STONE</v>
       </c>
       <c r="D2" t="str">
-        <v>6.0</v>
+        <v>6.8</v>
       </c>
       <c r="E2" t="str">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="F2" t="str">
-        <v>248</v>
+        <v>210</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>6lb./210m / 8lb/150m</v>
+        <v>14lb./120m / 16lb./105m</v>
       </c>
       <c r="I2" t="str">
         <v/>
@@ -2192,25 +2449,25 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="L2" t="str">
         <v/>
       </c>
       <c r="M2" t="str">
-        <v>12/1</v>
+        <v>10/1</v>
       </c>
       <c r="N2" t="str">
-        <v>¥55,000</v>
+        <v>¥92,500</v>
       </c>
       <c r="O2" t="str">
         <v/>
       </c>
       <c r="P2" t="str">
-        <v>2026-04-21T12:02:55.901Z</v>
+        <v>2026-04-21T12:02:57.077Z</v>
       </c>
       <c r="Q2" t="str">
-        <v>2026-04-21T12:02:55.901Z</v>
+        <v>2026-04-21T12:02:57.077Z</v>
       </c>
       <c r="R2" t="str">
         <v/>
@@ -2221,21 +2478,6 @@
       <c r="T2" t="str">
         <v/>
       </c>
-      <c r="U2" t="str">
-        <v/>
-      </c>
-      <c r="V2" t="str">
-        <v/>
-      </c>
-      <c r="W2" t="str">
-        <v>铝</v>
-      </c>
-      <c r="X2" t="str">
-        <v>高精度金属机身 / 磁性流体密封</v>
-      </c>
-      <c r="Y2" t="str">
-        <v/>
-      </c>
       <c r="Z2" t="str">
         <v/>
       </c>
@@ -2246,7 +2488,7 @@
         <v/>
       </c>
       <c r="AC2" t="str">
-        <v/>
+        <v>L/R</v>
       </c>
       <c r="AD2" t="str">
         <v/>
@@ -2270,63 +2512,78 @@
         <v/>
       </c>
       <c r="AK2" t="str">
-        <v>重装,高刚性,精细</v>
+        <v/>
       </c>
       <c r="AL2" t="str">
-        <v>约 3g+</v>
+        <v/>
       </c>
       <c r="AM2" t="str">
         <v/>
       </c>
       <c r="AN2" t="str">
-        <v>单摇臂</v>
+        <v/>
       </c>
       <c r="AO2" t="str">
         <v/>
       </c>
       <c r="AP2" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="AQ2" t="str">
-        <v>淡水路亚</v>
+        <v/>
       </c>
       <c r="AR2" t="str">
-        <v>Cover / 精细重装</v>
+        <v/>
       </c>
       <c r="AS2" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="AT2" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="AU2" t="str">
+        <v/>
+      </c>
+      <c r="AV2" t="str">
+        <v/>
+      </c>
+      <c r="AW2" t="str">
+        <v>drum</v>
+      </c>
+      <c r="AX2" t="str">
+        <v/>
+      </c>
+      <c r="BH2" t="str">
+        <v/>
+      </c>
+      <c r="BI2" t="str">
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>MRED50003</v>
+        <v>MRED50005</v>
       </c>
       <c r="B3" t="str">
-        <v>MRE5003</v>
+        <v>MRE5005</v>
       </c>
       <c r="C3" t="str">
-        <v>RC-IDATEN 256</v>
+        <v>MONOBLOCK SPECIALE ITO-GAMBLER</v>
       </c>
       <c r="D3" t="str">
-        <v>5.66</v>
+        <v>6.8</v>
       </c>
       <c r="E3" t="str">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="F3" t="str">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>4lb./190m / 5lb/150m</v>
+        <v>14lb./120m / 16lb./105m</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -2335,25 +2592,25 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="L3" t="str">
         <v/>
       </c>
       <c r="M3" t="str">
-        <v>7/1</v>
+        <v>10/1</v>
       </c>
       <c r="N3" t="str">
-        <v>¥59,800</v>
+        <v>¥92,500</v>
       </c>
       <c r="O3" t="str">
         <v/>
       </c>
       <c r="P3" t="str">
-        <v>2026-04-21T12:02:56.380Z</v>
+        <v>2026-04-21T12:02:57.755Z</v>
       </c>
       <c r="Q3" t="str">
-        <v>2026-04-21T12:02:56.380Z</v>
+        <v>2026-04-21T12:02:57.755Z</v>
       </c>
       <c r="R3" t="str">
         <v/>
@@ -2364,21 +2621,6 @@
       <c r="T3" t="str">
         <v/>
       </c>
-      <c r="U3" t="str">
-        <v/>
-      </c>
-      <c r="V3" t="str">
-        <v/>
-      </c>
-      <c r="W3" t="str">
-        <v>铝</v>
-      </c>
-      <c r="X3" t="str">
-        <v>高速回收平台</v>
-      </c>
-      <c r="Y3" t="str">
-        <v/>
-      </c>
       <c r="Z3" t="str">
         <v/>
       </c>
@@ -2389,7 +2631,7 @@
         <v/>
       </c>
       <c r="AC3" t="str">
-        <v/>
+        <v>L/R</v>
       </c>
       <c r="AD3" t="str">
         <v/>
@@ -2413,48 +2655,63 @@
         <v/>
       </c>
       <c r="AK3" t="str">
-        <v>高速,精细,泛用</v>
+        <v/>
       </c>
       <c r="AL3" t="str">
-        <v>约 2g+</v>
+        <v/>
       </c>
       <c r="AM3" t="str">
         <v/>
       </c>
       <c r="AN3" t="str">
-        <v>单摇臂</v>
+        <v/>
       </c>
       <c r="AO3" t="str">
         <v/>
       </c>
       <c r="AP3" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="AQ3" t="str">
-        <v>淡水路亚</v>
+        <v/>
       </c>
       <c r="AR3" t="str">
-        <v>快节奏精细</v>
+        <v/>
       </c>
       <c r="AS3" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="AT3" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="AU3" t="str">
+        <v/>
+      </c>
+      <c r="AV3" t="str">
+        <v/>
+      </c>
+      <c r="AW3" t="str">
+        <v>drum</v>
+      </c>
+      <c r="AX3" t="str">
+        <v/>
+      </c>
+      <c r="BH3" t="str">
+        <v/>
+      </c>
+      <c r="BI3" t="str">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>MRED50004</v>
+        <v>MRED50006</v>
       </c>
       <c r="B4" t="str">
-        <v>MRE5004</v>
+        <v>MRE5006</v>
       </c>
       <c r="C4" t="str">
-        <v>MONOBLOCK SPECIALE GRIGIO STONE</v>
+        <v>MONOBLOCK SPECIALE</v>
       </c>
       <c r="D4" t="str">
         <v>6.8</v>
@@ -2493,10 +2750,10 @@
         <v/>
       </c>
       <c r="P4" t="str">
-        <v>2026-04-21T12:02:57.077Z</v>
+        <v>2026-04-21T12:02:58.400Z</v>
       </c>
       <c r="Q4" t="str">
-        <v>2026-04-21T12:02:57.077Z</v>
+        <v>2026-04-21T12:02:58.400Z</v>
       </c>
       <c r="R4" t="str">
         <v/>
@@ -2507,33 +2764,18 @@
       <c r="T4" t="str">
         <v/>
       </c>
-      <c r="U4" t="str">
-        <v/>
-      </c>
-      <c r="V4" t="str">
+      <c r="Z4" t="str">
+        <v/>
+      </c>
+      <c r="AA4" t="str">
+        <v/>
+      </c>
+      <c r="AB4" t="str">
+        <v/>
+      </c>
+      <c r="AC4" t="str">
         <v>L/R</v>
       </c>
-      <c r="W4" t="str">
-        <v>铝</v>
-      </c>
-      <c r="X4" t="str">
-        <v>Monoblock 进化平台</v>
-      </c>
-      <c r="Y4" t="str">
-        <v/>
-      </c>
-      <c r="Z4" t="str">
-        <v/>
-      </c>
-      <c r="AA4" t="str">
-        <v/>
-      </c>
-      <c r="AB4" t="str">
-        <v/>
-      </c>
-      <c r="AC4" t="str">
-        <v/>
-      </c>
       <c r="AD4" t="str">
         <v/>
       </c>
@@ -2556,63 +2798,78 @@
         <v/>
       </c>
       <c r="AK4" t="str">
-        <v>复古,收藏,顶水</v>
+        <v/>
       </c>
       <c r="AL4" t="str">
-        <v>约 7g+</v>
+        <v/>
       </c>
       <c r="AM4" t="str">
         <v/>
       </c>
       <c r="AN4" t="str">
-        <v>单摇臂</v>
+        <v/>
       </c>
       <c r="AO4" t="str">
         <v/>
       </c>
       <c r="AP4" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="AQ4" t="str">
-        <v>淡水路亚</v>
+        <v/>
       </c>
       <c r="AR4" t="str">
-        <v>顶水 / 收藏</v>
+        <v/>
       </c>
       <c r="AS4" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="AT4" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="AU4" t="str">
+        <v/>
+      </c>
+      <c r="AV4" t="str">
+        <v/>
+      </c>
+      <c r="AW4" t="str">
+        <v>drum</v>
+      </c>
+      <c r="AX4" t="str">
+        <v/>
+      </c>
+      <c r="BH4" t="str">
+        <v/>
+      </c>
+      <c r="BI4" t="str">
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>MRED50005</v>
+        <v>MRED50007</v>
       </c>
       <c r="B5" t="str">
-        <v>MRE5005</v>
+        <v>MRE5007</v>
       </c>
       <c r="C5" t="str">
-        <v>MONOBLOCK SPECIALE ITO-GAMBLER</v>
+        <v>RHODIUM 73</v>
       </c>
       <c r="D5" t="str">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="E5" t="str">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F5" t="str">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>14lb./120m / 16lb./105m</v>
+        <v>16lb. / 80m</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -2621,25 +2878,25 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L5" t="str">
         <v/>
       </c>
       <c r="M5" t="str">
-        <v>10/1</v>
+        <v>6/1</v>
       </c>
       <c r="N5" t="str">
-        <v>¥92,500</v>
+        <v>¥32,000</v>
       </c>
       <c r="O5" t="str">
         <v/>
       </c>
       <c r="P5" t="str">
-        <v>2026-04-21T12:02:57.755Z</v>
+        <v>2026-04-21T12:02:59.044Z</v>
       </c>
       <c r="Q5" t="str">
-        <v>2026-04-21T12:02:57.755Z</v>
+        <v>2026-04-21T12:02:59.044Z</v>
       </c>
       <c r="R5" t="str">
         <v/>
@@ -2650,21 +2907,6 @@
       <c r="T5" t="str">
         <v/>
       </c>
-      <c r="U5" t="str">
-        <v/>
-      </c>
-      <c r="V5" t="str">
-        <v>L/R</v>
-      </c>
-      <c r="W5" t="str">
-        <v>铝</v>
-      </c>
-      <c r="X5" t="str">
-        <v>Monoblock 进化平台</v>
-      </c>
-      <c r="Y5" t="str">
-        <v/>
-      </c>
       <c r="Z5" t="str">
         <v/>
       </c>
@@ -2699,63 +2941,78 @@
         <v/>
       </c>
       <c r="AK5" t="str">
-        <v>复古,收藏,顶水</v>
+        <v/>
       </c>
       <c r="AL5" t="str">
-        <v>约 7g+</v>
+        <v/>
       </c>
       <c r="AM5" t="str">
         <v/>
       </c>
       <c r="AN5" t="str">
-        <v>单摇臂</v>
+        <v/>
       </c>
       <c r="AO5" t="str">
         <v/>
       </c>
       <c r="AP5" t="str">
+        <v/>
+      </c>
+      <c r="AQ5" t="str">
+        <v/>
+      </c>
+      <c r="AR5" t="str">
+        <v/>
+      </c>
+      <c r="AS5" t="str">
+        <v/>
+      </c>
+      <c r="AT5" t="str">
+        <v/>
+      </c>
+      <c r="AU5" t="str">
+        <v/>
+      </c>
+      <c r="AV5" t="str">
+        <v/>
+      </c>
+      <c r="AW5" t="str">
         <v>baitcasting</v>
       </c>
-      <c r="AQ5" t="str">
-        <v>淡水路亚</v>
-      </c>
-      <c r="AR5" t="str">
-        <v>顶水 / 收藏</v>
-      </c>
-      <c r="AS5" t="str">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="str">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="str">
+      <c r="AX5" t="str">
+        <v/>
+      </c>
+      <c r="BH5" t="str">
+        <v/>
+      </c>
+      <c r="BI5" t="str">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>MRED50006</v>
+        <v>MRED50008</v>
       </c>
       <c r="B6" t="str">
-        <v>MRE5006</v>
+        <v>MRE5008</v>
       </c>
       <c r="C6" t="str">
-        <v>MONOBLOCK SPECIALE</v>
+        <v>RHODIUM 81</v>
       </c>
       <c r="D6" t="str">
-        <v>6.8</v>
+        <v>8.1</v>
       </c>
       <c r="E6" t="str">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F6" t="str">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>14lb./120m / 16lb./105m</v>
+        <v>16lb. / 80m</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -2764,25 +3021,25 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="L6" t="str">
         <v/>
       </c>
       <c r="M6" t="str">
-        <v>10/1</v>
+        <v>6/1</v>
       </c>
       <c r="N6" t="str">
-        <v>¥92,500</v>
+        <v>¥32,000</v>
       </c>
       <c r="O6" t="str">
         <v/>
       </c>
       <c r="P6" t="str">
-        <v>2026-04-21T12:02:58.400Z</v>
+        <v>2026-04-21T12:02:59.672Z</v>
       </c>
       <c r="Q6" t="str">
-        <v>2026-04-21T12:02:58.400Z</v>
+        <v>2026-04-21T12:02:59.672Z</v>
       </c>
       <c r="R6" t="str">
         <v/>
@@ -2793,21 +3050,6 @@
       <c r="T6" t="str">
         <v/>
       </c>
-      <c r="U6" t="str">
-        <v/>
-      </c>
-      <c r="V6" t="str">
-        <v>L/R</v>
-      </c>
-      <c r="W6" t="str">
-        <v>铝</v>
-      </c>
-      <c r="X6" t="str">
-        <v>高性能 Monoblock 平台</v>
-      </c>
-      <c r="Y6" t="str">
-        <v/>
-      </c>
       <c r="Z6" t="str">
         <v/>
       </c>
@@ -2842,51 +3084,66 @@
         <v/>
       </c>
       <c r="AK6" t="str">
-        <v>高端,重装,快饵</v>
+        <v/>
       </c>
       <c r="AL6" t="str">
-        <v>约 7g+</v>
+        <v/>
       </c>
       <c r="AM6" t="str">
         <v/>
       </c>
       <c r="AN6" t="str">
-        <v>单摇臂</v>
+        <v/>
       </c>
       <c r="AO6" t="str">
         <v/>
       </c>
       <c r="AP6" t="str">
+        <v/>
+      </c>
+      <c r="AQ6" t="str">
+        <v/>
+      </c>
+      <c r="AR6" t="str">
+        <v/>
+      </c>
+      <c r="AS6" t="str">
+        <v/>
+      </c>
+      <c r="AT6" t="str">
+        <v/>
+      </c>
+      <c r="AU6" t="str">
+        <v/>
+      </c>
+      <c r="AV6" t="str">
+        <v/>
+      </c>
+      <c r="AW6" t="str">
         <v>baitcasting</v>
       </c>
-      <c r="AQ6" t="str">
-        <v>淡水路亚</v>
-      </c>
-      <c r="AR6" t="str">
-        <v>快饵 / 重装</v>
-      </c>
-      <c r="AS6" t="str">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="str">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="str">
+      <c r="AX6" t="str">
+        <v/>
+      </c>
+      <c r="BH6" t="str">
+        <v/>
+      </c>
+      <c r="BI6" t="str">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>MRED50007</v>
+        <v>MRED50009</v>
       </c>
       <c r="B7" t="str">
-        <v>MRE5007</v>
+        <v>MRE5009</v>
       </c>
       <c r="C7" t="str">
-        <v>RHODIUM 73</v>
+        <v>RHODIUM 63</v>
       </c>
       <c r="D7" t="str">
-        <v>7.3</v>
+        <v>6.3</v>
       </c>
       <c r="E7" t="str">
         <v>5.0</v>
@@ -2907,7 +3164,7 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="L7" t="str">
         <v/>
@@ -2922,10 +3179,10 @@
         <v/>
       </c>
       <c r="P7" t="str">
-        <v>2026-04-21T12:02:59.044Z</v>
+        <v>2026-04-21T12:03:00.367Z</v>
       </c>
       <c r="Q7" t="str">
-        <v>2026-04-21T12:02:59.044Z</v>
+        <v>2026-04-21T12:03:00.367Z</v>
       </c>
       <c r="R7" t="str">
         <v/>
@@ -2936,21 +3193,6 @@
       <c r="T7" t="str">
         <v/>
       </c>
-      <c r="U7" t="str">
-        <v/>
-      </c>
-      <c r="V7" t="str">
-        <v/>
-      </c>
-      <c r="W7" t="str">
-        <v>金属机身</v>
-      </c>
-      <c r="X7" t="str">
-        <v>AIR 制动系统 / 超轻量SV线杯</v>
-      </c>
-      <c r="Y7" t="str">
-        <v/>
-      </c>
       <c r="Z7" t="str">
         <v/>
       </c>
@@ -2985,63 +3227,78 @@
         <v/>
       </c>
       <c r="AK7" t="str">
-        <v>鲈鱼,高速,cover</v>
+        <v/>
       </c>
       <c r="AL7" t="str">
-        <v>约 5g+</v>
+        <v/>
       </c>
       <c r="AM7" t="str">
         <v/>
       </c>
       <c r="AN7" t="str">
-        <v>单摇臂</v>
+        <v/>
       </c>
       <c r="AO7" t="str">
         <v/>
       </c>
       <c r="AP7" t="str">
+        <v/>
+      </c>
+      <c r="AQ7" t="str">
+        <v/>
+      </c>
+      <c r="AR7" t="str">
+        <v/>
+      </c>
+      <c r="AS7" t="str">
+        <v/>
+      </c>
+      <c r="AT7" t="str">
+        <v/>
+      </c>
+      <c r="AU7" t="str">
+        <v/>
+      </c>
+      <c r="AV7" t="str">
+        <v/>
+      </c>
+      <c r="AW7" t="str">
         <v>baitcasting</v>
       </c>
-      <c r="AQ7" t="str">
-        <v>淡水路亚</v>
-      </c>
-      <c r="AR7" t="str">
-        <v>鲈鱼 / Cover</v>
-      </c>
-      <c r="AS7" t="str">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="str">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="str">
+      <c r="AX7" t="str">
+        <v/>
+      </c>
+      <c r="BH7" t="str">
+        <v/>
+      </c>
+      <c r="BI7" t="str">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>MRED50008</v>
+        <v>MRED50010</v>
       </c>
       <c r="B8" t="str">
-        <v>MRE5008</v>
+        <v>MRE5010</v>
       </c>
       <c r="C8" t="str">
-        <v>RHODIUM 81</v>
+        <v>Pagani R100</v>
       </c>
       <c r="D8" t="str">
-        <v>8.1</v>
+        <v>5.1 : 1</v>
       </c>
       <c r="E8" t="str">
-        <v>5.0</v>
+        <v>2.5</v>
       </c>
       <c r="F8" t="str">
-        <v>200</v>
+        <v>255</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>16lb. / 80m</v>
+        <v>8lb./100yd / 10lb./75yd</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -3050,25 +3307,25 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>83</v>
+        <v/>
       </c>
       <c r="L8" t="str">
         <v/>
       </c>
       <c r="M8" t="str">
-        <v>6/1</v>
+        <v>5/0</v>
       </c>
       <c r="N8" t="str">
-        <v>¥32,000</v>
+        <v>¥42,800</v>
       </c>
       <c r="O8" t="str">
         <v/>
       </c>
       <c r="P8" t="str">
-        <v>2026-04-21T12:02:59.672Z</v>
+        <v>2026-04-21T12:03:00.881Z</v>
       </c>
       <c r="Q8" t="str">
-        <v>2026-04-21T12:02:59.672Z</v>
+        <v>2026-04-21T12:03:00.881Z</v>
       </c>
       <c r="R8" t="str">
         <v/>
@@ -3079,21 +3336,6 @@
       <c r="T8" t="str">
         <v/>
       </c>
-      <c r="U8" t="str">
-        <v/>
-      </c>
-      <c r="V8" t="str">
-        <v/>
-      </c>
-      <c r="W8" t="str">
-        <v>金属机身</v>
-      </c>
-      <c r="X8" t="str">
-        <v>AIR 制动系统 / 超轻量SV线杯</v>
-      </c>
-      <c r="Y8" t="str">
-        <v/>
-      </c>
       <c r="Z8" t="str">
         <v/>
       </c>
@@ -3104,7 +3346,7 @@
         <v/>
       </c>
       <c r="AC8" t="str">
-        <v/>
+        <v>L/R</v>
       </c>
       <c r="AD8" t="str">
         <v/>
@@ -3128,63 +3370,78 @@
         <v/>
       </c>
       <c r="AK8" t="str">
-        <v>鲈鱼,超高速,cover</v>
+        <v/>
       </c>
       <c r="AL8" t="str">
-        <v>约 5g+</v>
+        <v/>
       </c>
       <c r="AM8" t="str">
         <v/>
       </c>
       <c r="AN8" t="str">
-        <v>单摇臂</v>
+        <v/>
       </c>
       <c r="AO8" t="str">
         <v/>
       </c>
       <c r="AP8" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="AQ8" t="str">
-        <v>淡水路亚</v>
+        <v/>
       </c>
       <c r="AR8" t="str">
-        <v>鲈鱼 / 快搜</v>
+        <v/>
       </c>
       <c r="AS8" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="AT8" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="AU8" t="str">
+        <v/>
+      </c>
+      <c r="AV8" t="str">
+        <v/>
+      </c>
+      <c r="AW8" t="str">
+        <v>drum</v>
+      </c>
+      <c r="AX8" t="str">
+        <v/>
+      </c>
+      <c r="BH8" t="str">
+        <v/>
+      </c>
+      <c r="BI8" t="str">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>MRED50009</v>
+        <v>MRED50011</v>
       </c>
       <c r="B9" t="str">
-        <v>MRE5009</v>
+        <v>MRE5011</v>
       </c>
       <c r="C9" t="str">
-        <v>RHODIUM 63</v>
+        <v>Pagani P200</v>
       </c>
       <c r="D9" t="str">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="E9" t="str">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="F9" t="str">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>16lb. / 80m</v>
+        <v>8lb./155yards、10lb./123yards</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -3193,25 +3450,25 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>65</v>
+        <v/>
       </c>
       <c r="L9" t="str">
         <v/>
       </c>
       <c r="M9" t="str">
-        <v>6/1</v>
+        <v>5/0</v>
       </c>
       <c r="N9" t="str">
-        <v>¥32,000</v>
+        <v>¥41,000</v>
       </c>
       <c r="O9" t="str">
         <v/>
       </c>
       <c r="P9" t="str">
-        <v>2026-04-21T12:03:00.367Z</v>
+        <v>2026-04-21T12:03:01.354Z</v>
       </c>
       <c r="Q9" t="str">
-        <v>2026-04-21T12:03:00.367Z</v>
+        <v>2026-04-21T12:03:01.354Z</v>
       </c>
       <c r="R9" t="str">
         <v/>
@@ -3222,21 +3479,6 @@
       <c r="T9" t="str">
         <v/>
       </c>
-      <c r="U9" t="str">
-        <v/>
-      </c>
-      <c r="V9" t="str">
-        <v/>
-      </c>
-      <c r="W9" t="str">
-        <v>金属机身</v>
-      </c>
-      <c r="X9" t="str">
-        <v>AIR 制动系统 / 超轻量SV线杯</v>
-      </c>
-      <c r="Y9" t="str">
-        <v/>
-      </c>
       <c r="Z9" t="str">
         <v/>
       </c>
@@ -3247,7 +3489,7 @@
         <v/>
       </c>
       <c r="AC9" t="str">
-        <v/>
+        <v>L/R</v>
       </c>
       <c r="AD9" t="str">
         <v/>
@@ -3271,63 +3513,78 @@
         <v/>
       </c>
       <c r="AK9" t="str">
-        <v>低速,扭矩,卷阻饵</v>
+        <v/>
       </c>
       <c r="AL9" t="str">
-        <v>约 7g+</v>
+        <v/>
       </c>
       <c r="AM9" t="str">
         <v/>
       </c>
       <c r="AN9" t="str">
-        <v>单摇臂</v>
+        <v/>
       </c>
       <c r="AO9" t="str">
         <v/>
       </c>
       <c r="AP9" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="AQ9" t="str">
-        <v>淡水路亚</v>
+        <v/>
       </c>
       <c r="AR9" t="str">
-        <v>卷阻饵 / 扭矩</v>
+        <v/>
       </c>
       <c r="AS9" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="AT9" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="AU9" t="str">
+        <v/>
+      </c>
+      <c r="AV9" t="str">
+        <v/>
+      </c>
+      <c r="AW9" t="str">
+        <v>drum</v>
+      </c>
+      <c r="AX9" t="str">
+        <v/>
+      </c>
+      <c r="BH9" t="str">
+        <v/>
+      </c>
+      <c r="BI9" t="str">
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>MRED50010</v>
+        <v>MRED50012</v>
       </c>
       <c r="B10" t="str">
-        <v>MRE5010</v>
+        <v>MRE5012</v>
       </c>
       <c r="C10" t="str">
-        <v>Pagani R100</v>
+        <v>Pagani P300</v>
       </c>
       <c r="D10" t="str">
-        <v>5.1 : 1</v>
+        <v>6.1</v>
       </c>
       <c r="E10" t="str">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="F10" t="str">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>8lb./100yd / 10lb./75yd</v>
+        <v>8lb./200yd / 10lb./160yd / 12lb./135yd</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -3345,16 +3602,16 @@
         <v>5/0</v>
       </c>
       <c r="N10" t="str">
-        <v>¥42,800</v>
+        <v>¥40,000</v>
       </c>
       <c r="O10" t="str">
         <v/>
       </c>
       <c r="P10" t="str">
-        <v>2026-04-21T12:03:00.881Z</v>
+        <v>2026-04-21T12:03:01.851Z</v>
       </c>
       <c r="Q10" t="str">
-        <v>2026-04-21T12:03:00.881Z</v>
+        <v>2026-04-21T12:03:01.851Z</v>
       </c>
       <c r="R10" t="str">
         <v/>
@@ -3365,33 +3622,18 @@
       <c r="T10" t="str">
         <v/>
       </c>
-      <c r="U10" t="str">
-        <v/>
-      </c>
-      <c r="V10" t="str">
+      <c r="Z10" t="str">
+        <v/>
+      </c>
+      <c r="AA10" t="str">
+        <v/>
+      </c>
+      <c r="AB10" t="str">
+        <v/>
+      </c>
+      <c r="AC10" t="str">
         <v>L/R</v>
       </c>
-      <c r="W10" t="str">
-        <v>复古金属机体</v>
-      </c>
-      <c r="X10" t="str">
-        <v>Quatro Servo Brake</v>
-      </c>
-      <c r="Y10" t="str">
-        <v/>
-      </c>
-      <c r="Z10" t="str">
-        <v/>
-      </c>
-      <c r="AA10" t="str">
-        <v/>
-      </c>
-      <c r="AB10" t="str">
-        <v/>
-      </c>
-      <c r="AC10" t="str">
-        <v/>
-      </c>
       <c r="AD10" t="str">
         <v/>
       </c>
@@ -3414,63 +3656,78 @@
         <v/>
       </c>
       <c r="AK10" t="str">
-        <v>复古,顶水,收藏</v>
+        <v/>
       </c>
       <c r="AL10" t="str">
-        <v>约 7g+</v>
+        <v/>
       </c>
       <c r="AM10" t="str">
         <v/>
       </c>
       <c r="AN10" t="str">
-        <v>单摇臂</v>
+        <v/>
       </c>
       <c r="AO10" t="str">
         <v/>
       </c>
       <c r="AP10" t="str">
-        <v>baitcasting</v>
+        <v/>
       </c>
       <c r="AQ10" t="str">
-        <v>淡水路亚</v>
+        <v/>
       </c>
       <c r="AR10" t="str">
-        <v>顶水 / 风格</v>
+        <v/>
       </c>
       <c r="AS10" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="AT10" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="AU10" t="str">
+        <v/>
+      </c>
+      <c r="AV10" t="str">
+        <v/>
+      </c>
+      <c r="AW10" t="str">
+        <v>drum</v>
+      </c>
+      <c r="AX10" t="str">
+        <v/>
+      </c>
+      <c r="BH10" t="str">
+        <v/>
+      </c>
+      <c r="BI10" t="str">
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>MRED50011</v>
+        <v>MRED50013</v>
       </c>
       <c r="B11" t="str">
-        <v>MRE5011</v>
+        <v>MRE5013</v>
       </c>
       <c r="C11" t="str">
-        <v>Pagani P200</v>
+        <v>LAUDA58</v>
       </c>
       <c r="D11" t="str">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="E11" t="str">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="F11" t="str">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>8lb./155yards、10lb./123yards</v>
+        <v>12lb./40-80m / 14lb./35-70m</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -3479,25 +3736,25 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v/>
+        <v>60</v>
       </c>
       <c r="L11" t="str">
         <v/>
       </c>
       <c r="M11" t="str">
-        <v>5/0</v>
+        <v>6/1</v>
       </c>
       <c r="N11" t="str">
-        <v>¥41,000</v>
+        <v>¥38,500</v>
       </c>
       <c r="O11" t="str">
         <v/>
       </c>
       <c r="P11" t="str">
-        <v>2026-04-21T12:03:01.354Z</v>
+        <v>2026-04-21T12:03:02.339Z</v>
       </c>
       <c r="Q11" t="str">
-        <v>2026-04-21T12:03:01.354Z</v>
+        <v>2026-04-21T12:03:02.339Z</v>
       </c>
       <c r="R11" t="str">
         <v/>
@@ -3508,33 +3765,18 @@
       <c r="T11" t="str">
         <v/>
       </c>
-      <c r="U11" t="str">
-        <v/>
-      </c>
-      <c r="V11" t="str">
+      <c r="Z11" t="str">
+        <v/>
+      </c>
+      <c r="AA11" t="str">
+        <v/>
+      </c>
+      <c r="AB11" t="str">
+        <v/>
+      </c>
+      <c r="AC11" t="str">
         <v>L/R</v>
       </c>
-      <c r="W11" t="str">
-        <v>复古金属机体</v>
-      </c>
-      <c r="X11" t="str">
-        <v>Quatro Servo Brake</v>
-      </c>
-      <c r="Y11" t="str">
-        <v/>
-      </c>
-      <c r="Z11" t="str">
-        <v/>
-      </c>
-      <c r="AA11" t="str">
-        <v/>
-      </c>
-      <c r="AB11" t="str">
-        <v/>
-      </c>
-      <c r="AC11" t="str">
-        <v/>
-      </c>
       <c r="AD11" t="str">
         <v/>
       </c>
@@ -3557,63 +3799,78 @@
         <v/>
       </c>
       <c r="AK11" t="str">
-        <v>复古,轻插,收藏</v>
+        <v/>
       </c>
       <c r="AL11" t="str">
-        <v>约 5g+</v>
+        <v/>
       </c>
       <c r="AM11" t="str">
         <v/>
       </c>
       <c r="AN11" t="str">
-        <v>单摇臂</v>
+        <v/>
       </c>
       <c r="AO11" t="str">
         <v/>
       </c>
       <c r="AP11" t="str">
+        <v/>
+      </c>
+      <c r="AQ11" t="str">
+        <v/>
+      </c>
+      <c r="AR11" t="str">
+        <v/>
+      </c>
+      <c r="AS11" t="str">
+        <v/>
+      </c>
+      <c r="AT11" t="str">
+        <v/>
+      </c>
+      <c r="AU11" t="str">
+        <v/>
+      </c>
+      <c r="AV11" t="str">
+        <v/>
+      </c>
+      <c r="AW11" t="str">
         <v>baitcasting</v>
       </c>
-      <c r="AQ11" t="str">
-        <v>淡水路亚</v>
-      </c>
-      <c r="AR11" t="str">
-        <v>顶水 / 风格</v>
-      </c>
-      <c r="AS11" t="str">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="str">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="str">
+      <c r="AX11" t="str">
+        <v/>
+      </c>
+      <c r="BH11" t="str">
+        <v/>
+      </c>
+      <c r="BI11" t="str">
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>MRED50012</v>
+        <v>MRED50014</v>
       </c>
       <c r="B12" t="str">
-        <v>MRE5012</v>
+        <v>MRE5014</v>
       </c>
       <c r="C12" t="str">
-        <v>Pagani P300</v>
+        <v>LAUDA72</v>
       </c>
       <c r="D12" t="str">
-        <v>6.1</v>
+        <v>7.2</v>
       </c>
       <c r="E12" t="str">
-        <v>3</v>
+        <v>4.0</v>
       </c>
       <c r="F12" t="str">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>8lb./200yd / 10lb./160yd / 12lb./135yd</v>
+        <v>12lb./40-80m / 14lb./35-70m</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -3622,25 +3879,25 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v/>
+        <v>73</v>
       </c>
       <c r="L12" t="str">
         <v/>
       </c>
       <c r="M12" t="str">
-        <v>5/0</v>
+        <v>6/1</v>
       </c>
       <c r="N12" t="str">
-        <v>¥40,000</v>
+        <v>¥38,500</v>
       </c>
       <c r="O12" t="str">
         <v/>
       </c>
       <c r="P12" t="str">
-        <v>2026-04-21T12:03:01.851Z</v>
+        <v>2026-04-21T12:03:02.843Z</v>
       </c>
       <c r="Q12" t="str">
-        <v>2026-04-21T12:03:01.851Z</v>
+        <v>2026-04-21T12:03:02.843Z</v>
       </c>
       <c r="R12" t="str">
         <v/>
@@ -3651,33 +3908,18 @@
       <c r="T12" t="str">
         <v/>
       </c>
-      <c r="U12" t="str">
-        <v/>
-      </c>
-      <c r="V12" t="str">
+      <c r="Z12" t="str">
+        <v/>
+      </c>
+      <c r="AA12" t="str">
+        <v/>
+      </c>
+      <c r="AB12" t="str">
+        <v/>
+      </c>
+      <c r="AC12" t="str">
         <v>L/R</v>
       </c>
-      <c r="W12" t="str">
-        <v>复古金属机体</v>
-      </c>
-      <c r="X12" t="str">
-        <v>Pagani 旗舰平台</v>
-      </c>
-      <c r="Y12" t="str">
-        <v/>
-      </c>
-      <c r="Z12" t="str">
-        <v/>
-      </c>
-      <c r="AA12" t="str">
-        <v/>
-      </c>
-      <c r="AB12" t="str">
-        <v/>
-      </c>
-      <c r="AC12" t="str">
-        <v/>
-      </c>
       <c r="AD12" t="str">
         <v/>
       </c>
@@ -3700,57 +3942,72 @@
         <v/>
       </c>
       <c r="AK12" t="str">
-        <v>复古,顶水,大尺寸</v>
+        <v/>
       </c>
       <c r="AL12" t="str">
-        <v>约 10g+</v>
+        <v/>
       </c>
       <c r="AM12" t="str">
         <v/>
       </c>
       <c r="AN12" t="str">
-        <v>单摇臂</v>
+        <v/>
       </c>
       <c r="AO12" t="str">
         <v/>
       </c>
       <c r="AP12" t="str">
+        <v/>
+      </c>
+      <c r="AQ12" t="str">
+        <v/>
+      </c>
+      <c r="AR12" t="str">
+        <v/>
+      </c>
+      <c r="AS12" t="str">
+        <v/>
+      </c>
+      <c r="AT12" t="str">
+        <v/>
+      </c>
+      <c r="AU12" t="str">
+        <v/>
+      </c>
+      <c r="AV12" t="str">
+        <v/>
+      </c>
+      <c r="AW12" t="str">
         <v>baitcasting</v>
       </c>
-      <c r="AQ12" t="str">
-        <v>淡水路亚</v>
-      </c>
-      <c r="AR12" t="str">
-        <v>顶水 / 风格</v>
-      </c>
-      <c r="AS12" t="str">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="str">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="str">
+      <c r="AX12" t="str">
+        <v/>
+      </c>
+      <c r="BH12" t="str">
+        <v/>
+      </c>
+      <c r="BI12" t="str">
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>MRED50013</v>
+        <v>MRED50015</v>
       </c>
       <c r="B13" t="str">
-        <v>MRE5013</v>
+        <v>MRE5015</v>
       </c>
       <c r="C13" t="str">
-        <v>LAUDA58</v>
+        <v>LAUDA72 LIMITED EDITION</v>
       </c>
       <c r="D13" t="str">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="E13" t="str">
         <v>4.0</v>
       </c>
       <c r="F13" t="str">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -3765,7 +4022,7 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="L13" t="str">
         <v/>
@@ -3774,16 +4031,16 @@
         <v>6/1</v>
       </c>
       <c r="N13" t="str">
-        <v>¥38,500</v>
+        <v>¥42,500</v>
       </c>
       <c r="O13" t="str">
         <v/>
       </c>
       <c r="P13" t="str">
-        <v>2026-04-21T12:03:02.339Z</v>
+        <v>2026-04-21T12:03:03.499Z</v>
       </c>
       <c r="Q13" t="str">
-        <v>2026-04-21T12:03:02.339Z</v>
+        <v>2026-04-21T12:03:03.499Z</v>
       </c>
       <c r="R13" t="str">
         <v/>
@@ -3794,33 +4051,18 @@
       <c r="T13" t="str">
         <v/>
       </c>
-      <c r="U13" t="str">
-        <v/>
-      </c>
-      <c r="V13" t="str">
+      <c r="Z13" t="str">
+        <v/>
+      </c>
+      <c r="AA13" t="str">
+        <v/>
+      </c>
+      <c r="AB13" t="str">
+        <v/>
+      </c>
+      <c r="AC13" t="str">
         <v>L/R</v>
       </c>
-      <c r="W13" t="str">
-        <v>铝合金机体</v>
-      </c>
-      <c r="X13" t="str">
-        <v>SV spool / 低速扭矩</v>
-      </c>
-      <c r="Y13" t="str">
-        <v/>
-      </c>
-      <c r="Z13" t="str">
-        <v/>
-      </c>
-      <c r="AA13" t="str">
-        <v/>
-      </c>
-      <c r="AB13" t="str">
-        <v/>
-      </c>
-      <c r="AC13" t="str">
-        <v/>
-      </c>
       <c r="AD13" t="str">
         <v/>
       </c>
@@ -3843,63 +4085,78 @@
         <v/>
       </c>
       <c r="AK13" t="str">
-        <v>低速,卷阻饵,扭矩</v>
+        <v/>
       </c>
       <c r="AL13" t="str">
-        <v>约 5g+</v>
+        <v/>
       </c>
       <c r="AM13" t="str">
         <v/>
       </c>
       <c r="AN13" t="str">
-        <v>单摇臂</v>
+        <v/>
       </c>
       <c r="AO13" t="str">
         <v/>
       </c>
       <c r="AP13" t="str">
+        <v/>
+      </c>
+      <c r="AQ13" t="str">
+        <v/>
+      </c>
+      <c r="AR13" t="str">
+        <v/>
+      </c>
+      <c r="AS13" t="str">
+        <v/>
+      </c>
+      <c r="AT13" t="str">
+        <v/>
+      </c>
+      <c r="AU13" t="str">
+        <v/>
+      </c>
+      <c r="AV13" t="str">
+        <v/>
+      </c>
+      <c r="AW13" t="str">
         <v>baitcasting</v>
       </c>
-      <c r="AQ13" t="str">
-        <v>淡水路亚</v>
-      </c>
-      <c r="AR13" t="str">
-        <v>卷阻饵 / 稳定检索</v>
-      </c>
-      <c r="AS13" t="str">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="str">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="str">
+      <c r="AX13" t="str">
+        <v/>
+      </c>
+      <c r="BH13" t="str">
+        <v/>
+      </c>
+      <c r="BI13" t="str">
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>MRED50014</v>
+        <v>MRED50016</v>
       </c>
       <c r="B14" t="str">
-        <v>MRE5014</v>
+        <v>MRE5016</v>
       </c>
       <c r="C14" t="str">
-        <v>LAUDA72</v>
+        <v>IP79</v>
       </c>
       <c r="D14" t="str">
-        <v>7.2</v>
+        <v>7.9</v>
       </c>
       <c r="E14" t="str">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F14" t="str">
-        <v>170</v>
+        <v>215</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>12lb./40-80m / 14lb./35-70m</v>
+        <v>12lb./135m / 16lb./100m</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -3908,25 +4165,25 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="L14" t="str">
         <v/>
       </c>
       <c r="M14" t="str">
-        <v>6/1</v>
+        <v>10/1</v>
       </c>
       <c r="N14" t="str">
-        <v>¥38,500</v>
+        <v>¥45,000</v>
       </c>
       <c r="O14" t="str">
         <v/>
       </c>
       <c r="P14" t="str">
-        <v>2026-04-21T12:03:02.843Z</v>
+        <v>2026-04-21T12:03:04.131Z</v>
       </c>
       <c r="Q14" t="str">
-        <v>2026-04-21T12:03:02.843Z</v>
+        <v>2026-04-21T12:03:04.131Z</v>
       </c>
       <c r="R14" t="str">
         <v/>
@@ -3937,33 +4194,18 @@
       <c r="T14" t="str">
         <v/>
       </c>
-      <c r="U14" t="str">
-        <v/>
-      </c>
-      <c r="V14" t="str">
+      <c r="Z14" t="str">
+        <v/>
+      </c>
+      <c r="AA14" t="str">
+        <v/>
+      </c>
+      <c r="AB14" t="str">
+        <v/>
+      </c>
+      <c r="AC14" t="str">
         <v>L/R</v>
       </c>
-      <c r="W14" t="str">
-        <v>铝合金机体</v>
-      </c>
-      <c r="X14" t="str">
-        <v>超轻量 duralumin SV spool / 高感度旋钮</v>
-      </c>
-      <c r="Y14" t="str">
-        <v/>
-      </c>
-      <c r="Z14" t="str">
-        <v/>
-      </c>
-      <c r="AA14" t="str">
-        <v/>
-      </c>
-      <c r="AB14" t="str">
-        <v/>
-      </c>
-      <c r="AC14" t="str">
-        <v/>
-      </c>
       <c r="AD14" t="str">
         <v/>
       </c>
@@ -3986,63 +4228,78 @@
         <v/>
       </c>
       <c r="AK14" t="str">
-        <v>高速,远投,鲈鱼</v>
+        <v/>
       </c>
       <c r="AL14" t="str">
-        <v>约 5g+</v>
+        <v/>
       </c>
       <c r="AM14" t="str">
         <v/>
       </c>
       <c r="AN14" t="str">
-        <v>单摇臂</v>
+        <v/>
       </c>
       <c r="AO14" t="str">
         <v/>
       </c>
       <c r="AP14" t="str">
+        <v/>
+      </c>
+      <c r="AQ14" t="str">
+        <v/>
+      </c>
+      <c r="AR14" t="str">
+        <v/>
+      </c>
+      <c r="AS14" t="str">
+        <v/>
+      </c>
+      <c r="AT14" t="str">
+        <v/>
+      </c>
+      <c r="AU14" t="str">
+        <v/>
+      </c>
+      <c r="AV14" t="str">
+        <v/>
+      </c>
+      <c r="AW14" t="str">
         <v>baitcasting</v>
       </c>
-      <c r="AQ14" t="str">
-        <v>淡水路亚</v>
-      </c>
-      <c r="AR14" t="str">
-        <v>鲈鱼 / 快节奏泛用</v>
-      </c>
-      <c r="AS14" t="str">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="str">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="str">
+      <c r="AX14" t="str">
+        <v/>
+      </c>
+      <c r="BH14" t="str">
+        <v/>
+      </c>
+      <c r="BI14" t="str">
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>MRED50015</v>
+        <v>MRED50017</v>
       </c>
       <c r="B15" t="str">
-        <v>MRE5015</v>
+        <v>MRE5017</v>
       </c>
       <c r="C15" t="str">
-        <v>LAUDA72 LIMITED EDITION</v>
+        <v>IP68</v>
       </c>
       <c r="D15" t="str">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="E15" t="str">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F15" t="str">
-        <v>170</v>
+        <v>215</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>12lb./40-80m / 14lb./35-70m</v>
+        <v>12lb./135m / 16lb./100m</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -4051,25 +4308,25 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L15" t="str">
         <v/>
       </c>
       <c r="M15" t="str">
-        <v>6/1</v>
+        <v>10/1</v>
       </c>
       <c r="N15" t="str">
-        <v>¥42,500</v>
+        <v>¥45,000</v>
       </c>
       <c r="O15" t="str">
         <v/>
       </c>
       <c r="P15" t="str">
-        <v>2026-04-21T12:03:03.499Z</v>
+        <v>2026-04-21T12:03:04.627Z</v>
       </c>
       <c r="Q15" t="str">
-        <v>2026-04-21T12:03:03.499Z</v>
+        <v>2026-04-21T12:03:04.627Z</v>
       </c>
       <c r="R15" t="str">
         <v/>
@@ -4080,33 +4337,18 @@
       <c r="T15" t="str">
         <v/>
       </c>
-      <c r="U15" t="str">
-        <v/>
-      </c>
-      <c r="V15" t="str">
+      <c r="Z15" t="str">
+        <v/>
+      </c>
+      <c r="AA15" t="str">
+        <v/>
+      </c>
+      <c r="AB15" t="str">
+        <v/>
+      </c>
+      <c r="AC15" t="str">
         <v>L/R</v>
       </c>
-      <c r="W15" t="str">
-        <v>铝合金机体</v>
-      </c>
-      <c r="X15" t="str">
-        <v>80mm 碳手柄 / 限量轻量版</v>
-      </c>
-      <c r="Y15" t="str">
-        <v/>
-      </c>
-      <c r="Z15" t="str">
-        <v/>
-      </c>
-      <c r="AA15" t="str">
-        <v/>
-      </c>
-      <c r="AB15" t="str">
-        <v/>
-      </c>
-      <c r="AC15" t="str">
-        <v/>
-      </c>
       <c r="AD15" t="str">
         <v/>
       </c>
@@ -4129,329 +4371,57 @@
         <v/>
       </c>
       <c r="AK15" t="str">
-        <v>限量,轻量,高速</v>
+        <v/>
       </c>
       <c r="AL15" t="str">
-        <v>约 5g+</v>
+        <v/>
       </c>
       <c r="AM15" t="str">
         <v/>
       </c>
       <c r="AN15" t="str">
-        <v>单摇臂</v>
+        <v/>
       </c>
       <c r="AO15" t="str">
         <v/>
       </c>
       <c r="AP15" t="str">
+        <v/>
+      </c>
+      <c r="AQ15" t="str">
+        <v/>
+      </c>
+      <c r="AR15" t="str">
+        <v/>
+      </c>
+      <c r="AS15" t="str">
+        <v/>
+      </c>
+      <c r="AT15" t="str">
+        <v/>
+      </c>
+      <c r="AU15" t="str">
+        <v/>
+      </c>
+      <c r="AV15" t="str">
+        <v/>
+      </c>
+      <c r="AW15" t="str">
         <v>baitcasting</v>
       </c>
-      <c r="AQ15" t="str">
-        <v>淡水路亚</v>
-      </c>
-      <c r="AR15" t="str">
-        <v>鲈鱼 / 轻量高端</v>
-      </c>
-      <c r="AS15" t="str">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="str">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>MRED50016</v>
-      </c>
-      <c r="B16" t="str">
-        <v>MRE5016</v>
-      </c>
-      <c r="C16" t="str">
-        <v>IP79</v>
-      </c>
-      <c r="D16" t="str">
-        <v>7.9</v>
-      </c>
-      <c r="E16" t="str">
-        <v>5.0</v>
-      </c>
-      <c r="F16" t="str">
-        <v>215</v>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v>12lb./135m / 16lb./100m</v>
-      </c>
-      <c r="I16" t="str">
-        <v/>
-      </c>
-      <c r="J16" t="str">
-        <v/>
-      </c>
-      <c r="K16" t="str">
-        <v>89</v>
-      </c>
-      <c r="L16" t="str">
-        <v/>
-      </c>
-      <c r="M16" t="str">
-        <v>10/1</v>
-      </c>
-      <c r="N16" t="str">
-        <v>¥45,000</v>
-      </c>
-      <c r="O16" t="str">
-        <v/>
-      </c>
-      <c r="P16" t="str">
-        <v>2026-04-21T12:03:04.131Z</v>
-      </c>
-      <c r="Q16" t="str">
-        <v>2026-04-21T12:03:04.131Z</v>
-      </c>
-      <c r="R16" t="str">
-        <v/>
-      </c>
-      <c r="S16" t="str">
-        <v/>
-      </c>
-      <c r="T16" t="str">
-        <v/>
-      </c>
-      <c r="U16" t="str">
-        <v/>
-      </c>
-      <c r="V16" t="str">
-        <v>L/R</v>
-      </c>
-      <c r="W16" t="str">
-        <v>全金属机身</v>
-      </c>
-      <c r="X16" t="str">
-        <v>大口径窄线杯 / 长柄 Power handle</v>
-      </c>
-      <c r="Y16" t="str">
-        <v/>
-      </c>
-      <c r="Z16" t="str">
-        <v/>
-      </c>
-      <c r="AA16" t="str">
-        <v/>
-      </c>
-      <c r="AB16" t="str">
-        <v/>
-      </c>
-      <c r="AC16" t="str">
-        <v/>
-      </c>
-      <c r="AD16" t="str">
-        <v/>
-      </c>
-      <c r="AE16" t="str">
-        <v/>
-      </c>
-      <c r="AF16" t="str">
-        <v/>
-      </c>
-      <c r="AG16" t="str">
-        <v/>
-      </c>
-      <c r="AH16" t="str">
-        <v/>
-      </c>
-      <c r="AI16" t="str">
-        <v/>
-      </c>
-      <c r="AJ16" t="str">
-        <v/>
-      </c>
-      <c r="AK16" t="str">
-        <v>power,高速,重装</v>
-      </c>
-      <c r="AL16" t="str">
-        <v>约 10g+</v>
-      </c>
-      <c r="AM16" t="str">
-        <v/>
-      </c>
-      <c r="AN16" t="str">
-        <v>单摇臂</v>
-      </c>
-      <c r="AO16" t="str">
-        <v/>
-      </c>
-      <c r="AP16" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="AQ16" t="str">
-        <v>淡水路亚</v>
-      </c>
-      <c r="AR16" t="str">
-        <v>Power Fishing</v>
-      </c>
-      <c r="AS16" t="str">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="str">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>MRED50017</v>
-      </c>
-      <c r="B17" t="str">
-        <v>MRE5017</v>
-      </c>
-      <c r="C17" t="str">
-        <v>IP68</v>
-      </c>
-      <c r="D17" t="str">
-        <v>6.8</v>
-      </c>
-      <c r="E17" t="str">
-        <v>5.0</v>
-      </c>
-      <c r="F17" t="str">
-        <v>215</v>
-      </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
-      <c r="H17" t="str">
-        <v>12lb./135m / 16lb./100m</v>
-      </c>
-      <c r="I17" t="str">
-        <v/>
-      </c>
-      <c r="J17" t="str">
-        <v/>
-      </c>
-      <c r="K17" t="str">
-        <v>77</v>
-      </c>
-      <c r="L17" t="str">
-        <v/>
-      </c>
-      <c r="M17" t="str">
-        <v>10/1</v>
-      </c>
-      <c r="N17" t="str">
-        <v>¥45,000</v>
-      </c>
-      <c r="O17" t="str">
-        <v/>
-      </c>
-      <c r="P17" t="str">
-        <v>2026-04-21T12:03:04.627Z</v>
-      </c>
-      <c r="Q17" t="str">
-        <v>2026-04-21T12:03:04.627Z</v>
-      </c>
-      <c r="R17" t="str">
-        <v/>
-      </c>
-      <c r="S17" t="str">
-        <v/>
-      </c>
-      <c r="T17" t="str">
-        <v/>
-      </c>
-      <c r="U17" t="str">
-        <v/>
-      </c>
-      <c r="V17" t="str">
-        <v>L/R</v>
-      </c>
-      <c r="W17" t="str">
-        <v>全金属机身</v>
-      </c>
-      <c r="X17" t="str">
-        <v>高扭矩平台 / Cover cranking</v>
-      </c>
-      <c r="Y17" t="str">
-        <v/>
-      </c>
-      <c r="Z17" t="str">
-        <v/>
-      </c>
-      <c r="AA17" t="str">
-        <v/>
-      </c>
-      <c r="AB17" t="str">
-        <v/>
-      </c>
-      <c r="AC17" t="str">
-        <v/>
-      </c>
-      <c r="AD17" t="str">
-        <v/>
-      </c>
-      <c r="AE17" t="str">
-        <v/>
-      </c>
-      <c r="AF17" t="str">
-        <v/>
-      </c>
-      <c r="AG17" t="str">
-        <v/>
-      </c>
-      <c r="AH17" t="str">
-        <v/>
-      </c>
-      <c r="AI17" t="str">
-        <v/>
-      </c>
-      <c r="AJ17" t="str">
-        <v/>
-      </c>
-      <c r="AK17" t="str">
-        <v>power,扭矩,cover</v>
-      </c>
-      <c r="AL17" t="str">
-        <v>约 10g+</v>
-      </c>
-      <c r="AM17" t="str">
-        <v/>
-      </c>
-      <c r="AN17" t="str">
-        <v>单摇臂</v>
-      </c>
-      <c r="AO17" t="str">
-        <v/>
-      </c>
-      <c r="AP17" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="AQ17" t="str">
-        <v>淡水路亚</v>
-      </c>
-      <c r="AR17" t="str">
-        <v>Power Fishing</v>
-      </c>
-      <c r="AS17" t="str">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="str">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="str">
+      <c r="AX15" t="str">
+        <v/>
+      </c>
+      <c r="BH15" t="str">
+        <v/>
+      </c>
+      <c r="BI15" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AU17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:BI15"/>
   </ignoredErrors>
 </worksheet>
 </file>